--- a/app/templates/shift_export/template.xlsx
+++ b/app/templates/shift_export/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C80E52-5975-4933-9855-7BD2BD60F323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A787171F-54AD-4DF0-AC78-ED89CA9DD176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -200,14 +200,14 @@
     <rPh sb="1" eb="4">
       <t>キボウキュウ</t>
     </rPh>
-    <phoneticPr fontId="11"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>：有休</t>
     <rPh sb="1" eb="3">
       <t>ユウキュウ</t>
     </rPh>
-    <phoneticPr fontId="11"/>
+    <phoneticPr fontId="9"/>
   </si>
 </sst>
 </file>
@@ -217,7 +217,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -266,22 +266,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="19"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <sz val="16"/>
       <color indexed="8"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="12"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -295,6 +281,27 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1125,7 +1132,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1327,320 +1334,179 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="44" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="50" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="44" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="50" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1648,30 +1514,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1681,46 +1526,163 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2929,41 +2891,41 @@
     <row r="2" spans="1:30" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="182" t="s">
+      <c r="C2" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="184" t="s">
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="184" t="s">
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="184" t="s">
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="183"/>
-      <c r="N2" s="183"/>
-      <c r="O2" s="184" t="s">
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="183"/>
-      <c r="Q2" s="183"/>
-      <c r="R2" s="184" t="s">
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="183"/>
-      <c r="T2" s="183"/>
-      <c r="U2" s="172" t="s">
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="173"/>
-      <c r="W2" s="173"/>
+      <c r="V2" s="126"/>
+      <c r="W2" s="126"/>
       <c r="X2" s="6"/>
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
@@ -2975,28 +2937,28 @@
     <row r="3" spans="1:30" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="174"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="176"/>
-      <c r="I3" s="177"/>
-      <c r="J3" s="178"/>
-      <c r="K3" s="176"/>
-      <c r="L3" s="177"/>
-      <c r="M3" s="175"/>
-      <c r="N3" s="176"/>
-      <c r="O3" s="177"/>
-      <c r="P3" s="175"/>
-      <c r="Q3" s="176"/>
-      <c r="R3" s="177"/>
-      <c r="S3" s="175"/>
-      <c r="T3" s="176"/>
-      <c r="U3" s="179"/>
-      <c r="V3" s="180"/>
-      <c r="W3" s="181"/>
-      <c r="X3" s="187" t="s">
+      <c r="C3" s="118"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="117"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="117"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="116"/>
+      <c r="Q3" s="117"/>
+      <c r="R3" s="115"/>
+      <c r="S3" s="116"/>
+      <c r="T3" s="117"/>
+      <c r="U3" s="109"/>
+      <c r="V3" s="110"/>
+      <c r="W3" s="111"/>
+      <c r="X3" s="119" t="s">
         <v>7</v>
       </c>
       <c r="Y3" s="8"/>
@@ -3072,7 +3034,7 @@
       <c r="W4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="X4" s="188"/>
+      <c r="X4" s="120"/>
       <c r="Y4" s="8"/>
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
@@ -3104,7 +3066,7 @@
       <c r="U5" s="23"/>
       <c r="V5" s="24"/>
       <c r="W5" s="25"/>
-      <c r="X5" s="188"/>
+      <c r="X5" s="120"/>
       <c r="Y5" s="8"/>
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
@@ -3136,7 +3098,7 @@
       <c r="U6" s="32"/>
       <c r="V6" s="33"/>
       <c r="W6" s="34"/>
-      <c r="X6" s="188"/>
+      <c r="X6" s="120"/>
       <c r="Y6" s="8"/>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
@@ -3168,7 +3130,7 @@
       <c r="U7" s="32"/>
       <c r="V7" s="33"/>
       <c r="W7" s="34"/>
-      <c r="X7" s="188"/>
+      <c r="X7" s="120"/>
       <c r="Y7" s="8"/>
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
@@ -3200,7 +3162,7 @@
       <c r="U8" s="32"/>
       <c r="V8" s="33"/>
       <c r="W8" s="34"/>
-      <c r="X8" s="188"/>
+      <c r="X8" s="120"/>
       <c r="Y8" s="8"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
@@ -3232,7 +3194,7 @@
       <c r="U9" s="32"/>
       <c r="V9" s="33"/>
       <c r="W9" s="34"/>
-      <c r="X9" s="188"/>
+      <c r="X9" s="120"/>
       <c r="Y9" s="8"/>
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
@@ -3264,7 +3226,7 @@
       <c r="U10" s="32"/>
       <c r="V10" s="33"/>
       <c r="W10" s="34"/>
-      <c r="X10" s="188"/>
+      <c r="X10" s="120"/>
       <c r="Y10" s="8"/>
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
@@ -3296,7 +3258,7 @@
       <c r="U11" s="32"/>
       <c r="V11" s="33"/>
       <c r="W11" s="34"/>
-      <c r="X11" s="188"/>
+      <c r="X11" s="120"/>
       <c r="Y11" s="8"/>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
@@ -3328,7 +3290,7 @@
       <c r="U12" s="32"/>
       <c r="V12" s="33"/>
       <c r="W12" s="34"/>
-      <c r="X12" s="188"/>
+      <c r="X12" s="120"/>
       <c r="Y12" s="8"/>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
@@ -3360,7 +3322,7 @@
       <c r="U13" s="32"/>
       <c r="V13" s="33"/>
       <c r="W13" s="34"/>
-      <c r="X13" s="188"/>
+      <c r="X13" s="120"/>
       <c r="Y13" s="8"/>
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
@@ -3392,7 +3354,7 @@
       <c r="U14" s="32"/>
       <c r="V14" s="33"/>
       <c r="W14" s="34"/>
-      <c r="X14" s="188"/>
+      <c r="X14" s="120"/>
       <c r="Y14" s="8"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
@@ -3424,7 +3386,7 @@
       <c r="U15" s="32"/>
       <c r="V15" s="33"/>
       <c r="W15" s="34"/>
-      <c r="X15" s="188"/>
+      <c r="X15" s="120"/>
       <c r="Y15" s="8"/>
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
@@ -3456,7 +3418,7 @@
       <c r="U16" s="43"/>
       <c r="V16" s="44"/>
       <c r="W16" s="45"/>
-      <c r="X16" s="188"/>
+      <c r="X16" s="120"/>
       <c r="Y16" s="8"/>
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
@@ -3488,7 +3450,7 @@
       <c r="U17" s="54"/>
       <c r="V17" s="55"/>
       <c r="W17" s="56"/>
-      <c r="X17" s="188"/>
+      <c r="X17" s="120"/>
       <c r="Y17" s="57"/>
       <c r="Z17" s="58"/>
       <c r="AA17" s="58"/>
@@ -3562,7 +3524,7 @@
       <c r="W18" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="X18" s="188"/>
+      <c r="X18" s="120"/>
       <c r="Y18" s="65"/>
       <c r="Z18" s="65"/>
       <c r="AA18" s="65"/>
@@ -3572,35 +3534,35 @@
     </row>
     <row r="19" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="59"/>
-      <c r="B19" s="185" t="s">
+      <c r="B19" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="67"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="190"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="70"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="70"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="69"/>
-      <c r="O19" s="70"/>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="69"/>
-      <c r="R19" s="70"/>
-      <c r="S19" s="68"/>
-      <c r="T19" s="69"/>
-      <c r="U19" s="73"/>
-      <c r="V19" s="74"/>
-      <c r="W19" s="69"/>
-      <c r="X19" s="188"/>
-      <c r="Y19" s="75" t="s">
+      <c r="C19" s="131"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="134"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="133"/>
+      <c r="I19" s="134"/>
+      <c r="J19" s="136"/>
+      <c r="K19" s="133"/>
+      <c r="L19" s="134"/>
+      <c r="M19" s="132"/>
+      <c r="N19" s="133"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="137"/>
+      <c r="Q19" s="133"/>
+      <c r="R19" s="134"/>
+      <c r="S19" s="132"/>
+      <c r="T19" s="133"/>
+      <c r="U19" s="134"/>
+      <c r="V19" s="132"/>
+      <c r="W19" s="133"/>
+      <c r="X19" s="120"/>
+      <c r="Y19" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="Z19" s="76">
+      <c r="Z19" s="68">
         <f>COUNTIF(B19:W38,C221)</f>
         <v>0</v>
       </c>
@@ -3611,33 +3573,33 @@
     </row>
     <row r="20" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="59"/>
-      <c r="B20" s="186"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="191"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="80"/>
-      <c r="L20" s="82"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="83"/>
-      <c r="O20" s="81"/>
-      <c r="P20" s="84"/>
-      <c r="Q20" s="80"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="79"/>
-      <c r="T20" s="80"/>
-      <c r="U20" s="85"/>
-      <c r="V20" s="86"/>
-      <c r="W20" s="83"/>
-      <c r="X20" s="188"/>
-      <c r="Y20" s="87" t="s">
+      <c r="B20" s="113"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="142"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="140"/>
+      <c r="L20" s="143"/>
+      <c r="M20" s="139"/>
+      <c r="N20" s="144"/>
+      <c r="O20" s="141"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="140"/>
+      <c r="R20" s="143"/>
+      <c r="S20" s="139"/>
+      <c r="T20" s="140"/>
+      <c r="U20" s="141"/>
+      <c r="V20" s="139"/>
+      <c r="W20" s="144"/>
+      <c r="X20" s="120"/>
+      <c r="Y20" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="Z20" s="88">
+      <c r="Z20" s="70">
         <f>COUNTIF(B19:W38,C222)</f>
         <v>0</v>
       </c>
@@ -3648,33 +3610,33 @@
     </row>
     <row r="21" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="59"/>
-      <c r="B21" s="186"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="191"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="79"/>
-      <c r="K21" s="80"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="79"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="84"/>
-      <c r="Q21" s="83"/>
-      <c r="R21" s="81"/>
-      <c r="S21" s="79"/>
-      <c r="T21" s="83"/>
-      <c r="U21" s="85"/>
-      <c r="V21" s="86"/>
-      <c r="W21" s="83"/>
-      <c r="X21" s="188"/>
-      <c r="Y21" s="87" t="s">
+      <c r="B21" s="113"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="139"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="142"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="141"/>
+      <c r="J21" s="139"/>
+      <c r="K21" s="140"/>
+      <c r="L21" s="143"/>
+      <c r="M21" s="139"/>
+      <c r="N21" s="144"/>
+      <c r="O21" s="141"/>
+      <c r="P21" s="145"/>
+      <c r="Q21" s="144"/>
+      <c r="R21" s="141"/>
+      <c r="S21" s="139"/>
+      <c r="T21" s="144"/>
+      <c r="U21" s="141"/>
+      <c r="V21" s="139"/>
+      <c r="W21" s="144"/>
+      <c r="X21" s="120"/>
+      <c r="Y21" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="Z21" s="88">
+      <c r="Z21" s="70">
         <f>COUNTIF(B19:W38,C223)</f>
         <v>0</v>
       </c>
@@ -3685,33 +3647,33 @@
     </row>
     <row r="22" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="59"/>
-      <c r="B22" s="186"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="79"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="79"/>
-      <c r="N22" s="83"/>
-      <c r="O22" s="82"/>
-      <c r="P22" s="84"/>
-      <c r="Q22" s="83"/>
-      <c r="R22" s="82"/>
-      <c r="S22" s="79"/>
-      <c r="T22" s="83"/>
-      <c r="U22" s="85"/>
-      <c r="V22" s="86"/>
-      <c r="W22" s="83"/>
-      <c r="X22" s="188"/>
-      <c r="Y22" s="87" t="s">
+      <c r="B22" s="113"/>
+      <c r="C22" s="146"/>
+      <c r="D22" s="139"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="143"/>
+      <c r="G22" s="139"/>
+      <c r="H22" s="144"/>
+      <c r="I22" s="143"/>
+      <c r="J22" s="139"/>
+      <c r="K22" s="144"/>
+      <c r="L22" s="143"/>
+      <c r="M22" s="139"/>
+      <c r="N22" s="144"/>
+      <c r="O22" s="143"/>
+      <c r="P22" s="145"/>
+      <c r="Q22" s="144"/>
+      <c r="R22" s="143"/>
+      <c r="S22" s="139"/>
+      <c r="T22" s="144"/>
+      <c r="U22" s="141"/>
+      <c r="V22" s="139"/>
+      <c r="W22" s="144"/>
+      <c r="X22" s="120"/>
+      <c r="Y22" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="Z22" s="88">
+      <c r="Z22" s="70">
         <f>COUNTIF(B19:W38,C224)</f>
         <v>0</v>
       </c>
@@ -3722,33 +3684,33 @@
     </row>
     <row r="23" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="59"/>
-      <c r="B23" s="189"/>
-      <c r="C23" s="91"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="94"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="93"/>
-      <c r="I23" s="95"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="93"/>
-      <c r="L23" s="96"/>
-      <c r="M23" s="92"/>
-      <c r="N23" s="93"/>
-      <c r="O23" s="94"/>
-      <c r="P23" s="97"/>
-      <c r="Q23" s="93"/>
-      <c r="R23" s="98"/>
-      <c r="S23" s="92"/>
-      <c r="T23" s="93"/>
-      <c r="U23" s="99"/>
-      <c r="V23" s="100"/>
-      <c r="W23" s="93"/>
-      <c r="X23" s="188"/>
-      <c r="Y23" s="87" t="s">
+      <c r="B23" s="114"/>
+      <c r="C23" s="147"/>
+      <c r="D23" s="148"/>
+      <c r="E23" s="149"/>
+      <c r="F23" s="150"/>
+      <c r="G23" s="148"/>
+      <c r="H23" s="149"/>
+      <c r="I23" s="151"/>
+      <c r="J23" s="148"/>
+      <c r="K23" s="149"/>
+      <c r="L23" s="152"/>
+      <c r="M23" s="148"/>
+      <c r="N23" s="149"/>
+      <c r="O23" s="150"/>
+      <c r="P23" s="153"/>
+      <c r="Q23" s="149"/>
+      <c r="R23" s="151"/>
+      <c r="S23" s="148"/>
+      <c r="T23" s="149"/>
+      <c r="U23" s="151"/>
+      <c r="V23" s="148"/>
+      <c r="W23" s="149"/>
+      <c r="X23" s="120"/>
+      <c r="Y23" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="Z23" s="88">
+      <c r="Z23" s="70">
         <f>COUNTIF(B19:W38,C225)</f>
         <v>0</v>
       </c>
@@ -3759,35 +3721,35 @@
     </row>
     <row r="24" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="59"/>
-      <c r="B24" s="101" t="s">
+      <c r="B24" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="102"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="103"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="103"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="103"/>
-      <c r="N24" s="104"/>
-      <c r="O24" s="102"/>
-      <c r="P24" s="103"/>
-      <c r="Q24" s="104"/>
-      <c r="R24" s="102"/>
-      <c r="S24" s="105"/>
-      <c r="T24" s="106"/>
-      <c r="U24" s="107"/>
-      <c r="V24" s="105"/>
-      <c r="W24" s="106"/>
-      <c r="X24" s="188"/>
-      <c r="Y24" s="87" t="s">
+      <c r="C24" s="154"/>
+      <c r="D24" s="155"/>
+      <c r="E24" s="156"/>
+      <c r="F24" s="154"/>
+      <c r="G24" s="155"/>
+      <c r="H24" s="156"/>
+      <c r="I24" s="154"/>
+      <c r="J24" s="155"/>
+      <c r="K24" s="156"/>
+      <c r="L24" s="154"/>
+      <c r="M24" s="155"/>
+      <c r="N24" s="156"/>
+      <c r="O24" s="154"/>
+      <c r="P24" s="155"/>
+      <c r="Q24" s="156"/>
+      <c r="R24" s="154"/>
+      <c r="S24" s="157"/>
+      <c r="T24" s="158"/>
+      <c r="U24" s="154"/>
+      <c r="V24" s="157"/>
+      <c r="W24" s="158"/>
+      <c r="X24" s="120"/>
+      <c r="Y24" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="Z24" s="88">
+      <c r="Z24" s="70">
         <f>COUNTIF(B19:W38,C226)</f>
         <v>0</v>
       </c>
@@ -3798,33 +3760,33 @@
     </row>
     <row r="25" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="59"/>
-      <c r="B25" s="192"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="108"/>
-      <c r="E25" s="109"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="109"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="109"/>
-      <c r="L25" s="110"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="109"/>
-      <c r="O25" s="110"/>
-      <c r="P25" s="68"/>
-      <c r="Q25" s="109"/>
-      <c r="R25" s="110"/>
-      <c r="S25" s="68"/>
-      <c r="T25" s="109"/>
-      <c r="U25" s="111"/>
-      <c r="V25" s="68"/>
-      <c r="W25" s="109"/>
-      <c r="X25" s="193"/>
-      <c r="Y25" s="112" t="s">
+      <c r="B25" s="121"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="159"/>
+      <c r="E25" s="160"/>
+      <c r="F25" s="161"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="160"/>
+      <c r="I25" s="161"/>
+      <c r="J25" s="132"/>
+      <c r="K25" s="160"/>
+      <c r="L25" s="161"/>
+      <c r="M25" s="132"/>
+      <c r="N25" s="160"/>
+      <c r="O25" s="161"/>
+      <c r="P25" s="132"/>
+      <c r="Q25" s="160"/>
+      <c r="R25" s="161"/>
+      <c r="S25" s="132"/>
+      <c r="T25" s="160"/>
+      <c r="U25" s="161"/>
+      <c r="V25" s="132"/>
+      <c r="W25" s="160"/>
+      <c r="X25" s="122"/>
+      <c r="Y25" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="Z25" s="88">
+      <c r="Z25" s="70">
         <f>COUNTIF(B19:W38,C227)</f>
         <v>0</v>
       </c>
@@ -3835,33 +3797,33 @@
     </row>
     <row r="26" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="59"/>
-      <c r="B26" s="186"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="113"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="79"/>
-      <c r="H26" s="113"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="114"/>
-      <c r="K26" s="113"/>
-      <c r="L26" s="81"/>
-      <c r="M26" s="79"/>
-      <c r="N26" s="113"/>
-      <c r="O26" s="81"/>
-      <c r="P26" s="79"/>
-      <c r="Q26" s="113"/>
-      <c r="R26" s="81"/>
-      <c r="S26" s="114"/>
-      <c r="T26" s="113"/>
-      <c r="U26" s="85"/>
-      <c r="V26" s="79"/>
-      <c r="W26" s="113"/>
-      <c r="X26" s="194"/>
-      <c r="Y26" s="112" t="s">
+      <c r="B26" s="113"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="162"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="162"/>
+      <c r="I26" s="141"/>
+      <c r="J26" s="163"/>
+      <c r="K26" s="162"/>
+      <c r="L26" s="141"/>
+      <c r="M26" s="139"/>
+      <c r="N26" s="162"/>
+      <c r="O26" s="141"/>
+      <c r="P26" s="139"/>
+      <c r="Q26" s="162"/>
+      <c r="R26" s="141"/>
+      <c r="S26" s="163"/>
+      <c r="T26" s="162"/>
+      <c r="U26" s="141"/>
+      <c r="V26" s="139"/>
+      <c r="W26" s="162"/>
+      <c r="X26" s="123"/>
+      <c r="Y26" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="Z26" s="88">
+      <c r="Z26" s="70">
         <f>COUNTIF(B19:W38,C228)</f>
         <v>0</v>
       </c>
@@ -3872,33 +3834,33 @@
     </row>
     <row r="27" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="59"/>
-      <c r="B27" s="186"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="113"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="79"/>
-      <c r="H27" s="113"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="113"/>
-      <c r="L27" s="81"/>
-      <c r="M27" s="79"/>
-      <c r="N27" s="113"/>
-      <c r="O27" s="81"/>
-      <c r="P27" s="79"/>
-      <c r="Q27" s="113"/>
-      <c r="R27" s="81"/>
-      <c r="S27" s="114"/>
-      <c r="T27" s="113"/>
-      <c r="U27" s="85"/>
-      <c r="V27" s="79"/>
-      <c r="W27" s="113"/>
-      <c r="X27" s="194"/>
-      <c r="Y27" s="112" t="s">
+      <c r="B27" s="113"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="162"/>
+      <c r="F27" s="141"/>
+      <c r="G27" s="139"/>
+      <c r="H27" s="162"/>
+      <c r="I27" s="141"/>
+      <c r="J27" s="163"/>
+      <c r="K27" s="162"/>
+      <c r="L27" s="141"/>
+      <c r="M27" s="139"/>
+      <c r="N27" s="162"/>
+      <c r="O27" s="141"/>
+      <c r="P27" s="139"/>
+      <c r="Q27" s="162"/>
+      <c r="R27" s="141"/>
+      <c r="S27" s="163"/>
+      <c r="T27" s="162"/>
+      <c r="U27" s="141"/>
+      <c r="V27" s="139"/>
+      <c r="W27" s="162"/>
+      <c r="X27" s="123"/>
+      <c r="Y27" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="Z27" s="88">
+      <c r="Z27" s="70">
         <f>COUNTIF(B19:W38,C229)</f>
         <v>0</v>
       </c>
@@ -3909,33 +3871,33 @@
     </row>
     <row r="28" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="59"/>
-      <c r="B28" s="186"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="81"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="81"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="80"/>
-      <c r="L28" s="81"/>
-      <c r="M28" s="79"/>
-      <c r="N28" s="80"/>
-      <c r="O28" s="81"/>
-      <c r="P28" s="79"/>
-      <c r="Q28" s="80"/>
-      <c r="R28" s="81"/>
-      <c r="S28" s="79"/>
-      <c r="T28" s="80"/>
-      <c r="U28" s="85"/>
-      <c r="V28" s="79"/>
-      <c r="W28" s="80"/>
-      <c r="X28" s="115"/>
-      <c r="Y28" s="116" t="s">
+      <c r="B28" s="113"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="139"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="163"/>
+      <c r="H28" s="140"/>
+      <c r="I28" s="141"/>
+      <c r="J28" s="139"/>
+      <c r="K28" s="140"/>
+      <c r="L28" s="141"/>
+      <c r="M28" s="139"/>
+      <c r="N28" s="140"/>
+      <c r="O28" s="141"/>
+      <c r="P28" s="139"/>
+      <c r="Q28" s="140"/>
+      <c r="R28" s="141"/>
+      <c r="S28" s="139"/>
+      <c r="T28" s="140"/>
+      <c r="U28" s="141"/>
+      <c r="V28" s="139"/>
+      <c r="W28" s="140"/>
+      <c r="X28" s="74"/>
+      <c r="Y28" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="Z28" s="117">
+      <c r="Z28" s="76">
         <f>COUNTIF(B19:W38,C230)</f>
         <v>0</v>
       </c>
@@ -3946,29 +3908,29 @@
     </row>
     <row r="29" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="59"/>
-      <c r="B29" s="186"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="113"/>
-      <c r="F29" s="82"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="113"/>
-      <c r="I29" s="82"/>
-      <c r="J29" s="114"/>
-      <c r="K29" s="113"/>
-      <c r="L29" s="82"/>
-      <c r="M29" s="79"/>
-      <c r="N29" s="113"/>
-      <c r="O29" s="82"/>
-      <c r="P29" s="79"/>
-      <c r="Q29" s="113"/>
-      <c r="R29" s="82"/>
-      <c r="S29" s="114"/>
-      <c r="T29" s="113"/>
-      <c r="U29" s="118"/>
-      <c r="V29" s="79"/>
-      <c r="W29" s="113"/>
-      <c r="X29" s="119"/>
+      <c r="B29" s="113"/>
+      <c r="C29" s="146"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="162"/>
+      <c r="F29" s="143"/>
+      <c r="G29" s="139"/>
+      <c r="H29" s="162"/>
+      <c r="I29" s="143"/>
+      <c r="J29" s="163"/>
+      <c r="K29" s="162"/>
+      <c r="L29" s="143"/>
+      <c r="M29" s="139"/>
+      <c r="N29" s="162"/>
+      <c r="O29" s="143"/>
+      <c r="P29" s="139"/>
+      <c r="Q29" s="162"/>
+      <c r="R29" s="143"/>
+      <c r="S29" s="163"/>
+      <c r="T29" s="162"/>
+      <c r="U29" s="143"/>
+      <c r="V29" s="139"/>
+      <c r="W29" s="162"/>
+      <c r="X29" s="77"/>
       <c r="Y29" s="65"/>
       <c r="Z29" s="65"/>
       <c r="AA29" s="65"/>
@@ -3978,29 +3940,29 @@
     </row>
     <row r="30" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="59"/>
-      <c r="B30" s="186"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="113"/>
-      <c r="F30" s="82"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="113"/>
-      <c r="I30" s="82"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="113"/>
-      <c r="L30" s="82"/>
-      <c r="M30" s="79"/>
-      <c r="N30" s="113"/>
-      <c r="O30" s="82"/>
-      <c r="P30" s="79"/>
-      <c r="Q30" s="113"/>
-      <c r="R30" s="82"/>
-      <c r="S30" s="114"/>
-      <c r="T30" s="113"/>
-      <c r="U30" s="85"/>
-      <c r="V30" s="79"/>
-      <c r="W30" s="113"/>
-      <c r="X30" s="120" t="s">
+      <c r="B30" s="113"/>
+      <c r="C30" s="146"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="162"/>
+      <c r="F30" s="143"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="162"/>
+      <c r="I30" s="143"/>
+      <c r="J30" s="163"/>
+      <c r="K30" s="162"/>
+      <c r="L30" s="143"/>
+      <c r="M30" s="139"/>
+      <c r="N30" s="162"/>
+      <c r="O30" s="143"/>
+      <c r="P30" s="139"/>
+      <c r="Q30" s="162"/>
+      <c r="R30" s="143"/>
+      <c r="S30" s="163"/>
+      <c r="T30" s="162"/>
+      <c r="U30" s="141"/>
+      <c r="V30" s="139"/>
+      <c r="W30" s="162"/>
+      <c r="X30" s="78" t="s">
         <v>26</v>
       </c>
       <c r="Y30" s="65"/>
@@ -4012,31 +3974,31 @@
     </row>
     <row r="31" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="59"/>
-      <c r="B31" s="186"/>
-      <c r="C31" s="78"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="113"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="113"/>
-      <c r="I31" s="118"/>
-      <c r="J31" s="114"/>
-      <c r="K31" s="113"/>
-      <c r="L31" s="118"/>
-      <c r="M31" s="79"/>
-      <c r="N31" s="113"/>
-      <c r="O31" s="81"/>
-      <c r="P31" s="79"/>
-      <c r="Q31" s="113"/>
-      <c r="R31" s="81"/>
-      <c r="S31" s="114"/>
-      <c r="T31" s="113"/>
-      <c r="U31" s="118"/>
-      <c r="V31" s="79"/>
-      <c r="W31" s="113"/>
-      <c r="X31" s="195">
+      <c r="B31" s="113"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="162"/>
+      <c r="F31" s="141"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="162"/>
+      <c r="I31" s="143"/>
+      <c r="J31" s="163"/>
+      <c r="K31" s="162"/>
+      <c r="L31" s="143"/>
+      <c r="M31" s="139"/>
+      <c r="N31" s="162"/>
+      <c r="O31" s="141"/>
+      <c r="P31" s="139"/>
+      <c r="Q31" s="162"/>
+      <c r="R31" s="141"/>
+      <c r="S31" s="163"/>
+      <c r="T31" s="162"/>
+      <c r="U31" s="143"/>
+      <c r="V31" s="139"/>
+      <c r="W31" s="162"/>
+      <c r="X31" s="124">
         <f ca="1">TODAY()</f>
-        <v>46124</v>
+        <v>46131</v>
       </c>
       <c r="Y31" s="65"/>
       <c r="Z31" s="65"/>
@@ -4047,29 +4009,29 @@
     </row>
     <row r="32" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="59"/>
-      <c r="B32" s="186"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="79"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="121"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="81"/>
-      <c r="M32" s="79"/>
-      <c r="N32" s="80"/>
-      <c r="O32" s="81"/>
-      <c r="P32" s="79"/>
-      <c r="Q32" s="122"/>
-      <c r="R32" s="81"/>
-      <c r="S32" s="114"/>
-      <c r="T32" s="113"/>
-      <c r="U32" s="85"/>
-      <c r="V32" s="79"/>
-      <c r="W32" s="113"/>
-      <c r="X32" s="195"/>
+      <c r="B32" s="113"/>
+      <c r="C32" s="138"/>
+      <c r="D32" s="139"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="141"/>
+      <c r="G32" s="139"/>
+      <c r="H32" s="140"/>
+      <c r="I32" s="141"/>
+      <c r="J32" s="164"/>
+      <c r="K32" s="140"/>
+      <c r="L32" s="141"/>
+      <c r="M32" s="139"/>
+      <c r="N32" s="140"/>
+      <c r="O32" s="141"/>
+      <c r="P32" s="139"/>
+      <c r="Q32" s="140"/>
+      <c r="R32" s="141"/>
+      <c r="S32" s="163"/>
+      <c r="T32" s="162"/>
+      <c r="U32" s="141"/>
+      <c r="V32" s="139"/>
+      <c r="W32" s="162"/>
+      <c r="X32" s="124"/>
       <c r="Y32" s="65"/>
       <c r="Z32" s="65"/>
       <c r="AA32" s="65"/>
@@ -4079,29 +4041,29 @@
     </row>
     <row r="33" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="59"/>
-      <c r="B33" s="186"/>
-      <c r="C33" s="123"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="113"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="79"/>
-      <c r="H33" s="113"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="113"/>
-      <c r="L33" s="81"/>
-      <c r="M33" s="79"/>
-      <c r="N33" s="113"/>
-      <c r="O33" s="81"/>
-      <c r="P33" s="79"/>
-      <c r="Q33" s="124"/>
-      <c r="R33" s="85"/>
-      <c r="S33" s="79"/>
-      <c r="T33" s="124"/>
-      <c r="U33" s="85"/>
-      <c r="V33" s="79"/>
-      <c r="W33" s="80"/>
-      <c r="X33" s="195"/>
+      <c r="B33" s="113"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="139"/>
+      <c r="E33" s="162"/>
+      <c r="F33" s="141"/>
+      <c r="G33" s="139"/>
+      <c r="H33" s="162"/>
+      <c r="I33" s="141"/>
+      <c r="J33" s="139"/>
+      <c r="K33" s="162"/>
+      <c r="L33" s="141"/>
+      <c r="M33" s="139"/>
+      <c r="N33" s="162"/>
+      <c r="O33" s="141"/>
+      <c r="P33" s="139"/>
+      <c r="Q33" s="162"/>
+      <c r="R33" s="141"/>
+      <c r="S33" s="139"/>
+      <c r="T33" s="162"/>
+      <c r="U33" s="141"/>
+      <c r="V33" s="139"/>
+      <c r="W33" s="140"/>
+      <c r="X33" s="124"/>
       <c r="Y33" s="65"/>
       <c r="Z33" s="65"/>
       <c r="AA33" s="65"/>
@@ -4111,29 +4073,29 @@
     </row>
     <row r="34" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="59"/>
-      <c r="B34" s="186"/>
-      <c r="C34" s="123"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="113"/>
-      <c r="F34" s="85"/>
-      <c r="G34" s="79"/>
-      <c r="H34" s="113"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="79"/>
-      <c r="K34" s="113"/>
-      <c r="L34" s="85"/>
-      <c r="M34" s="79"/>
-      <c r="N34" s="113"/>
-      <c r="O34" s="81"/>
-      <c r="P34" s="79"/>
-      <c r="Q34" s="124"/>
-      <c r="R34" s="81"/>
-      <c r="S34" s="79"/>
-      <c r="T34" s="124"/>
-      <c r="U34" s="85"/>
-      <c r="V34" s="79"/>
-      <c r="W34" s="80"/>
-      <c r="X34" s="195"/>
+      <c r="B34" s="113"/>
+      <c r="C34" s="138"/>
+      <c r="D34" s="139"/>
+      <c r="E34" s="162"/>
+      <c r="F34" s="141"/>
+      <c r="G34" s="139"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="141"/>
+      <c r="J34" s="139"/>
+      <c r="K34" s="162"/>
+      <c r="L34" s="141"/>
+      <c r="M34" s="139"/>
+      <c r="N34" s="162"/>
+      <c r="O34" s="141"/>
+      <c r="P34" s="139"/>
+      <c r="Q34" s="162"/>
+      <c r="R34" s="141"/>
+      <c r="S34" s="139"/>
+      <c r="T34" s="162"/>
+      <c r="U34" s="141"/>
+      <c r="V34" s="139"/>
+      <c r="W34" s="140"/>
+      <c r="X34" s="124"/>
       <c r="Y34" s="65"/>
       <c r="Z34" s="65"/>
       <c r="AA34" s="65"/>
@@ -4142,62 +4104,62 @@
       <c r="AD34" s="66"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="125"/>
-      <c r="B35" s="186"/>
-      <c r="C35" s="123"/>
-      <c r="D35" s="126"/>
-      <c r="E35" s="113"/>
-      <c r="F35" s="127"/>
-      <c r="G35" s="126"/>
-      <c r="H35" s="113"/>
-      <c r="I35" s="85"/>
-      <c r="J35" s="126"/>
-      <c r="K35" s="113"/>
-      <c r="L35" s="127"/>
-      <c r="M35" s="126"/>
-      <c r="N35" s="113"/>
-      <c r="O35" s="85"/>
-      <c r="P35" s="126"/>
-      <c r="Q35" s="124"/>
-      <c r="R35" s="85"/>
-      <c r="S35" s="126"/>
-      <c r="T35" s="124"/>
-      <c r="U35" s="85"/>
-      <c r="V35" s="126"/>
-      <c r="W35" s="113"/>
-      <c r="X35" s="195"/>
-      <c r="Y35" s="128"/>
-      <c r="Z35" s="129"/>
-      <c r="AA35" s="129"/>
-      <c r="AB35" s="129"/>
-      <c r="AC35" s="129"/>
-      <c r="AD35" s="129"/>
+      <c r="A35" s="79"/>
+      <c r="B35" s="113"/>
+      <c r="C35" s="138"/>
+      <c r="D35" s="165"/>
+      <c r="E35" s="162"/>
+      <c r="F35" s="166"/>
+      <c r="G35" s="165"/>
+      <c r="H35" s="162"/>
+      <c r="I35" s="141"/>
+      <c r="J35" s="165"/>
+      <c r="K35" s="162"/>
+      <c r="L35" s="166"/>
+      <c r="M35" s="165"/>
+      <c r="N35" s="162"/>
+      <c r="O35" s="141"/>
+      <c r="P35" s="165"/>
+      <c r="Q35" s="162"/>
+      <c r="R35" s="141"/>
+      <c r="S35" s="165"/>
+      <c r="T35" s="162"/>
+      <c r="U35" s="141"/>
+      <c r="V35" s="165"/>
+      <c r="W35" s="162"/>
+      <c r="X35" s="124"/>
+      <c r="Y35" s="80"/>
+      <c r="Z35" s="81"/>
+      <c r="AA35" s="81"/>
+      <c r="AB35" s="81"/>
+      <c r="AC35" s="81"/>
+      <c r="AD35" s="81"/>
     </row>
     <row r="36" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="90"/>
-      <c r="C36" s="130"/>
-      <c r="D36" s="92"/>
-      <c r="E36" s="131"/>
-      <c r="F36" s="99"/>
-      <c r="G36" s="92"/>
-      <c r="H36" s="131"/>
-      <c r="I36" s="95"/>
-      <c r="J36" s="92"/>
-      <c r="K36" s="131"/>
-      <c r="L36" s="99"/>
-      <c r="M36" s="92"/>
-      <c r="N36" s="131"/>
-      <c r="O36" s="95"/>
-      <c r="P36" s="92"/>
-      <c r="Q36" s="132"/>
-      <c r="R36" s="99"/>
-      <c r="S36" s="92"/>
-      <c r="T36" s="132"/>
-      <c r="U36" s="99"/>
-      <c r="V36" s="92"/>
-      <c r="W36" s="131"/>
-      <c r="X36" s="195"/>
+      <c r="B36" s="71"/>
+      <c r="C36" s="167"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="168"/>
+      <c r="F36" s="151"/>
+      <c r="G36" s="148"/>
+      <c r="H36" s="168"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="148"/>
+      <c r="K36" s="168"/>
+      <c r="L36" s="151"/>
+      <c r="M36" s="148"/>
+      <c r="N36" s="168"/>
+      <c r="O36" s="151"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="168"/>
+      <c r="R36" s="151"/>
+      <c r="S36" s="148"/>
+      <c r="T36" s="168"/>
+      <c r="U36" s="151"/>
+      <c r="V36" s="148"/>
+      <c r="W36" s="168"/>
+      <c r="X36" s="124"/>
       <c r="Y36" s="8"/>
       <c r="Z36" s="2"/>
       <c r="AA36" s="2"/>
@@ -4207,31 +4169,31 @@
     </row>
     <row r="37" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="133" t="s">
+      <c r="B37" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="134"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="106"/>
-      <c r="F37" s="135"/>
-      <c r="G37" s="105"/>
-      <c r="H37" s="106"/>
-      <c r="I37" s="135"/>
-      <c r="J37" s="105"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="135"/>
-      <c r="M37" s="105"/>
-      <c r="N37" s="106"/>
-      <c r="O37" s="135"/>
-      <c r="P37" s="105"/>
-      <c r="Q37" s="106"/>
-      <c r="R37" s="136"/>
-      <c r="S37" s="137"/>
-      <c r="T37" s="138"/>
-      <c r="U37" s="136"/>
-      <c r="V37" s="105"/>
-      <c r="W37" s="106"/>
-      <c r="X37" s="195"/>
+      <c r="C37" s="169"/>
+      <c r="D37" s="157"/>
+      <c r="E37" s="158"/>
+      <c r="F37" s="170"/>
+      <c r="G37" s="157"/>
+      <c r="H37" s="158"/>
+      <c r="I37" s="170"/>
+      <c r="J37" s="157"/>
+      <c r="K37" s="158"/>
+      <c r="L37" s="170"/>
+      <c r="M37" s="157"/>
+      <c r="N37" s="158"/>
+      <c r="O37" s="170"/>
+      <c r="P37" s="157"/>
+      <c r="Q37" s="158"/>
+      <c r="R37" s="170"/>
+      <c r="S37" s="157"/>
+      <c r="T37" s="158"/>
+      <c r="U37" s="170"/>
+      <c r="V37" s="157"/>
+      <c r="W37" s="158"/>
+      <c r="X37" s="124"/>
       <c r="Y37" s="8"/>
       <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
@@ -4241,31 +4203,31 @@
     </row>
     <row r="38" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
-      <c r="B38" s="139" t="s">
+      <c r="B38" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="140"/>
-      <c r="D38" s="141"/>
-      <c r="E38" s="142"/>
-      <c r="F38" s="143"/>
-      <c r="G38" s="141"/>
-      <c r="H38" s="142"/>
-      <c r="I38" s="144"/>
-      <c r="J38" s="141"/>
-      <c r="K38" s="142"/>
-      <c r="L38" s="144"/>
-      <c r="M38" s="141"/>
-      <c r="N38" s="142"/>
-      <c r="O38" s="143"/>
-      <c r="P38" s="141"/>
-      <c r="Q38" s="142"/>
-      <c r="R38" s="143"/>
-      <c r="S38" s="145"/>
-      <c r="T38" s="146"/>
-      <c r="U38" s="143"/>
-      <c r="V38" s="141"/>
-      <c r="W38" s="142"/>
-      <c r="X38" s="195"/>
+      <c r="C38" s="171"/>
+      <c r="D38" s="172"/>
+      <c r="E38" s="173"/>
+      <c r="F38" s="174"/>
+      <c r="G38" s="172"/>
+      <c r="H38" s="173"/>
+      <c r="I38" s="174"/>
+      <c r="J38" s="172"/>
+      <c r="K38" s="173"/>
+      <c r="L38" s="174"/>
+      <c r="M38" s="172"/>
+      <c r="N38" s="173"/>
+      <c r="O38" s="174"/>
+      <c r="P38" s="172"/>
+      <c r="Q38" s="173"/>
+      <c r="R38" s="174"/>
+      <c r="S38" s="172"/>
+      <c r="T38" s="173"/>
+      <c r="U38" s="174"/>
+      <c r="V38" s="172"/>
+      <c r="W38" s="173"/>
+      <c r="X38" s="124"/>
       <c r="Y38" s="8"/>
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
@@ -4275,29 +4237,29 @@
     </row>
     <row r="39" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
-      <c r="B39" s="147"/>
-      <c r="C39" s="174"/>
-      <c r="D39" s="175"/>
-      <c r="E39" s="176"/>
-      <c r="F39" s="177"/>
-      <c r="G39" s="175"/>
-      <c r="H39" s="176"/>
-      <c r="I39" s="177"/>
-      <c r="J39" s="175"/>
-      <c r="K39" s="176"/>
-      <c r="L39" s="177"/>
-      <c r="M39" s="175"/>
-      <c r="N39" s="176"/>
-      <c r="O39" s="177"/>
-      <c r="P39" s="175"/>
-      <c r="Q39" s="176"/>
-      <c r="R39" s="177"/>
-      <c r="S39" s="175"/>
-      <c r="T39" s="176"/>
-      <c r="U39" s="179"/>
-      <c r="V39" s="180"/>
-      <c r="W39" s="181"/>
-      <c r="X39" s="195"/>
+      <c r="B39" s="84"/>
+      <c r="C39" s="118"/>
+      <c r="D39" s="116"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="115"/>
+      <c r="G39" s="116"/>
+      <c r="H39" s="117"/>
+      <c r="I39" s="115"/>
+      <c r="J39" s="116"/>
+      <c r="K39" s="117"/>
+      <c r="L39" s="115"/>
+      <c r="M39" s="116"/>
+      <c r="N39" s="117"/>
+      <c r="O39" s="115"/>
+      <c r="P39" s="116"/>
+      <c r="Q39" s="117"/>
+      <c r="R39" s="115"/>
+      <c r="S39" s="116"/>
+      <c r="T39" s="117"/>
+      <c r="U39" s="109"/>
+      <c r="V39" s="110"/>
+      <c r="W39" s="111"/>
+      <c r="X39" s="124"/>
       <c r="Y39" s="8"/>
       <c r="Z39" s="2"/>
       <c r="AA39" s="2"/>
@@ -4308,7 +4270,7 @@
     <row r="40" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="9"/>
-      <c r="C40" s="148" t="s">
+      <c r="C40" s="85" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="15" t="s">
@@ -4371,7 +4333,7 @@
       <c r="W40" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="X40" s="195"/>
+      <c r="X40" s="124"/>
       <c r="Y40" s="8"/>
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
@@ -4403,7 +4365,7 @@
       <c r="U41" s="23"/>
       <c r="V41" s="24"/>
       <c r="W41" s="25"/>
-      <c r="X41" s="195"/>
+      <c r="X41" s="124"/>
       <c r="Y41" s="8"/>
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
@@ -4435,7 +4397,7 @@
       <c r="U42" s="32"/>
       <c r="V42" s="33"/>
       <c r="W42" s="34"/>
-      <c r="X42" s="195"/>
+      <c r="X42" s="124"/>
       <c r="Y42" s="8"/>
       <c r="Z42" s="2"/>
       <c r="AA42" s="2"/>
@@ -4467,7 +4429,7 @@
       <c r="U43" s="32"/>
       <c r="V43" s="33"/>
       <c r="W43" s="34"/>
-      <c r="X43" s="119"/>
+      <c r="X43" s="77"/>
       <c r="Y43" s="8"/>
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
@@ -4499,7 +4461,7 @@
       <c r="U44" s="32"/>
       <c r="V44" s="33"/>
       <c r="W44" s="34"/>
-      <c r="X44" s="119"/>
+      <c r="X44" s="77"/>
       <c r="Y44" s="8"/>
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
@@ -4531,7 +4493,7 @@
       <c r="U45" s="32"/>
       <c r="V45" s="33"/>
       <c r="W45" s="34"/>
-      <c r="X45" s="149"/>
+      <c r="X45" s="86"/>
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
@@ -4563,7 +4525,7 @@
       <c r="U46" s="32"/>
       <c r="V46" s="33"/>
       <c r="W46" s="34"/>
-      <c r="X46" s="150"/>
+      <c r="X46" s="87"/>
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
@@ -4595,7 +4557,7 @@
       <c r="U47" s="32"/>
       <c r="V47" s="33"/>
       <c r="W47" s="34"/>
-      <c r="X47" s="150"/>
+      <c r="X47" s="87"/>
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
       <c r="AA47" s="2"/>
@@ -4627,7 +4589,7 @@
       <c r="U48" s="32"/>
       <c r="V48" s="33"/>
       <c r="W48" s="34"/>
-      <c r="X48" s="150"/>
+      <c r="X48" s="87"/>
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
@@ -4659,7 +4621,7 @@
       <c r="U49" s="32"/>
       <c r="V49" s="33"/>
       <c r="W49" s="34"/>
-      <c r="X49" s="150"/>
+      <c r="X49" s="87"/>
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
       <c r="AA49" s="2"/>
@@ -4691,7 +4653,7 @@
       <c r="U50" s="32"/>
       <c r="V50" s="33"/>
       <c r="W50" s="34"/>
-      <c r="X50" s="150"/>
+      <c r="X50" s="87"/>
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
       <c r="AA50" s="2"/>
@@ -4723,7 +4685,7 @@
       <c r="U51" s="32"/>
       <c r="V51" s="33"/>
       <c r="W51" s="34"/>
-      <c r="X51" s="150"/>
+      <c r="X51" s="87"/>
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
       <c r="AA51" s="2"/>
@@ -4736,7 +4698,7 @@
       <c r="B52" s="26"/>
       <c r="C52" s="37"/>
       <c r="D52" s="38"/>
-      <c r="E52" s="151"/>
+      <c r="E52" s="88"/>
       <c r="F52" s="40"/>
       <c r="G52" s="38"/>
       <c r="H52" s="41"/>
@@ -4755,7 +4717,7 @@
       <c r="U52" s="43"/>
       <c r="V52" s="44"/>
       <c r="W52" s="45"/>
-      <c r="X52" s="150"/>
+      <c r="X52" s="87"/>
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
       <c r="AA52" s="2"/>
@@ -4861,7 +4823,7 @@
       <c r="W54" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="X54" s="119"/>
+      <c r="X54" s="77"/>
       <c r="Y54" s="65"/>
       <c r="Z54" s="65"/>
       <c r="AA54" s="65"/>
@@ -4871,35 +4833,35 @@
     </row>
     <row r="55" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="59"/>
-      <c r="B55" s="185" t="s">
+      <c r="B55" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="C55" s="67"/>
-      <c r="D55" s="68"/>
-      <c r="E55" s="69"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="190"/>
-      <c r="H55" s="69"/>
-      <c r="I55" s="70"/>
-      <c r="J55" s="71"/>
-      <c r="K55" s="69"/>
-      <c r="L55" s="70"/>
-      <c r="M55" s="68"/>
-      <c r="N55" s="69"/>
-      <c r="O55" s="70"/>
-      <c r="P55" s="72"/>
-      <c r="Q55" s="69"/>
-      <c r="R55" s="70"/>
-      <c r="S55" s="68"/>
-      <c r="T55" s="69"/>
-      <c r="U55" s="70"/>
-      <c r="V55" s="68"/>
-      <c r="W55" s="69"/>
-      <c r="X55" s="119"/>
-      <c r="Y55" s="75" t="s">
+      <c r="C55" s="131"/>
+      <c r="D55" s="132"/>
+      <c r="E55" s="133"/>
+      <c r="F55" s="134"/>
+      <c r="G55" s="135"/>
+      <c r="H55" s="133"/>
+      <c r="I55" s="134"/>
+      <c r="J55" s="136"/>
+      <c r="K55" s="133"/>
+      <c r="L55" s="134"/>
+      <c r="M55" s="132"/>
+      <c r="N55" s="133"/>
+      <c r="O55" s="134"/>
+      <c r="P55" s="137"/>
+      <c r="Q55" s="133"/>
+      <c r="R55" s="134"/>
+      <c r="S55" s="132"/>
+      <c r="T55" s="133"/>
+      <c r="U55" s="134"/>
+      <c r="V55" s="132"/>
+      <c r="W55" s="133"/>
+      <c r="X55" s="77"/>
+      <c r="Y55" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="Z55" s="76">
+      <c r="Z55" s="68">
         <f>COUNTIF(C55:W74,Y55)</f>
         <v>0</v>
       </c>
@@ -4910,33 +4872,33 @@
     </row>
     <row r="56" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="59"/>
-      <c r="B56" s="186"/>
-      <c r="C56" s="78"/>
-      <c r="D56" s="79"/>
-      <c r="E56" s="80"/>
-      <c r="F56" s="81"/>
-      <c r="G56" s="191"/>
-      <c r="H56" s="80"/>
-      <c r="I56" s="81"/>
-      <c r="J56" s="79"/>
-      <c r="K56" s="80"/>
-      <c r="L56" s="82"/>
-      <c r="M56" s="79"/>
-      <c r="N56" s="83"/>
-      <c r="O56" s="81"/>
-      <c r="P56" s="84"/>
-      <c r="Q56" s="80"/>
-      <c r="R56" s="82"/>
-      <c r="S56" s="79"/>
-      <c r="T56" s="80"/>
-      <c r="U56" s="81"/>
-      <c r="V56" s="79"/>
-      <c r="W56" s="83"/>
-      <c r="X56" s="119"/>
-      <c r="Y56" s="87" t="s">
+      <c r="B56" s="113"/>
+      <c r="C56" s="138"/>
+      <c r="D56" s="139"/>
+      <c r="E56" s="140"/>
+      <c r="F56" s="141"/>
+      <c r="G56" s="142"/>
+      <c r="H56" s="140"/>
+      <c r="I56" s="141"/>
+      <c r="J56" s="139"/>
+      <c r="K56" s="140"/>
+      <c r="L56" s="143"/>
+      <c r="M56" s="139"/>
+      <c r="N56" s="144"/>
+      <c r="O56" s="141"/>
+      <c r="P56" s="145"/>
+      <c r="Q56" s="140"/>
+      <c r="R56" s="143"/>
+      <c r="S56" s="139"/>
+      <c r="T56" s="140"/>
+      <c r="U56" s="141"/>
+      <c r="V56" s="139"/>
+      <c r="W56" s="144"/>
+      <c r="X56" s="77"/>
+      <c r="Y56" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="Z56" s="88">
+      <c r="Z56" s="70">
         <f>COUNTIF(C55:W74,Y56)</f>
         <v>0</v>
       </c>
@@ -4947,33 +4909,33 @@
     </row>
     <row r="57" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="59"/>
-      <c r="B57" s="186"/>
-      <c r="C57" s="78"/>
-      <c r="D57" s="79"/>
-      <c r="E57" s="80"/>
-      <c r="F57" s="81"/>
-      <c r="G57" s="191"/>
-      <c r="H57" s="80"/>
-      <c r="I57" s="81"/>
-      <c r="J57" s="79"/>
-      <c r="K57" s="80"/>
-      <c r="L57" s="82"/>
-      <c r="M57" s="79"/>
-      <c r="N57" s="83"/>
-      <c r="O57" s="81"/>
-      <c r="P57" s="84"/>
-      <c r="Q57" s="83"/>
-      <c r="R57" s="81"/>
-      <c r="S57" s="79"/>
-      <c r="T57" s="83"/>
-      <c r="U57" s="81"/>
-      <c r="V57" s="79"/>
-      <c r="W57" s="83"/>
-      <c r="X57" s="119"/>
-      <c r="Y57" s="87" t="s">
+      <c r="B57" s="113"/>
+      <c r="C57" s="138"/>
+      <c r="D57" s="139"/>
+      <c r="E57" s="140"/>
+      <c r="F57" s="141"/>
+      <c r="G57" s="142"/>
+      <c r="H57" s="140"/>
+      <c r="I57" s="141"/>
+      <c r="J57" s="139"/>
+      <c r="K57" s="140"/>
+      <c r="L57" s="143"/>
+      <c r="M57" s="139"/>
+      <c r="N57" s="144"/>
+      <c r="O57" s="141"/>
+      <c r="P57" s="145"/>
+      <c r="Q57" s="144"/>
+      <c r="R57" s="141"/>
+      <c r="S57" s="139"/>
+      <c r="T57" s="144"/>
+      <c r="U57" s="141"/>
+      <c r="V57" s="139"/>
+      <c r="W57" s="144"/>
+      <c r="X57" s="77"/>
+      <c r="Y57" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="Z57" s="88">
+      <c r="Z57" s="70">
         <f>COUNTIF(C55:W74,Y57)</f>
         <v>0</v>
       </c>
@@ -4984,33 +4946,33 @@
     </row>
     <row r="58" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="59"/>
-      <c r="B58" s="186"/>
-      <c r="C58" s="89"/>
-      <c r="D58" s="79"/>
-      <c r="E58" s="83"/>
-      <c r="F58" s="82"/>
-      <c r="G58" s="79"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="82"/>
-      <c r="J58" s="79"/>
-      <c r="K58" s="83"/>
-      <c r="L58" s="82"/>
-      <c r="M58" s="79"/>
-      <c r="N58" s="83"/>
-      <c r="O58" s="82"/>
-      <c r="P58" s="84"/>
-      <c r="Q58" s="83"/>
-      <c r="R58" s="82"/>
-      <c r="S58" s="79"/>
-      <c r="T58" s="83"/>
-      <c r="U58" s="81"/>
-      <c r="V58" s="79"/>
-      <c r="W58" s="83"/>
-      <c r="X58" s="119"/>
-      <c r="Y58" s="87" t="s">
+      <c r="B58" s="113"/>
+      <c r="C58" s="146"/>
+      <c r="D58" s="139"/>
+      <c r="E58" s="144"/>
+      <c r="F58" s="143"/>
+      <c r="G58" s="139"/>
+      <c r="H58" s="144"/>
+      <c r="I58" s="143"/>
+      <c r="J58" s="139"/>
+      <c r="K58" s="144"/>
+      <c r="L58" s="143"/>
+      <c r="M58" s="139"/>
+      <c r="N58" s="144"/>
+      <c r="O58" s="143"/>
+      <c r="P58" s="145"/>
+      <c r="Q58" s="144"/>
+      <c r="R58" s="143"/>
+      <c r="S58" s="139"/>
+      <c r="T58" s="144"/>
+      <c r="U58" s="141"/>
+      <c r="V58" s="139"/>
+      <c r="W58" s="144"/>
+      <c r="X58" s="77"/>
+      <c r="Y58" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="Z58" s="88">
+      <c r="Z58" s="70">
         <f>COUNTIF(C55:W74,Y58)</f>
         <v>0</v>
       </c>
@@ -5021,33 +4983,33 @@
     </row>
     <row r="59" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="59"/>
-      <c r="B59" s="189"/>
-      <c r="C59" s="91"/>
-      <c r="D59" s="92"/>
-      <c r="E59" s="93"/>
-      <c r="F59" s="94"/>
-      <c r="G59" s="92"/>
-      <c r="H59" s="93"/>
-      <c r="I59" s="95"/>
-      <c r="J59" s="92"/>
-      <c r="K59" s="93"/>
-      <c r="L59" s="96"/>
-      <c r="M59" s="92"/>
-      <c r="N59" s="93"/>
-      <c r="O59" s="94"/>
-      <c r="P59" s="97"/>
-      <c r="Q59" s="93"/>
-      <c r="R59" s="95"/>
-      <c r="S59" s="92"/>
-      <c r="T59" s="93"/>
-      <c r="U59" s="95"/>
-      <c r="V59" s="92"/>
-      <c r="W59" s="93"/>
-      <c r="X59" s="119"/>
-      <c r="Y59" s="87" t="s">
+      <c r="B59" s="114"/>
+      <c r="C59" s="147"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="151"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="149"/>
+      <c r="L59" s="152"/>
+      <c r="M59" s="148"/>
+      <c r="N59" s="149"/>
+      <c r="O59" s="150"/>
+      <c r="P59" s="153"/>
+      <c r="Q59" s="149"/>
+      <c r="R59" s="151"/>
+      <c r="S59" s="148"/>
+      <c r="T59" s="149"/>
+      <c r="U59" s="151"/>
+      <c r="V59" s="148"/>
+      <c r="W59" s="149"/>
+      <c r="X59" s="77"/>
+      <c r="Y59" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="Z59" s="88">
+      <c r="Z59" s="70">
         <f>COUNTIF(C55:W74,Y59)</f>
         <v>0</v>
       </c>
@@ -5058,35 +5020,35 @@
     </row>
     <row r="60" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="59"/>
-      <c r="B60" s="101" t="s">
+      <c r="B60" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="C60" s="102"/>
-      <c r="D60" s="103"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="102"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="102"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="104"/>
-      <c r="L60" s="102"/>
-      <c r="M60" s="103"/>
-      <c r="N60" s="104"/>
-      <c r="O60" s="102"/>
-      <c r="P60" s="103"/>
-      <c r="Q60" s="104"/>
-      <c r="R60" s="102"/>
-      <c r="S60" s="105"/>
-      <c r="T60" s="106"/>
-      <c r="U60" s="102"/>
-      <c r="V60" s="105"/>
-      <c r="W60" s="106"/>
-      <c r="X60" s="119"/>
-      <c r="Y60" s="87" t="s">
+      <c r="C60" s="154"/>
+      <c r="D60" s="155"/>
+      <c r="E60" s="156"/>
+      <c r="F60" s="154"/>
+      <c r="G60" s="155"/>
+      <c r="H60" s="156"/>
+      <c r="I60" s="154"/>
+      <c r="J60" s="155"/>
+      <c r="K60" s="156"/>
+      <c r="L60" s="154"/>
+      <c r="M60" s="155"/>
+      <c r="N60" s="156"/>
+      <c r="O60" s="154"/>
+      <c r="P60" s="155"/>
+      <c r="Q60" s="156"/>
+      <c r="R60" s="154"/>
+      <c r="S60" s="157"/>
+      <c r="T60" s="158"/>
+      <c r="U60" s="154"/>
+      <c r="V60" s="157"/>
+      <c r="W60" s="158"/>
+      <c r="X60" s="77"/>
+      <c r="Y60" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="Z60" s="88">
+      <c r="Z60" s="70">
         <f>COUNTIF(C55:W74,Y60)</f>
         <v>0</v>
       </c>
@@ -5097,35 +5059,35 @@
     </row>
     <row r="61" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="59"/>
-      <c r="B61" s="185" t="s">
+      <c r="B61" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="C61" s="67"/>
-      <c r="D61" s="108"/>
-      <c r="E61" s="109"/>
-      <c r="F61" s="110"/>
-      <c r="G61" s="68"/>
-      <c r="H61" s="109"/>
-      <c r="I61" s="110"/>
-      <c r="J61" s="68"/>
-      <c r="K61" s="109"/>
-      <c r="L61" s="110"/>
-      <c r="M61" s="68"/>
-      <c r="N61" s="109"/>
-      <c r="O61" s="110"/>
-      <c r="P61" s="68"/>
-      <c r="Q61" s="109"/>
-      <c r="R61" s="110"/>
-      <c r="S61" s="68"/>
-      <c r="T61" s="109"/>
-      <c r="U61" s="110"/>
-      <c r="V61" s="68"/>
-      <c r="W61" s="152"/>
-      <c r="X61" s="119"/>
-      <c r="Y61" s="87" t="s">
+      <c r="C61" s="131"/>
+      <c r="D61" s="159"/>
+      <c r="E61" s="160"/>
+      <c r="F61" s="161"/>
+      <c r="G61" s="132"/>
+      <c r="H61" s="160"/>
+      <c r="I61" s="161"/>
+      <c r="J61" s="132"/>
+      <c r="K61" s="160"/>
+      <c r="L61" s="161"/>
+      <c r="M61" s="132"/>
+      <c r="N61" s="160"/>
+      <c r="O61" s="161"/>
+      <c r="P61" s="132"/>
+      <c r="Q61" s="160"/>
+      <c r="R61" s="161"/>
+      <c r="S61" s="132"/>
+      <c r="T61" s="160"/>
+      <c r="U61" s="161"/>
+      <c r="V61" s="132"/>
+      <c r="W61" s="175"/>
+      <c r="X61" s="77"/>
+      <c r="Y61" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="Z61" s="88">
+      <c r="Z61" s="70">
         <f>COUNTIF(C55:W74,Y61)</f>
         <v>0</v>
       </c>
@@ -5136,33 +5098,33 @@
     </row>
     <row r="62" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="59"/>
-      <c r="B62" s="186"/>
-      <c r="C62" s="78"/>
-      <c r="D62" s="79"/>
-      <c r="E62" s="113"/>
-      <c r="F62" s="81"/>
-      <c r="G62" s="79"/>
-      <c r="H62" s="113"/>
-      <c r="I62" s="81"/>
-      <c r="J62" s="114"/>
-      <c r="K62" s="113"/>
-      <c r="L62" s="81"/>
-      <c r="M62" s="79"/>
-      <c r="N62" s="113"/>
-      <c r="O62" s="81"/>
-      <c r="P62" s="79"/>
-      <c r="Q62" s="113"/>
-      <c r="R62" s="81"/>
-      <c r="S62" s="114"/>
-      <c r="T62" s="113"/>
-      <c r="U62" s="81"/>
-      <c r="V62" s="79"/>
-      <c r="W62" s="113"/>
-      <c r="X62" s="119"/>
-      <c r="Y62" s="87" t="s">
+      <c r="B62" s="113"/>
+      <c r="C62" s="138"/>
+      <c r="D62" s="139"/>
+      <c r="E62" s="162"/>
+      <c r="F62" s="141"/>
+      <c r="G62" s="139"/>
+      <c r="H62" s="162"/>
+      <c r="I62" s="141"/>
+      <c r="J62" s="163"/>
+      <c r="K62" s="162"/>
+      <c r="L62" s="141"/>
+      <c r="M62" s="139"/>
+      <c r="N62" s="162"/>
+      <c r="O62" s="141"/>
+      <c r="P62" s="139"/>
+      <c r="Q62" s="162"/>
+      <c r="R62" s="141"/>
+      <c r="S62" s="163"/>
+      <c r="T62" s="162"/>
+      <c r="U62" s="141"/>
+      <c r="V62" s="139"/>
+      <c r="W62" s="162"/>
+      <c r="X62" s="77"/>
+      <c r="Y62" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="Z62" s="88">
+      <c r="Z62" s="70">
         <f>COUNTIF(C55:W74,Y62)</f>
         <v>0</v>
       </c>
@@ -5173,33 +5135,33 @@
     </row>
     <row r="63" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="59"/>
-      <c r="B63" s="186"/>
-      <c r="C63" s="78"/>
-      <c r="D63" s="79"/>
-      <c r="E63" s="113"/>
-      <c r="F63" s="81"/>
-      <c r="G63" s="79"/>
-      <c r="H63" s="113"/>
-      <c r="I63" s="81"/>
-      <c r="J63" s="114"/>
-      <c r="K63" s="113"/>
-      <c r="L63" s="81"/>
-      <c r="M63" s="79"/>
-      <c r="N63" s="113"/>
-      <c r="O63" s="81"/>
-      <c r="P63" s="79"/>
-      <c r="Q63" s="113"/>
-      <c r="R63" s="81"/>
-      <c r="S63" s="114"/>
-      <c r="T63" s="113"/>
-      <c r="U63" s="81"/>
-      <c r="V63" s="79"/>
-      <c r="W63" s="113"/>
-      <c r="X63" s="119"/>
-      <c r="Y63" s="87" t="s">
+      <c r="B63" s="113"/>
+      <c r="C63" s="138"/>
+      <c r="D63" s="139"/>
+      <c r="E63" s="162"/>
+      <c r="F63" s="141"/>
+      <c r="G63" s="139"/>
+      <c r="H63" s="162"/>
+      <c r="I63" s="141"/>
+      <c r="J63" s="163"/>
+      <c r="K63" s="162"/>
+      <c r="L63" s="141"/>
+      <c r="M63" s="139"/>
+      <c r="N63" s="162"/>
+      <c r="O63" s="141"/>
+      <c r="P63" s="139"/>
+      <c r="Q63" s="162"/>
+      <c r="R63" s="141"/>
+      <c r="S63" s="163"/>
+      <c r="T63" s="162"/>
+      <c r="U63" s="141"/>
+      <c r="V63" s="139"/>
+      <c r="W63" s="162"/>
+      <c r="X63" s="77"/>
+      <c r="Y63" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="Z63" s="88">
+      <c r="Z63" s="70">
         <f>COUNTIF(C55:W74,Y63)</f>
         <v>0</v>
       </c>
@@ -5210,33 +5172,33 @@
     </row>
     <row r="64" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="59"/>
-      <c r="B64" s="186"/>
-      <c r="C64" s="78"/>
-      <c r="D64" s="79"/>
-      <c r="E64" s="80"/>
-      <c r="F64" s="81"/>
-      <c r="G64" s="114"/>
-      <c r="H64" s="80"/>
-      <c r="I64" s="81"/>
-      <c r="J64" s="79"/>
-      <c r="K64" s="80"/>
-      <c r="L64" s="81"/>
-      <c r="M64" s="79"/>
-      <c r="N64" s="80"/>
-      <c r="O64" s="81"/>
-      <c r="P64" s="79"/>
-      <c r="Q64" s="80"/>
-      <c r="R64" s="81"/>
-      <c r="S64" s="79"/>
-      <c r="T64" s="80"/>
-      <c r="U64" s="81"/>
-      <c r="V64" s="79"/>
-      <c r="W64" s="113"/>
-      <c r="X64" s="119"/>
-      <c r="Y64" s="153" t="s">
+      <c r="B64" s="113"/>
+      <c r="C64" s="138"/>
+      <c r="D64" s="139"/>
+      <c r="E64" s="140"/>
+      <c r="F64" s="141"/>
+      <c r="G64" s="163"/>
+      <c r="H64" s="140"/>
+      <c r="I64" s="141"/>
+      <c r="J64" s="139"/>
+      <c r="K64" s="140"/>
+      <c r="L64" s="141"/>
+      <c r="M64" s="139"/>
+      <c r="N64" s="140"/>
+      <c r="O64" s="141"/>
+      <c r="P64" s="139"/>
+      <c r="Q64" s="140"/>
+      <c r="R64" s="141"/>
+      <c r="S64" s="139"/>
+      <c r="T64" s="140"/>
+      <c r="U64" s="141"/>
+      <c r="V64" s="139"/>
+      <c r="W64" s="162"/>
+      <c r="X64" s="77"/>
+      <c r="Y64" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="Z64" s="117">
+      <c r="Z64" s="76">
         <f>COUNTIF(C55:W74,Y64)</f>
         <v>0</v>
       </c>
@@ -5247,29 +5209,29 @@
     </row>
     <row r="65" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="59"/>
-      <c r="B65" s="186"/>
-      <c r="C65" s="89"/>
-      <c r="D65" s="79"/>
-      <c r="E65" s="113"/>
-      <c r="F65" s="82"/>
-      <c r="G65" s="79"/>
-      <c r="H65" s="113"/>
-      <c r="I65" s="82"/>
-      <c r="J65" s="114"/>
-      <c r="K65" s="113"/>
-      <c r="L65" s="82"/>
-      <c r="M65" s="79"/>
-      <c r="N65" s="113"/>
-      <c r="O65" s="82"/>
-      <c r="P65" s="79"/>
-      <c r="Q65" s="113"/>
-      <c r="R65" s="82"/>
-      <c r="S65" s="114"/>
-      <c r="T65" s="113"/>
-      <c r="U65" s="82"/>
-      <c r="V65" s="79"/>
-      <c r="W65" s="113"/>
-      <c r="X65" s="119"/>
+      <c r="B65" s="113"/>
+      <c r="C65" s="146"/>
+      <c r="D65" s="139"/>
+      <c r="E65" s="162"/>
+      <c r="F65" s="143"/>
+      <c r="G65" s="139"/>
+      <c r="H65" s="162"/>
+      <c r="I65" s="143"/>
+      <c r="J65" s="163"/>
+      <c r="K65" s="162"/>
+      <c r="L65" s="143"/>
+      <c r="M65" s="139"/>
+      <c r="N65" s="162"/>
+      <c r="O65" s="143"/>
+      <c r="P65" s="139"/>
+      <c r="Q65" s="162"/>
+      <c r="R65" s="143"/>
+      <c r="S65" s="163"/>
+      <c r="T65" s="162"/>
+      <c r="U65" s="143"/>
+      <c r="V65" s="139"/>
+      <c r="W65" s="162"/>
+      <c r="X65" s="77"/>
       <c r="Y65" s="65"/>
       <c r="Z65" s="65"/>
       <c r="AA65" s="65"/>
@@ -5279,29 +5241,29 @@
     </row>
     <row r="66" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="59"/>
-      <c r="B66" s="186"/>
-      <c r="C66" s="89"/>
-      <c r="D66" s="79"/>
-      <c r="E66" s="113"/>
-      <c r="F66" s="82"/>
-      <c r="G66" s="79"/>
-      <c r="H66" s="113"/>
-      <c r="I66" s="82"/>
-      <c r="J66" s="114"/>
-      <c r="K66" s="113"/>
-      <c r="L66" s="82"/>
-      <c r="M66" s="79"/>
-      <c r="N66" s="113"/>
-      <c r="O66" s="82"/>
-      <c r="P66" s="79"/>
-      <c r="Q66" s="113"/>
-      <c r="R66" s="82"/>
-      <c r="S66" s="114"/>
-      <c r="T66" s="113"/>
-      <c r="U66" s="81"/>
-      <c r="V66" s="79"/>
-      <c r="W66" s="113"/>
-      <c r="X66" s="119"/>
+      <c r="B66" s="113"/>
+      <c r="C66" s="146"/>
+      <c r="D66" s="139"/>
+      <c r="E66" s="162"/>
+      <c r="F66" s="143"/>
+      <c r="G66" s="139"/>
+      <c r="H66" s="162"/>
+      <c r="I66" s="143"/>
+      <c r="J66" s="163"/>
+      <c r="K66" s="162"/>
+      <c r="L66" s="143"/>
+      <c r="M66" s="139"/>
+      <c r="N66" s="162"/>
+      <c r="O66" s="143"/>
+      <c r="P66" s="139"/>
+      <c r="Q66" s="162"/>
+      <c r="R66" s="143"/>
+      <c r="S66" s="163"/>
+      <c r="T66" s="162"/>
+      <c r="U66" s="141"/>
+      <c r="V66" s="139"/>
+      <c r="W66" s="162"/>
+      <c r="X66" s="77"/>
       <c r="Y66" s="65"/>
       <c r="Z66" s="65"/>
       <c r="AA66" s="65"/>
@@ -5311,29 +5273,29 @@
     </row>
     <row r="67" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="59"/>
-      <c r="B67" s="186"/>
-      <c r="C67" s="78"/>
-      <c r="D67" s="79"/>
-      <c r="E67" s="113"/>
-      <c r="F67" s="81"/>
-      <c r="G67" s="79"/>
-      <c r="H67" s="113"/>
-      <c r="I67" s="82"/>
-      <c r="J67" s="114"/>
-      <c r="K67" s="113"/>
-      <c r="L67" s="82"/>
-      <c r="M67" s="79"/>
-      <c r="N67" s="113"/>
-      <c r="O67" s="81"/>
-      <c r="P67" s="79"/>
-      <c r="Q67" s="113"/>
-      <c r="R67" s="81"/>
-      <c r="S67" s="114"/>
-      <c r="T67" s="113"/>
-      <c r="U67" s="82"/>
-      <c r="V67" s="79"/>
-      <c r="W67" s="113"/>
-      <c r="X67" s="119"/>
+      <c r="B67" s="113"/>
+      <c r="C67" s="138"/>
+      <c r="D67" s="139"/>
+      <c r="E67" s="162"/>
+      <c r="F67" s="141"/>
+      <c r="G67" s="139"/>
+      <c r="H67" s="162"/>
+      <c r="I67" s="143"/>
+      <c r="J67" s="163"/>
+      <c r="K67" s="162"/>
+      <c r="L67" s="143"/>
+      <c r="M67" s="139"/>
+      <c r="N67" s="162"/>
+      <c r="O67" s="141"/>
+      <c r="P67" s="139"/>
+      <c r="Q67" s="162"/>
+      <c r="R67" s="141"/>
+      <c r="S67" s="163"/>
+      <c r="T67" s="162"/>
+      <c r="U67" s="143"/>
+      <c r="V67" s="139"/>
+      <c r="W67" s="162"/>
+      <c r="X67" s="77"/>
       <c r="Y67" s="65"/>
       <c r="Z67" s="65"/>
       <c r="AA67" s="65"/>
@@ -5343,29 +5305,29 @@
     </row>
     <row r="68" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="59"/>
-      <c r="B68" s="186"/>
-      <c r="C68" s="78"/>
-      <c r="D68" s="79"/>
-      <c r="E68" s="80"/>
-      <c r="F68" s="81"/>
-      <c r="G68" s="79"/>
-      <c r="H68" s="80"/>
-      <c r="I68" s="81"/>
-      <c r="J68" s="121"/>
-      <c r="K68" s="80"/>
-      <c r="L68" s="81"/>
-      <c r="M68" s="79"/>
-      <c r="N68" s="80"/>
-      <c r="O68" s="81"/>
-      <c r="P68" s="79"/>
-      <c r="Q68" s="80"/>
-      <c r="R68" s="81"/>
-      <c r="S68" s="114"/>
-      <c r="T68" s="113"/>
-      <c r="U68" s="81"/>
-      <c r="V68" s="79"/>
-      <c r="W68" s="113"/>
-      <c r="X68" s="119"/>
+      <c r="B68" s="113"/>
+      <c r="C68" s="138"/>
+      <c r="D68" s="139"/>
+      <c r="E68" s="140"/>
+      <c r="F68" s="141"/>
+      <c r="G68" s="139"/>
+      <c r="H68" s="140"/>
+      <c r="I68" s="141"/>
+      <c r="J68" s="164"/>
+      <c r="K68" s="140"/>
+      <c r="L68" s="141"/>
+      <c r="M68" s="139"/>
+      <c r="N68" s="140"/>
+      <c r="O68" s="141"/>
+      <c r="P68" s="139"/>
+      <c r="Q68" s="140"/>
+      <c r="R68" s="141"/>
+      <c r="S68" s="163"/>
+      <c r="T68" s="162"/>
+      <c r="U68" s="141"/>
+      <c r="V68" s="139"/>
+      <c r="W68" s="162"/>
+      <c r="X68" s="77"/>
       <c r="Y68" s="65"/>
       <c r="Z68" s="65"/>
       <c r="AA68" s="65"/>
@@ -5375,29 +5337,29 @@
     </row>
     <row r="69" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="59"/>
-      <c r="B69" s="186"/>
-      <c r="C69" s="78"/>
-      <c r="D69" s="79"/>
-      <c r="E69" s="113"/>
-      <c r="F69" s="81"/>
-      <c r="G69" s="79"/>
-      <c r="H69" s="113"/>
-      <c r="I69" s="81"/>
-      <c r="J69" s="79"/>
-      <c r="K69" s="113"/>
-      <c r="L69" s="81"/>
-      <c r="M69" s="79"/>
-      <c r="N69" s="113"/>
-      <c r="O69" s="81"/>
-      <c r="P69" s="79"/>
-      <c r="Q69" s="113"/>
-      <c r="R69" s="81"/>
-      <c r="S69" s="79"/>
-      <c r="T69" s="113"/>
-      <c r="U69" s="81"/>
-      <c r="V69" s="79"/>
-      <c r="W69" s="80"/>
-      <c r="X69" s="119"/>
+      <c r="B69" s="113"/>
+      <c r="C69" s="138"/>
+      <c r="D69" s="139"/>
+      <c r="E69" s="162"/>
+      <c r="F69" s="141"/>
+      <c r="G69" s="139"/>
+      <c r="H69" s="162"/>
+      <c r="I69" s="141"/>
+      <c r="J69" s="139"/>
+      <c r="K69" s="162"/>
+      <c r="L69" s="141"/>
+      <c r="M69" s="139"/>
+      <c r="N69" s="162"/>
+      <c r="O69" s="141"/>
+      <c r="P69" s="139"/>
+      <c r="Q69" s="162"/>
+      <c r="R69" s="141"/>
+      <c r="S69" s="139"/>
+      <c r="T69" s="162"/>
+      <c r="U69" s="141"/>
+      <c r="V69" s="139"/>
+      <c r="W69" s="140"/>
+      <c r="X69" s="77"/>
       <c r="Y69" s="65"/>
       <c r="Z69" s="65"/>
       <c r="AA69" s="65"/>
@@ -5407,29 +5369,29 @@
     </row>
     <row r="70" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="59"/>
-      <c r="B70" s="186"/>
-      <c r="C70" s="78"/>
-      <c r="D70" s="79"/>
-      <c r="E70" s="113"/>
-      <c r="F70" s="81"/>
-      <c r="G70" s="79"/>
-      <c r="H70" s="113"/>
-      <c r="I70" s="81"/>
-      <c r="J70" s="79"/>
-      <c r="K70" s="113"/>
-      <c r="L70" s="81"/>
-      <c r="M70" s="79"/>
-      <c r="N70" s="113"/>
-      <c r="O70" s="81"/>
-      <c r="P70" s="79"/>
-      <c r="Q70" s="113"/>
-      <c r="R70" s="81"/>
-      <c r="S70" s="79"/>
-      <c r="T70" s="113"/>
-      <c r="U70" s="81"/>
-      <c r="V70" s="79"/>
-      <c r="W70" s="80"/>
-      <c r="X70" s="119"/>
+      <c r="B70" s="113"/>
+      <c r="C70" s="138"/>
+      <c r="D70" s="139"/>
+      <c r="E70" s="162"/>
+      <c r="F70" s="141"/>
+      <c r="G70" s="139"/>
+      <c r="H70" s="162"/>
+      <c r="I70" s="141"/>
+      <c r="J70" s="139"/>
+      <c r="K70" s="162"/>
+      <c r="L70" s="141"/>
+      <c r="M70" s="139"/>
+      <c r="N70" s="162"/>
+      <c r="O70" s="141"/>
+      <c r="P70" s="139"/>
+      <c r="Q70" s="162"/>
+      <c r="R70" s="141"/>
+      <c r="S70" s="139"/>
+      <c r="T70" s="162"/>
+      <c r="U70" s="141"/>
+      <c r="V70" s="139"/>
+      <c r="W70" s="140"/>
+      <c r="X70" s="77"/>
       <c r="Y70" s="65"/>
       <c r="Z70" s="65"/>
       <c r="AA70" s="65"/>
@@ -5438,62 +5400,62 @@
       <c r="AD70" s="66"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="125"/>
-      <c r="B71" s="186"/>
-      <c r="C71" s="78"/>
-      <c r="D71" s="126"/>
-      <c r="E71" s="113"/>
-      <c r="F71" s="127"/>
-      <c r="G71" s="126"/>
-      <c r="H71" s="113"/>
-      <c r="I71" s="81"/>
-      <c r="J71" s="126"/>
-      <c r="K71" s="113"/>
-      <c r="L71" s="127"/>
-      <c r="M71" s="126"/>
-      <c r="N71" s="113"/>
-      <c r="O71" s="81"/>
-      <c r="P71" s="126"/>
-      <c r="Q71" s="113"/>
-      <c r="R71" s="81"/>
-      <c r="S71" s="126"/>
-      <c r="T71" s="113"/>
-      <c r="U71" s="81"/>
-      <c r="V71" s="126"/>
-      <c r="W71" s="113"/>
-      <c r="X71" s="149"/>
-      <c r="Y71" s="129"/>
-      <c r="Z71" s="129"/>
-      <c r="AA71" s="129"/>
-      <c r="AB71" s="129"/>
-      <c r="AC71" s="129"/>
-      <c r="AD71" s="129"/>
+      <c r="A71" s="79"/>
+      <c r="B71" s="113"/>
+      <c r="C71" s="138"/>
+      <c r="D71" s="165"/>
+      <c r="E71" s="162"/>
+      <c r="F71" s="166"/>
+      <c r="G71" s="165"/>
+      <c r="H71" s="162"/>
+      <c r="I71" s="141"/>
+      <c r="J71" s="165"/>
+      <c r="K71" s="162"/>
+      <c r="L71" s="166"/>
+      <c r="M71" s="165"/>
+      <c r="N71" s="162"/>
+      <c r="O71" s="141"/>
+      <c r="P71" s="165"/>
+      <c r="Q71" s="162"/>
+      <c r="R71" s="141"/>
+      <c r="S71" s="165"/>
+      <c r="T71" s="162"/>
+      <c r="U71" s="141"/>
+      <c r="V71" s="165"/>
+      <c r="W71" s="162"/>
+      <c r="X71" s="86"/>
+      <c r="Y71" s="81"/>
+      <c r="Z71" s="81"/>
+      <c r="AA71" s="81"/>
+      <c r="AB71" s="81"/>
+      <c r="AC71" s="81"/>
+      <c r="AD71" s="81"/>
     </row>
     <row r="72" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
-      <c r="B72" s="90"/>
-      <c r="C72" s="154"/>
-      <c r="D72" s="92"/>
-      <c r="E72" s="131"/>
-      <c r="F72" s="95"/>
-      <c r="G72" s="92"/>
-      <c r="H72" s="131"/>
-      <c r="I72" s="95"/>
-      <c r="J72" s="92"/>
-      <c r="K72" s="131"/>
-      <c r="L72" s="95"/>
-      <c r="M72" s="92"/>
-      <c r="N72" s="131"/>
-      <c r="O72" s="95"/>
-      <c r="P72" s="92"/>
-      <c r="Q72" s="131"/>
-      <c r="R72" s="95"/>
-      <c r="S72" s="92"/>
-      <c r="T72" s="131"/>
-      <c r="U72" s="95"/>
-      <c r="V72" s="92"/>
-      <c r="W72" s="131"/>
-      <c r="X72" s="150"/>
+      <c r="B72" s="71"/>
+      <c r="C72" s="167"/>
+      <c r="D72" s="148"/>
+      <c r="E72" s="168"/>
+      <c r="F72" s="151"/>
+      <c r="G72" s="148"/>
+      <c r="H72" s="168"/>
+      <c r="I72" s="151"/>
+      <c r="J72" s="148"/>
+      <c r="K72" s="168"/>
+      <c r="L72" s="151"/>
+      <c r="M72" s="148"/>
+      <c r="N72" s="168"/>
+      <c r="O72" s="151"/>
+      <c r="P72" s="148"/>
+      <c r="Q72" s="168"/>
+      <c r="R72" s="151"/>
+      <c r="S72" s="148"/>
+      <c r="T72" s="168"/>
+      <c r="U72" s="151"/>
+      <c r="V72" s="148"/>
+      <c r="W72" s="168"/>
+      <c r="X72" s="87"/>
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
       <c r="AA72" s="2"/>
@@ -5503,31 +5465,31 @@
     </row>
     <row r="73" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
-      <c r="B73" s="133" t="s">
+      <c r="B73" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="C73" s="134"/>
-      <c r="D73" s="105"/>
-      <c r="E73" s="106"/>
-      <c r="F73" s="135"/>
-      <c r="G73" s="105"/>
-      <c r="H73" s="106"/>
-      <c r="I73" s="135"/>
-      <c r="J73" s="105"/>
-      <c r="K73" s="106"/>
-      <c r="L73" s="135"/>
-      <c r="M73" s="105"/>
-      <c r="N73" s="106"/>
-      <c r="O73" s="135"/>
-      <c r="P73" s="105"/>
-      <c r="Q73" s="106"/>
-      <c r="R73" s="135"/>
-      <c r="S73" s="105"/>
-      <c r="T73" s="106"/>
-      <c r="U73" s="135"/>
-      <c r="V73" s="105"/>
-      <c r="W73" s="106"/>
-      <c r="X73" s="150"/>
+      <c r="C73" s="169"/>
+      <c r="D73" s="157"/>
+      <c r="E73" s="158"/>
+      <c r="F73" s="170"/>
+      <c r="G73" s="157"/>
+      <c r="H73" s="158"/>
+      <c r="I73" s="170"/>
+      <c r="J73" s="157"/>
+      <c r="K73" s="158"/>
+      <c r="L73" s="170"/>
+      <c r="M73" s="157"/>
+      <c r="N73" s="158"/>
+      <c r="O73" s="170"/>
+      <c r="P73" s="157"/>
+      <c r="Q73" s="158"/>
+      <c r="R73" s="170"/>
+      <c r="S73" s="157"/>
+      <c r="T73" s="158"/>
+      <c r="U73" s="170"/>
+      <c r="V73" s="157"/>
+      <c r="W73" s="158"/>
+      <c r="X73" s="87"/>
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
       <c r="AA73" s="2"/>
@@ -5537,31 +5499,31 @@
     </row>
     <row r="74" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
-      <c r="B74" s="139" t="s">
+      <c r="B74" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="C74" s="155"/>
-      <c r="D74" s="141"/>
-      <c r="E74" s="142"/>
-      <c r="F74" s="144"/>
-      <c r="G74" s="141"/>
-      <c r="H74" s="142"/>
-      <c r="I74" s="144"/>
-      <c r="J74" s="141"/>
-      <c r="K74" s="142"/>
-      <c r="L74" s="144"/>
-      <c r="M74" s="141"/>
-      <c r="N74" s="142"/>
-      <c r="O74" s="144"/>
-      <c r="P74" s="141"/>
-      <c r="Q74" s="142"/>
-      <c r="R74" s="144"/>
-      <c r="S74" s="141"/>
-      <c r="T74" s="142"/>
-      <c r="U74" s="144"/>
-      <c r="V74" s="141"/>
-      <c r="W74" s="142"/>
-      <c r="X74" s="150"/>
+      <c r="C74" s="171"/>
+      <c r="D74" s="172"/>
+      <c r="E74" s="173"/>
+      <c r="F74" s="174"/>
+      <c r="G74" s="172"/>
+      <c r="H74" s="173"/>
+      <c r="I74" s="174"/>
+      <c r="J74" s="172"/>
+      <c r="K74" s="173"/>
+      <c r="L74" s="174"/>
+      <c r="M74" s="172"/>
+      <c r="N74" s="173"/>
+      <c r="O74" s="174"/>
+      <c r="P74" s="172"/>
+      <c r="Q74" s="173"/>
+      <c r="R74" s="174"/>
+      <c r="S74" s="172"/>
+      <c r="T74" s="173"/>
+      <c r="U74" s="174"/>
+      <c r="V74" s="172"/>
+      <c r="W74" s="173"/>
+      <c r="X74" s="87"/>
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
       <c r="AA74" s="2"/>
@@ -5571,29 +5533,29 @@
     </row>
     <row r="75" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
-      <c r="B75" s="147"/>
-      <c r="C75" s="174"/>
-      <c r="D75" s="175"/>
-      <c r="E75" s="176"/>
-      <c r="F75" s="177"/>
-      <c r="G75" s="175"/>
-      <c r="H75" s="176"/>
-      <c r="I75" s="177"/>
-      <c r="J75" s="175"/>
-      <c r="K75" s="176"/>
-      <c r="L75" s="177"/>
-      <c r="M75" s="175"/>
-      <c r="N75" s="176"/>
-      <c r="O75" s="177"/>
-      <c r="P75" s="175"/>
-      <c r="Q75" s="176"/>
-      <c r="R75" s="177"/>
-      <c r="S75" s="175"/>
-      <c r="T75" s="176"/>
-      <c r="U75" s="179"/>
-      <c r="V75" s="180"/>
-      <c r="W75" s="181"/>
-      <c r="X75" s="150"/>
+      <c r="B75" s="84"/>
+      <c r="C75" s="118"/>
+      <c r="D75" s="116"/>
+      <c r="E75" s="117"/>
+      <c r="F75" s="115"/>
+      <c r="G75" s="116"/>
+      <c r="H75" s="117"/>
+      <c r="I75" s="115"/>
+      <c r="J75" s="116"/>
+      <c r="K75" s="117"/>
+      <c r="L75" s="115"/>
+      <c r="M75" s="116"/>
+      <c r="N75" s="117"/>
+      <c r="O75" s="115"/>
+      <c r="P75" s="116"/>
+      <c r="Q75" s="117"/>
+      <c r="R75" s="115"/>
+      <c r="S75" s="116"/>
+      <c r="T75" s="117"/>
+      <c r="U75" s="109"/>
+      <c r="V75" s="110"/>
+      <c r="W75" s="111"/>
+      <c r="X75" s="87"/>
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
       <c r="AA75" s="2"/>
@@ -5604,7 +5566,7 @@
     <row r="76" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
       <c r="B76" s="9"/>
-      <c r="C76" s="148" t="s">
+      <c r="C76" s="85" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="15" t="s">
@@ -5667,7 +5629,7 @@
       <c r="W76" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="X76" s="150"/>
+      <c r="X76" s="87"/>
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
       <c r="AA76" s="2"/>
@@ -5699,7 +5661,7 @@
       <c r="U77" s="23"/>
       <c r="V77" s="24"/>
       <c r="W77" s="25"/>
-      <c r="X77" s="150"/>
+      <c r="X77" s="87"/>
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
       <c r="AA77" s="2"/>
@@ -5731,7 +5693,7 @@
       <c r="U78" s="32"/>
       <c r="V78" s="33"/>
       <c r="W78" s="34"/>
-      <c r="X78" s="150"/>
+      <c r="X78" s="87"/>
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
       <c r="AA78" s="2"/>
@@ -5763,7 +5725,7 @@
       <c r="U79" s="32"/>
       <c r="V79" s="33"/>
       <c r="W79" s="34"/>
-      <c r="X79" s="150"/>
+      <c r="X79" s="87"/>
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
       <c r="AA79" s="2"/>
@@ -5795,7 +5757,7 @@
       <c r="U80" s="32"/>
       <c r="V80" s="33"/>
       <c r="W80" s="34"/>
-      <c r="X80" s="150"/>
+      <c r="X80" s="87"/>
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
       <c r="AA80" s="2"/>
@@ -5827,7 +5789,7 @@
       <c r="U81" s="32"/>
       <c r="V81" s="33"/>
       <c r="W81" s="34"/>
-      <c r="X81" s="150"/>
+      <c r="X81" s="87"/>
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
       <c r="AA81" s="2"/>
@@ -5859,7 +5821,7 @@
       <c r="U82" s="32"/>
       <c r="V82" s="33"/>
       <c r="W82" s="34"/>
-      <c r="X82" s="150"/>
+      <c r="X82" s="87"/>
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
       <c r="AA82" s="2"/>
@@ -5891,7 +5853,7 @@
       <c r="U83" s="32"/>
       <c r="V83" s="33"/>
       <c r="W83" s="34"/>
-      <c r="X83" s="150"/>
+      <c r="X83" s="87"/>
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
       <c r="AA83" s="2"/>
@@ -5923,7 +5885,7 @@
       <c r="U84" s="32"/>
       <c r="V84" s="33"/>
       <c r="W84" s="34"/>
-      <c r="X84" s="150"/>
+      <c r="X84" s="87"/>
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
       <c r="AA84" s="2"/>
@@ -5955,7 +5917,7 @@
       <c r="U85" s="32"/>
       <c r="V85" s="33"/>
       <c r="W85" s="34"/>
-      <c r="X85" s="150"/>
+      <c r="X85" s="87"/>
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
       <c r="AA85" s="2"/>
@@ -5987,7 +5949,7 @@
       <c r="U86" s="32"/>
       <c r="V86" s="33"/>
       <c r="W86" s="34"/>
-      <c r="X86" s="150"/>
+      <c r="X86" s="87"/>
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
       <c r="AA86" s="2"/>
@@ -6019,7 +5981,7 @@
       <c r="U87" s="32"/>
       <c r="V87" s="33"/>
       <c r="W87" s="34"/>
-      <c r="X87" s="150"/>
+      <c r="X87" s="87"/>
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
       <c r="AA87" s="2"/>
@@ -6032,7 +5994,7 @@
       <c r="B88" s="26"/>
       <c r="C88" s="37"/>
       <c r="D88" s="38"/>
-      <c r="E88" s="151"/>
+      <c r="E88" s="88"/>
       <c r="F88" s="40"/>
       <c r="G88" s="38"/>
       <c r="H88" s="41"/>
@@ -6051,7 +6013,7 @@
       <c r="U88" s="43"/>
       <c r="V88" s="44"/>
       <c r="W88" s="45"/>
-      <c r="X88" s="150"/>
+      <c r="X88" s="87"/>
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
       <c r="AA88" s="2"/>
@@ -6157,7 +6119,7 @@
       <c r="W90" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="X90" s="119"/>
+      <c r="X90" s="77"/>
       <c r="Y90" s="65"/>
       <c r="Z90" s="65"/>
       <c r="AA90" s="65"/>
@@ -6167,35 +6129,35 @@
     </row>
     <row r="91" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="59"/>
-      <c r="B91" s="185" t="s">
+      <c r="B91" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="C91" s="67"/>
-      <c r="D91" s="68"/>
-      <c r="E91" s="69"/>
-      <c r="F91" s="70"/>
-      <c r="G91" s="190"/>
-      <c r="H91" s="69"/>
-      <c r="I91" s="70"/>
-      <c r="J91" s="71"/>
-      <c r="K91" s="69"/>
-      <c r="L91" s="70"/>
-      <c r="M91" s="68"/>
-      <c r="N91" s="69"/>
-      <c r="O91" s="70"/>
-      <c r="P91" s="72"/>
-      <c r="Q91" s="69"/>
-      <c r="R91" s="70"/>
-      <c r="S91" s="68"/>
-      <c r="T91" s="69"/>
-      <c r="U91" s="70"/>
-      <c r="V91" s="68"/>
-      <c r="W91" s="69"/>
-      <c r="X91" s="119"/>
-      <c r="Y91" s="75" t="s">
+      <c r="C91" s="131"/>
+      <c r="D91" s="132"/>
+      <c r="E91" s="133"/>
+      <c r="F91" s="134"/>
+      <c r="G91" s="135"/>
+      <c r="H91" s="133"/>
+      <c r="I91" s="134"/>
+      <c r="J91" s="136"/>
+      <c r="K91" s="133"/>
+      <c r="L91" s="134"/>
+      <c r="M91" s="132"/>
+      <c r="N91" s="133"/>
+      <c r="O91" s="134"/>
+      <c r="P91" s="137"/>
+      <c r="Q91" s="133"/>
+      <c r="R91" s="134"/>
+      <c r="S91" s="132"/>
+      <c r="T91" s="133"/>
+      <c r="U91" s="134"/>
+      <c r="V91" s="132"/>
+      <c r="W91" s="133"/>
+      <c r="X91" s="77"/>
+      <c r="Y91" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="Z91" s="76">
+      <c r="Z91" s="68">
         <f>COUNTIF(C91:W110,Y91)</f>
         <v>0</v>
       </c>
@@ -6206,33 +6168,33 @@
     </row>
     <row r="92" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="59"/>
-      <c r="B92" s="186"/>
-      <c r="C92" s="78"/>
-      <c r="D92" s="79"/>
-      <c r="E92" s="80"/>
-      <c r="F92" s="81"/>
-      <c r="G92" s="191"/>
-      <c r="H92" s="80"/>
-      <c r="I92" s="81"/>
-      <c r="J92" s="79"/>
-      <c r="K92" s="80"/>
-      <c r="L92" s="82"/>
-      <c r="M92" s="79"/>
-      <c r="N92" s="83"/>
-      <c r="O92" s="81"/>
-      <c r="P92" s="84"/>
-      <c r="Q92" s="80"/>
-      <c r="R92" s="82"/>
-      <c r="S92" s="79"/>
-      <c r="T92" s="80"/>
-      <c r="U92" s="81"/>
-      <c r="V92" s="79"/>
-      <c r="W92" s="83"/>
-      <c r="X92" s="119"/>
-      <c r="Y92" s="87" t="s">
+      <c r="B92" s="113"/>
+      <c r="C92" s="138"/>
+      <c r="D92" s="139"/>
+      <c r="E92" s="140"/>
+      <c r="F92" s="141"/>
+      <c r="G92" s="142"/>
+      <c r="H92" s="140"/>
+      <c r="I92" s="141"/>
+      <c r="J92" s="139"/>
+      <c r="K92" s="140"/>
+      <c r="L92" s="143"/>
+      <c r="M92" s="139"/>
+      <c r="N92" s="144"/>
+      <c r="O92" s="141"/>
+      <c r="P92" s="145"/>
+      <c r="Q92" s="140"/>
+      <c r="R92" s="143"/>
+      <c r="S92" s="139"/>
+      <c r="T92" s="140"/>
+      <c r="U92" s="141"/>
+      <c r="V92" s="139"/>
+      <c r="W92" s="144"/>
+      <c r="X92" s="77"/>
+      <c r="Y92" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="Z92" s="88">
+      <c r="Z92" s="70">
         <f>COUNTIF(C91:W110,Y92)</f>
         <v>0</v>
       </c>
@@ -6243,33 +6205,33 @@
     </row>
     <row r="93" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="59"/>
-      <c r="B93" s="186"/>
-      <c r="C93" s="78"/>
-      <c r="D93" s="79"/>
-      <c r="E93" s="80"/>
-      <c r="F93" s="81"/>
-      <c r="G93" s="191"/>
-      <c r="H93" s="80"/>
-      <c r="I93" s="81"/>
-      <c r="J93" s="79"/>
-      <c r="K93" s="80"/>
-      <c r="L93" s="82"/>
-      <c r="M93" s="79"/>
-      <c r="N93" s="83"/>
-      <c r="O93" s="81"/>
-      <c r="P93" s="84"/>
-      <c r="Q93" s="83"/>
-      <c r="R93" s="81"/>
-      <c r="S93" s="79"/>
-      <c r="T93" s="83"/>
-      <c r="U93" s="81"/>
-      <c r="V93" s="79"/>
-      <c r="W93" s="83"/>
-      <c r="X93" s="119"/>
-      <c r="Y93" s="87" t="s">
+      <c r="B93" s="113"/>
+      <c r="C93" s="138"/>
+      <c r="D93" s="139"/>
+      <c r="E93" s="140"/>
+      <c r="F93" s="141"/>
+      <c r="G93" s="142"/>
+      <c r="H93" s="140"/>
+      <c r="I93" s="141"/>
+      <c r="J93" s="139"/>
+      <c r="K93" s="140"/>
+      <c r="L93" s="143"/>
+      <c r="M93" s="139"/>
+      <c r="N93" s="144"/>
+      <c r="O93" s="141"/>
+      <c r="P93" s="145"/>
+      <c r="Q93" s="144"/>
+      <c r="R93" s="141"/>
+      <c r="S93" s="139"/>
+      <c r="T93" s="144"/>
+      <c r="U93" s="141"/>
+      <c r="V93" s="139"/>
+      <c r="W93" s="144"/>
+      <c r="X93" s="77"/>
+      <c r="Y93" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="Z93" s="88">
+      <c r="Z93" s="70">
         <f>COUNTIF(C91:W110,Y93)</f>
         <v>0</v>
       </c>
@@ -6280,33 +6242,33 @@
     </row>
     <row r="94" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="59"/>
-      <c r="B94" s="186"/>
-      <c r="C94" s="89"/>
-      <c r="D94" s="79"/>
-      <c r="E94" s="83"/>
-      <c r="F94" s="82"/>
-      <c r="G94" s="79"/>
-      <c r="H94" s="83"/>
-      <c r="I94" s="82"/>
-      <c r="J94" s="79"/>
-      <c r="K94" s="83"/>
-      <c r="L94" s="82"/>
-      <c r="M94" s="79"/>
-      <c r="N94" s="83"/>
-      <c r="O94" s="82"/>
-      <c r="P94" s="84"/>
-      <c r="Q94" s="83"/>
-      <c r="R94" s="82"/>
-      <c r="S94" s="79"/>
-      <c r="T94" s="83"/>
-      <c r="U94" s="81"/>
-      <c r="V94" s="79"/>
-      <c r="W94" s="83"/>
-      <c r="X94" s="119"/>
-      <c r="Y94" s="87" t="s">
+      <c r="B94" s="113"/>
+      <c r="C94" s="146"/>
+      <c r="D94" s="139"/>
+      <c r="E94" s="144"/>
+      <c r="F94" s="143"/>
+      <c r="G94" s="139"/>
+      <c r="H94" s="144"/>
+      <c r="I94" s="143"/>
+      <c r="J94" s="139"/>
+      <c r="K94" s="144"/>
+      <c r="L94" s="143"/>
+      <c r="M94" s="139"/>
+      <c r="N94" s="144"/>
+      <c r="O94" s="143"/>
+      <c r="P94" s="145"/>
+      <c r="Q94" s="144"/>
+      <c r="R94" s="143"/>
+      <c r="S94" s="139"/>
+      <c r="T94" s="144"/>
+      <c r="U94" s="141"/>
+      <c r="V94" s="139"/>
+      <c r="W94" s="144"/>
+      <c r="X94" s="77"/>
+      <c r="Y94" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="Z94" s="88">
+      <c r="Z94" s="70">
         <f>COUNTIF(C91:W110,Y94)</f>
         <v>0</v>
       </c>
@@ -6317,33 +6279,33 @@
     </row>
     <row r="95" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="59"/>
-      <c r="B95" s="189"/>
-      <c r="C95" s="91"/>
-      <c r="D95" s="92"/>
-      <c r="E95" s="93"/>
-      <c r="F95" s="94"/>
-      <c r="G95" s="92"/>
-      <c r="H95" s="93"/>
-      <c r="I95" s="95"/>
-      <c r="J95" s="92"/>
-      <c r="K95" s="93"/>
-      <c r="L95" s="96"/>
-      <c r="M95" s="92"/>
-      <c r="N95" s="93"/>
-      <c r="O95" s="94"/>
-      <c r="P95" s="97"/>
-      <c r="Q95" s="93"/>
-      <c r="R95" s="95"/>
-      <c r="S95" s="92"/>
-      <c r="T95" s="93"/>
-      <c r="U95" s="95"/>
-      <c r="V95" s="92"/>
-      <c r="W95" s="93"/>
-      <c r="X95" s="119"/>
-      <c r="Y95" s="87" t="s">
+      <c r="B95" s="114"/>
+      <c r="C95" s="147"/>
+      <c r="D95" s="148"/>
+      <c r="E95" s="149"/>
+      <c r="F95" s="150"/>
+      <c r="G95" s="148"/>
+      <c r="H95" s="149"/>
+      <c r="I95" s="151"/>
+      <c r="J95" s="148"/>
+      <c r="K95" s="149"/>
+      <c r="L95" s="152"/>
+      <c r="M95" s="148"/>
+      <c r="N95" s="149"/>
+      <c r="O95" s="150"/>
+      <c r="P95" s="153"/>
+      <c r="Q95" s="149"/>
+      <c r="R95" s="151"/>
+      <c r="S95" s="148"/>
+      <c r="T95" s="149"/>
+      <c r="U95" s="151"/>
+      <c r="V95" s="148"/>
+      <c r="W95" s="149"/>
+      <c r="X95" s="77"/>
+      <c r="Y95" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="Z95" s="88">
+      <c r="Z95" s="70">
         <f>COUNTIF(C91:W110,Y95)</f>
         <v>0</v>
       </c>
@@ -6354,35 +6316,35 @@
     </row>
     <row r="96" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="59"/>
-      <c r="B96" s="101" t="s">
+      <c r="B96" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="C96" s="102"/>
-      <c r="D96" s="103"/>
-      <c r="E96" s="104"/>
-      <c r="F96" s="102"/>
-      <c r="G96" s="103"/>
-      <c r="H96" s="104"/>
-      <c r="I96" s="102"/>
-      <c r="J96" s="103"/>
-      <c r="K96" s="104"/>
-      <c r="L96" s="102"/>
-      <c r="M96" s="103"/>
-      <c r="N96" s="104"/>
-      <c r="O96" s="102"/>
-      <c r="P96" s="103"/>
-      <c r="Q96" s="104"/>
-      <c r="R96" s="102"/>
-      <c r="S96" s="105"/>
-      <c r="T96" s="106"/>
-      <c r="U96" s="102"/>
-      <c r="V96" s="105"/>
-      <c r="W96" s="106"/>
-      <c r="X96" s="119"/>
-      <c r="Y96" s="87" t="s">
+      <c r="C96" s="154"/>
+      <c r="D96" s="155"/>
+      <c r="E96" s="156"/>
+      <c r="F96" s="154"/>
+      <c r="G96" s="155"/>
+      <c r="H96" s="156"/>
+      <c r="I96" s="154"/>
+      <c r="J96" s="155"/>
+      <c r="K96" s="156"/>
+      <c r="L96" s="154"/>
+      <c r="M96" s="155"/>
+      <c r="N96" s="156"/>
+      <c r="O96" s="154"/>
+      <c r="P96" s="155"/>
+      <c r="Q96" s="156"/>
+      <c r="R96" s="154"/>
+      <c r="S96" s="157"/>
+      <c r="T96" s="158"/>
+      <c r="U96" s="154"/>
+      <c r="V96" s="157"/>
+      <c r="W96" s="158"/>
+      <c r="X96" s="77"/>
+      <c r="Y96" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="Z96" s="88">
+      <c r="Z96" s="70">
         <f>COUNTIF(C91:W110,Y96)</f>
         <v>0</v>
       </c>
@@ -6393,35 +6355,35 @@
     </row>
     <row r="97" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="59"/>
-      <c r="B97" s="185" t="s">
+      <c r="B97" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="C97" s="67"/>
-      <c r="D97" s="108"/>
-      <c r="E97" s="109"/>
-      <c r="F97" s="110"/>
-      <c r="G97" s="68"/>
-      <c r="H97" s="109"/>
-      <c r="I97" s="110"/>
-      <c r="J97" s="68"/>
-      <c r="K97" s="109"/>
-      <c r="L97" s="110"/>
-      <c r="M97" s="68"/>
-      <c r="N97" s="109"/>
-      <c r="O97" s="110"/>
-      <c r="P97" s="68"/>
-      <c r="Q97" s="109"/>
-      <c r="R97" s="110"/>
-      <c r="S97" s="68"/>
-      <c r="T97" s="109"/>
-      <c r="U97" s="110"/>
-      <c r="V97" s="68"/>
-      <c r="W97" s="152"/>
-      <c r="X97" s="119"/>
-      <c r="Y97" s="87" t="s">
+      <c r="C97" s="131"/>
+      <c r="D97" s="159"/>
+      <c r="E97" s="160"/>
+      <c r="F97" s="161"/>
+      <c r="G97" s="132"/>
+      <c r="H97" s="160"/>
+      <c r="I97" s="161"/>
+      <c r="J97" s="132"/>
+      <c r="K97" s="160"/>
+      <c r="L97" s="161"/>
+      <c r="M97" s="132"/>
+      <c r="N97" s="160"/>
+      <c r="O97" s="161"/>
+      <c r="P97" s="132"/>
+      <c r="Q97" s="160"/>
+      <c r="R97" s="161"/>
+      <c r="S97" s="132"/>
+      <c r="T97" s="160"/>
+      <c r="U97" s="161"/>
+      <c r="V97" s="132"/>
+      <c r="W97" s="175"/>
+      <c r="X97" s="77"/>
+      <c r="Y97" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="Z97" s="88">
+      <c r="Z97" s="70">
         <f>COUNTIF(C91:W110,Y97)</f>
         <v>0</v>
       </c>
@@ -6432,33 +6394,33 @@
     </row>
     <row r="98" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="59"/>
-      <c r="B98" s="186"/>
-      <c r="C98" s="78"/>
-      <c r="D98" s="79"/>
-      <c r="E98" s="113"/>
-      <c r="F98" s="81"/>
-      <c r="G98" s="79"/>
-      <c r="H98" s="113"/>
-      <c r="I98" s="81"/>
-      <c r="J98" s="114"/>
-      <c r="K98" s="113"/>
-      <c r="L98" s="81"/>
-      <c r="M98" s="79"/>
-      <c r="N98" s="113"/>
-      <c r="O98" s="81"/>
-      <c r="P98" s="79"/>
-      <c r="Q98" s="113"/>
-      <c r="R98" s="81"/>
-      <c r="S98" s="114"/>
-      <c r="T98" s="113"/>
-      <c r="U98" s="81"/>
-      <c r="V98" s="79"/>
-      <c r="W98" s="113"/>
-      <c r="X98" s="119"/>
-      <c r="Y98" s="87" t="s">
+      <c r="B98" s="113"/>
+      <c r="C98" s="138"/>
+      <c r="D98" s="139"/>
+      <c r="E98" s="162"/>
+      <c r="F98" s="141"/>
+      <c r="G98" s="139"/>
+      <c r="H98" s="162"/>
+      <c r="I98" s="141"/>
+      <c r="J98" s="163"/>
+      <c r="K98" s="162"/>
+      <c r="L98" s="141"/>
+      <c r="M98" s="139"/>
+      <c r="N98" s="162"/>
+      <c r="O98" s="141"/>
+      <c r="P98" s="139"/>
+      <c r="Q98" s="162"/>
+      <c r="R98" s="141"/>
+      <c r="S98" s="163"/>
+      <c r="T98" s="162"/>
+      <c r="U98" s="141"/>
+      <c r="V98" s="139"/>
+      <c r="W98" s="162"/>
+      <c r="X98" s="77"/>
+      <c r="Y98" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="Z98" s="88">
+      <c r="Z98" s="70">
         <f>COUNTIF(C91:W110,Y98)</f>
         <v>0</v>
       </c>
@@ -6469,33 +6431,33 @@
     </row>
     <row r="99" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="59"/>
-      <c r="B99" s="186"/>
-      <c r="C99" s="78"/>
-      <c r="D99" s="79"/>
-      <c r="E99" s="113"/>
-      <c r="F99" s="81"/>
-      <c r="G99" s="79"/>
-      <c r="H99" s="113"/>
-      <c r="I99" s="81"/>
-      <c r="J99" s="114"/>
-      <c r="K99" s="113"/>
-      <c r="L99" s="81"/>
-      <c r="M99" s="79"/>
-      <c r="N99" s="113"/>
-      <c r="O99" s="81"/>
-      <c r="P99" s="79"/>
-      <c r="Q99" s="113"/>
-      <c r="R99" s="81"/>
-      <c r="S99" s="114"/>
-      <c r="T99" s="113"/>
-      <c r="U99" s="81"/>
-      <c r="V99" s="79"/>
-      <c r="W99" s="113"/>
-      <c r="X99" s="119"/>
-      <c r="Y99" s="87" t="s">
+      <c r="B99" s="113"/>
+      <c r="C99" s="138"/>
+      <c r="D99" s="139"/>
+      <c r="E99" s="162"/>
+      <c r="F99" s="141"/>
+      <c r="G99" s="139"/>
+      <c r="H99" s="162"/>
+      <c r="I99" s="141"/>
+      <c r="J99" s="163"/>
+      <c r="K99" s="162"/>
+      <c r="L99" s="141"/>
+      <c r="M99" s="139"/>
+      <c r="N99" s="162"/>
+      <c r="O99" s="141"/>
+      <c r="P99" s="139"/>
+      <c r="Q99" s="162"/>
+      <c r="R99" s="141"/>
+      <c r="S99" s="163"/>
+      <c r="T99" s="162"/>
+      <c r="U99" s="141"/>
+      <c r="V99" s="139"/>
+      <c r="W99" s="162"/>
+      <c r="X99" s="77"/>
+      <c r="Y99" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="Z99" s="88">
+      <c r="Z99" s="70">
         <f>COUNTIF(C91:W110,Y99)</f>
         <v>0</v>
       </c>
@@ -6506,33 +6468,33 @@
     </row>
     <row r="100" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="59"/>
-      <c r="B100" s="186"/>
-      <c r="C100" s="78"/>
-      <c r="D100" s="79"/>
-      <c r="E100" s="80"/>
-      <c r="F100" s="81"/>
-      <c r="G100" s="114"/>
-      <c r="H100" s="80"/>
-      <c r="I100" s="81"/>
-      <c r="J100" s="79"/>
-      <c r="K100" s="80"/>
-      <c r="L100" s="81"/>
-      <c r="M100" s="79"/>
-      <c r="N100" s="80"/>
-      <c r="O100" s="81"/>
-      <c r="P100" s="79"/>
-      <c r="Q100" s="80"/>
-      <c r="R100" s="81"/>
-      <c r="S100" s="79"/>
-      <c r="T100" s="80"/>
-      <c r="U100" s="81"/>
-      <c r="V100" s="79"/>
-      <c r="W100" s="113"/>
-      <c r="X100" s="119"/>
-      <c r="Y100" s="153" t="s">
+      <c r="B100" s="113"/>
+      <c r="C100" s="138"/>
+      <c r="D100" s="139"/>
+      <c r="E100" s="140"/>
+      <c r="F100" s="141"/>
+      <c r="G100" s="163"/>
+      <c r="H100" s="140"/>
+      <c r="I100" s="141"/>
+      <c r="J100" s="139"/>
+      <c r="K100" s="140"/>
+      <c r="L100" s="141"/>
+      <c r="M100" s="139"/>
+      <c r="N100" s="140"/>
+      <c r="O100" s="141"/>
+      <c r="P100" s="139"/>
+      <c r="Q100" s="140"/>
+      <c r="R100" s="141"/>
+      <c r="S100" s="139"/>
+      <c r="T100" s="140"/>
+      <c r="U100" s="141"/>
+      <c r="V100" s="139"/>
+      <c r="W100" s="162"/>
+      <c r="X100" s="77"/>
+      <c r="Y100" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="Z100" s="117">
+      <c r="Z100" s="76">
         <f>COUNTIF(C91:W110,Y100)</f>
         <v>0</v>
       </c>
@@ -6543,29 +6505,29 @@
     </row>
     <row r="101" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="59"/>
-      <c r="B101" s="186"/>
-      <c r="C101" s="89"/>
-      <c r="D101" s="79"/>
-      <c r="E101" s="113"/>
-      <c r="F101" s="82"/>
-      <c r="G101" s="79"/>
-      <c r="H101" s="113"/>
-      <c r="I101" s="82"/>
-      <c r="J101" s="114"/>
-      <c r="K101" s="113"/>
-      <c r="L101" s="82"/>
-      <c r="M101" s="79"/>
-      <c r="N101" s="113"/>
-      <c r="O101" s="82"/>
-      <c r="P101" s="79"/>
-      <c r="Q101" s="113"/>
-      <c r="R101" s="82"/>
-      <c r="S101" s="114"/>
-      <c r="T101" s="113"/>
-      <c r="U101" s="82"/>
-      <c r="V101" s="79"/>
-      <c r="W101" s="113"/>
-      <c r="X101" s="119"/>
+      <c r="B101" s="113"/>
+      <c r="C101" s="146"/>
+      <c r="D101" s="139"/>
+      <c r="E101" s="162"/>
+      <c r="F101" s="143"/>
+      <c r="G101" s="139"/>
+      <c r="H101" s="162"/>
+      <c r="I101" s="143"/>
+      <c r="J101" s="163"/>
+      <c r="K101" s="162"/>
+      <c r="L101" s="143"/>
+      <c r="M101" s="139"/>
+      <c r="N101" s="162"/>
+      <c r="O101" s="143"/>
+      <c r="P101" s="139"/>
+      <c r="Q101" s="162"/>
+      <c r="R101" s="143"/>
+      <c r="S101" s="163"/>
+      <c r="T101" s="162"/>
+      <c r="U101" s="143"/>
+      <c r="V101" s="139"/>
+      <c r="W101" s="162"/>
+      <c r="X101" s="77"/>
       <c r="Y101" s="65"/>
       <c r="Z101" s="65"/>
       <c r="AA101" s="65"/>
@@ -6575,29 +6537,29 @@
     </row>
     <row r="102" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="59"/>
-      <c r="B102" s="186"/>
-      <c r="C102" s="89"/>
-      <c r="D102" s="79"/>
-      <c r="E102" s="113"/>
-      <c r="F102" s="82"/>
-      <c r="G102" s="79"/>
-      <c r="H102" s="113"/>
-      <c r="I102" s="82"/>
-      <c r="J102" s="114"/>
-      <c r="K102" s="113"/>
-      <c r="L102" s="82"/>
-      <c r="M102" s="79"/>
-      <c r="N102" s="113"/>
-      <c r="O102" s="82"/>
-      <c r="P102" s="79"/>
-      <c r="Q102" s="113"/>
-      <c r="R102" s="82"/>
-      <c r="S102" s="114"/>
-      <c r="T102" s="113"/>
-      <c r="U102" s="81"/>
-      <c r="V102" s="79"/>
-      <c r="W102" s="113"/>
-      <c r="X102" s="119"/>
+      <c r="B102" s="113"/>
+      <c r="C102" s="146"/>
+      <c r="D102" s="139"/>
+      <c r="E102" s="162"/>
+      <c r="F102" s="143"/>
+      <c r="G102" s="139"/>
+      <c r="H102" s="162"/>
+      <c r="I102" s="143"/>
+      <c r="J102" s="163"/>
+      <c r="K102" s="162"/>
+      <c r="L102" s="143"/>
+      <c r="M102" s="139"/>
+      <c r="N102" s="162"/>
+      <c r="O102" s="143"/>
+      <c r="P102" s="139"/>
+      <c r="Q102" s="162"/>
+      <c r="R102" s="143"/>
+      <c r="S102" s="163"/>
+      <c r="T102" s="162"/>
+      <c r="U102" s="141"/>
+      <c r="V102" s="139"/>
+      <c r="W102" s="162"/>
+      <c r="X102" s="77"/>
       <c r="Y102" s="65"/>
       <c r="Z102" s="65"/>
       <c r="AA102" s="65"/>
@@ -6607,29 +6569,29 @@
     </row>
     <row r="103" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="59"/>
-      <c r="B103" s="186"/>
-      <c r="C103" s="78"/>
-      <c r="D103" s="79"/>
-      <c r="E103" s="113"/>
-      <c r="F103" s="81"/>
-      <c r="G103" s="79"/>
-      <c r="H103" s="113"/>
-      <c r="I103" s="82"/>
-      <c r="J103" s="114"/>
-      <c r="K103" s="113"/>
-      <c r="L103" s="82"/>
-      <c r="M103" s="79"/>
-      <c r="N103" s="113"/>
-      <c r="O103" s="81"/>
-      <c r="P103" s="79"/>
-      <c r="Q103" s="113"/>
-      <c r="R103" s="81"/>
-      <c r="S103" s="114"/>
-      <c r="T103" s="113"/>
-      <c r="U103" s="82"/>
-      <c r="V103" s="79"/>
-      <c r="W103" s="113"/>
-      <c r="X103" s="119"/>
+      <c r="B103" s="113"/>
+      <c r="C103" s="138"/>
+      <c r="D103" s="139"/>
+      <c r="E103" s="162"/>
+      <c r="F103" s="141"/>
+      <c r="G103" s="139"/>
+      <c r="H103" s="162"/>
+      <c r="I103" s="143"/>
+      <c r="J103" s="163"/>
+      <c r="K103" s="162"/>
+      <c r="L103" s="143"/>
+      <c r="M103" s="139"/>
+      <c r="N103" s="162"/>
+      <c r="O103" s="141"/>
+      <c r="P103" s="139"/>
+      <c r="Q103" s="162"/>
+      <c r="R103" s="141"/>
+      <c r="S103" s="163"/>
+      <c r="T103" s="162"/>
+      <c r="U103" s="143"/>
+      <c r="V103" s="139"/>
+      <c r="W103" s="162"/>
+      <c r="X103" s="77"/>
       <c r="Y103" s="65"/>
       <c r="Z103" s="65"/>
       <c r="AA103" s="65"/>
@@ -6639,29 +6601,29 @@
     </row>
     <row r="104" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="59"/>
-      <c r="B104" s="186"/>
-      <c r="C104" s="78"/>
-      <c r="D104" s="79"/>
-      <c r="E104" s="80"/>
-      <c r="F104" s="81"/>
-      <c r="G104" s="79"/>
-      <c r="H104" s="80"/>
-      <c r="I104" s="81"/>
-      <c r="J104" s="121"/>
-      <c r="K104" s="80"/>
-      <c r="L104" s="81"/>
-      <c r="M104" s="79"/>
-      <c r="N104" s="80"/>
-      <c r="O104" s="81"/>
-      <c r="P104" s="79"/>
-      <c r="Q104" s="80"/>
-      <c r="R104" s="81"/>
-      <c r="S104" s="114"/>
-      <c r="T104" s="113"/>
-      <c r="U104" s="81"/>
-      <c r="V104" s="79"/>
-      <c r="W104" s="113"/>
-      <c r="X104" s="119"/>
+      <c r="B104" s="113"/>
+      <c r="C104" s="138"/>
+      <c r="D104" s="139"/>
+      <c r="E104" s="140"/>
+      <c r="F104" s="141"/>
+      <c r="G104" s="139"/>
+      <c r="H104" s="140"/>
+      <c r="I104" s="141"/>
+      <c r="J104" s="164"/>
+      <c r="K104" s="140"/>
+      <c r="L104" s="141"/>
+      <c r="M104" s="139"/>
+      <c r="N104" s="140"/>
+      <c r="O104" s="141"/>
+      <c r="P104" s="139"/>
+      <c r="Q104" s="140"/>
+      <c r="R104" s="141"/>
+      <c r="S104" s="163"/>
+      <c r="T104" s="162"/>
+      <c r="U104" s="141"/>
+      <c r="V104" s="139"/>
+      <c r="W104" s="162"/>
+      <c r="X104" s="77"/>
       <c r="Y104" s="65"/>
       <c r="Z104" s="65"/>
       <c r="AA104" s="65"/>
@@ -6671,29 +6633,29 @@
     </row>
     <row r="105" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="59"/>
-      <c r="B105" s="186"/>
-      <c r="C105" s="78"/>
-      <c r="D105" s="79"/>
-      <c r="E105" s="113"/>
-      <c r="F105" s="81"/>
-      <c r="G105" s="79"/>
-      <c r="H105" s="113"/>
-      <c r="I105" s="81"/>
-      <c r="J105" s="79"/>
-      <c r="K105" s="113"/>
-      <c r="L105" s="81"/>
-      <c r="M105" s="79"/>
-      <c r="N105" s="113"/>
-      <c r="O105" s="81"/>
-      <c r="P105" s="79"/>
-      <c r="Q105" s="113"/>
-      <c r="R105" s="81"/>
-      <c r="S105" s="79"/>
-      <c r="T105" s="113"/>
-      <c r="U105" s="81"/>
-      <c r="V105" s="79"/>
-      <c r="W105" s="80"/>
-      <c r="X105" s="119"/>
+      <c r="B105" s="113"/>
+      <c r="C105" s="138"/>
+      <c r="D105" s="139"/>
+      <c r="E105" s="162"/>
+      <c r="F105" s="141"/>
+      <c r="G105" s="139"/>
+      <c r="H105" s="162"/>
+      <c r="I105" s="141"/>
+      <c r="J105" s="139"/>
+      <c r="K105" s="162"/>
+      <c r="L105" s="141"/>
+      <c r="M105" s="139"/>
+      <c r="N105" s="162"/>
+      <c r="O105" s="141"/>
+      <c r="P105" s="139"/>
+      <c r="Q105" s="162"/>
+      <c r="R105" s="141"/>
+      <c r="S105" s="139"/>
+      <c r="T105" s="162"/>
+      <c r="U105" s="141"/>
+      <c r="V105" s="139"/>
+      <c r="W105" s="140"/>
+      <c r="X105" s="77"/>
       <c r="Y105" s="65"/>
       <c r="Z105" s="65"/>
       <c r="AA105" s="65"/>
@@ -6703,29 +6665,29 @@
     </row>
     <row r="106" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="59"/>
-      <c r="B106" s="186"/>
-      <c r="C106" s="78"/>
-      <c r="D106" s="79"/>
-      <c r="E106" s="113"/>
-      <c r="F106" s="81"/>
-      <c r="G106" s="79"/>
-      <c r="H106" s="113"/>
-      <c r="I106" s="81"/>
-      <c r="J106" s="79"/>
-      <c r="K106" s="113"/>
-      <c r="L106" s="81"/>
-      <c r="M106" s="79"/>
-      <c r="N106" s="113"/>
-      <c r="O106" s="81"/>
-      <c r="P106" s="79"/>
-      <c r="Q106" s="113"/>
-      <c r="R106" s="81"/>
-      <c r="S106" s="79"/>
-      <c r="T106" s="113"/>
-      <c r="U106" s="81"/>
-      <c r="V106" s="79"/>
-      <c r="W106" s="80"/>
-      <c r="X106" s="119"/>
+      <c r="B106" s="113"/>
+      <c r="C106" s="138"/>
+      <c r="D106" s="139"/>
+      <c r="E106" s="162"/>
+      <c r="F106" s="141"/>
+      <c r="G106" s="139"/>
+      <c r="H106" s="162"/>
+      <c r="I106" s="141"/>
+      <c r="J106" s="139"/>
+      <c r="K106" s="162"/>
+      <c r="L106" s="141"/>
+      <c r="M106" s="139"/>
+      <c r="N106" s="162"/>
+      <c r="O106" s="141"/>
+      <c r="P106" s="139"/>
+      <c r="Q106" s="162"/>
+      <c r="R106" s="141"/>
+      <c r="S106" s="139"/>
+      <c r="T106" s="162"/>
+      <c r="U106" s="141"/>
+      <c r="V106" s="139"/>
+      <c r="W106" s="140"/>
+      <c r="X106" s="77"/>
       <c r="Y106" s="65"/>
       <c r="Z106" s="65"/>
       <c r="AA106" s="65"/>
@@ -6734,62 +6696,62 @@
       <c r="AD106" s="66"/>
     </row>
     <row r="107" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="125"/>
-      <c r="B107" s="186"/>
-      <c r="C107" s="78"/>
-      <c r="D107" s="126"/>
-      <c r="E107" s="113"/>
-      <c r="F107" s="127"/>
-      <c r="G107" s="126"/>
-      <c r="H107" s="113"/>
-      <c r="I107" s="81"/>
-      <c r="J107" s="126"/>
-      <c r="K107" s="113"/>
-      <c r="L107" s="127"/>
-      <c r="M107" s="126"/>
-      <c r="N107" s="113"/>
-      <c r="O107" s="81"/>
-      <c r="P107" s="126"/>
-      <c r="Q107" s="113"/>
-      <c r="R107" s="81"/>
-      <c r="S107" s="126"/>
-      <c r="T107" s="113"/>
-      <c r="U107" s="81"/>
-      <c r="V107" s="126"/>
-      <c r="W107" s="113"/>
-      <c r="X107" s="149"/>
-      <c r="Y107" s="129"/>
-      <c r="Z107" s="129"/>
-      <c r="AA107" s="129"/>
-      <c r="AB107" s="129"/>
-      <c r="AC107" s="129"/>
-      <c r="AD107" s="129"/>
+      <c r="A107" s="79"/>
+      <c r="B107" s="113"/>
+      <c r="C107" s="138"/>
+      <c r="D107" s="165"/>
+      <c r="E107" s="162"/>
+      <c r="F107" s="166"/>
+      <c r="G107" s="165"/>
+      <c r="H107" s="162"/>
+      <c r="I107" s="141"/>
+      <c r="J107" s="165"/>
+      <c r="K107" s="162"/>
+      <c r="L107" s="166"/>
+      <c r="M107" s="165"/>
+      <c r="N107" s="162"/>
+      <c r="O107" s="141"/>
+      <c r="P107" s="165"/>
+      <c r="Q107" s="162"/>
+      <c r="R107" s="141"/>
+      <c r="S107" s="165"/>
+      <c r="T107" s="162"/>
+      <c r="U107" s="141"/>
+      <c r="V107" s="165"/>
+      <c r="W107" s="162"/>
+      <c r="X107" s="86"/>
+      <c r="Y107" s="81"/>
+      <c r="Z107" s="81"/>
+      <c r="AA107" s="81"/>
+      <c r="AB107" s="81"/>
+      <c r="AC107" s="81"/>
+      <c r="AD107" s="81"/>
     </row>
     <row r="108" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
-      <c r="B108" s="90"/>
-      <c r="C108" s="154"/>
-      <c r="D108" s="92"/>
-      <c r="E108" s="131"/>
-      <c r="F108" s="95"/>
-      <c r="G108" s="92"/>
-      <c r="H108" s="131"/>
-      <c r="I108" s="95"/>
-      <c r="J108" s="92"/>
-      <c r="K108" s="131"/>
-      <c r="L108" s="95"/>
-      <c r="M108" s="92"/>
-      <c r="N108" s="131"/>
-      <c r="O108" s="95"/>
-      <c r="P108" s="92"/>
-      <c r="Q108" s="131"/>
-      <c r="R108" s="95"/>
-      <c r="S108" s="92"/>
-      <c r="T108" s="131"/>
-      <c r="U108" s="95"/>
-      <c r="V108" s="92"/>
-      <c r="W108" s="131"/>
-      <c r="X108" s="150"/>
+      <c r="B108" s="71"/>
+      <c r="C108" s="167"/>
+      <c r="D108" s="148"/>
+      <c r="E108" s="168"/>
+      <c r="F108" s="151"/>
+      <c r="G108" s="148"/>
+      <c r="H108" s="168"/>
+      <c r="I108" s="151"/>
+      <c r="J108" s="148"/>
+      <c r="K108" s="168"/>
+      <c r="L108" s="151"/>
+      <c r="M108" s="148"/>
+      <c r="N108" s="168"/>
+      <c r="O108" s="151"/>
+      <c r="P108" s="148"/>
+      <c r="Q108" s="168"/>
+      <c r="R108" s="151"/>
+      <c r="S108" s="148"/>
+      <c r="T108" s="168"/>
+      <c r="U108" s="151"/>
+      <c r="V108" s="148"/>
+      <c r="W108" s="168"/>
+      <c r="X108" s="87"/>
       <c r="Y108" s="2"/>
       <c r="Z108" s="2"/>
       <c r="AA108" s="2"/>
@@ -6799,31 +6761,31 @@
     </row>
     <row r="109" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
-      <c r="B109" s="133" t="s">
+      <c r="B109" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="C109" s="134"/>
-      <c r="D109" s="105"/>
-      <c r="E109" s="106"/>
-      <c r="F109" s="135"/>
-      <c r="G109" s="105"/>
-      <c r="H109" s="106"/>
-      <c r="I109" s="135"/>
-      <c r="J109" s="105"/>
-      <c r="K109" s="106"/>
-      <c r="L109" s="135"/>
-      <c r="M109" s="105"/>
-      <c r="N109" s="106"/>
-      <c r="O109" s="135"/>
-      <c r="P109" s="105"/>
-      <c r="Q109" s="106"/>
-      <c r="R109" s="135"/>
-      <c r="S109" s="105"/>
-      <c r="T109" s="106"/>
-      <c r="U109" s="135"/>
-      <c r="V109" s="105"/>
-      <c r="W109" s="106"/>
-      <c r="X109" s="150"/>
+      <c r="C109" s="169"/>
+      <c r="D109" s="157"/>
+      <c r="E109" s="158"/>
+      <c r="F109" s="170"/>
+      <c r="G109" s="157"/>
+      <c r="H109" s="158"/>
+      <c r="I109" s="170"/>
+      <c r="J109" s="157"/>
+      <c r="K109" s="158"/>
+      <c r="L109" s="170"/>
+      <c r="M109" s="157"/>
+      <c r="N109" s="158"/>
+      <c r="O109" s="170"/>
+      <c r="P109" s="157"/>
+      <c r="Q109" s="158"/>
+      <c r="R109" s="170"/>
+      <c r="S109" s="157"/>
+      <c r="T109" s="158"/>
+      <c r="U109" s="170"/>
+      <c r="V109" s="157"/>
+      <c r="W109" s="158"/>
+      <c r="X109" s="87"/>
       <c r="Y109" s="2"/>
       <c r="Z109" s="2"/>
       <c r="AA109" s="2"/>
@@ -6833,31 +6795,31 @@
     </row>
     <row r="110" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
-      <c r="B110" s="139" t="s">
+      <c r="B110" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="C110" s="155"/>
-      <c r="D110" s="141"/>
-      <c r="E110" s="142"/>
-      <c r="F110" s="144"/>
-      <c r="G110" s="141"/>
-      <c r="H110" s="142"/>
-      <c r="I110" s="144"/>
-      <c r="J110" s="141"/>
-      <c r="K110" s="142"/>
-      <c r="L110" s="144"/>
-      <c r="M110" s="141"/>
-      <c r="N110" s="142"/>
-      <c r="O110" s="144"/>
-      <c r="P110" s="141"/>
-      <c r="Q110" s="142"/>
-      <c r="R110" s="144"/>
-      <c r="S110" s="141"/>
-      <c r="T110" s="142"/>
-      <c r="U110" s="144"/>
-      <c r="V110" s="141"/>
-      <c r="W110" s="142"/>
-      <c r="X110" s="150"/>
+      <c r="C110" s="171"/>
+      <c r="D110" s="172"/>
+      <c r="E110" s="173"/>
+      <c r="F110" s="174"/>
+      <c r="G110" s="172"/>
+      <c r="H110" s="173"/>
+      <c r="I110" s="174"/>
+      <c r="J110" s="172"/>
+      <c r="K110" s="173"/>
+      <c r="L110" s="174"/>
+      <c r="M110" s="172"/>
+      <c r="N110" s="173"/>
+      <c r="O110" s="174"/>
+      <c r="P110" s="172"/>
+      <c r="Q110" s="173"/>
+      <c r="R110" s="174"/>
+      <c r="S110" s="172"/>
+      <c r="T110" s="173"/>
+      <c r="U110" s="174"/>
+      <c r="V110" s="172"/>
+      <c r="W110" s="173"/>
+      <c r="X110" s="87"/>
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
       <c r="AA110" s="2"/>
@@ -6867,29 +6829,29 @@
     </row>
     <row r="111" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4"/>
-      <c r="B111" s="147"/>
-      <c r="C111" s="174"/>
-      <c r="D111" s="175"/>
-      <c r="E111" s="176"/>
-      <c r="F111" s="177"/>
-      <c r="G111" s="175"/>
-      <c r="H111" s="176"/>
-      <c r="I111" s="177"/>
-      <c r="J111" s="175"/>
-      <c r="K111" s="176"/>
-      <c r="L111" s="177"/>
-      <c r="M111" s="175"/>
-      <c r="N111" s="176"/>
-      <c r="O111" s="177"/>
-      <c r="P111" s="175"/>
-      <c r="Q111" s="176"/>
-      <c r="R111" s="177"/>
-      <c r="S111" s="175"/>
-      <c r="T111" s="176"/>
-      <c r="U111" s="179"/>
-      <c r="V111" s="180"/>
-      <c r="W111" s="181"/>
-      <c r="X111" s="150"/>
+      <c r="B111" s="84"/>
+      <c r="C111" s="118"/>
+      <c r="D111" s="116"/>
+      <c r="E111" s="117"/>
+      <c r="F111" s="115"/>
+      <c r="G111" s="116"/>
+      <c r="H111" s="117"/>
+      <c r="I111" s="115"/>
+      <c r="J111" s="116"/>
+      <c r="K111" s="117"/>
+      <c r="L111" s="115"/>
+      <c r="M111" s="116"/>
+      <c r="N111" s="117"/>
+      <c r="O111" s="115"/>
+      <c r="P111" s="116"/>
+      <c r="Q111" s="117"/>
+      <c r="R111" s="115"/>
+      <c r="S111" s="116"/>
+      <c r="T111" s="117"/>
+      <c r="U111" s="109"/>
+      <c r="V111" s="110"/>
+      <c r="W111" s="111"/>
+      <c r="X111" s="87"/>
       <c r="Y111" s="2"/>
       <c r="Z111" s="2"/>
       <c r="AA111" s="2"/>
@@ -6900,7 +6862,7 @@
     <row r="112" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4"/>
       <c r="B112" s="9"/>
-      <c r="C112" s="148" t="s">
+      <c r="C112" s="85" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="15" t="s">
@@ -6963,7 +6925,7 @@
       <c r="W112" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="X112" s="150"/>
+      <c r="X112" s="87"/>
       <c r="Y112" s="2"/>
       <c r="Z112" s="2"/>
       <c r="AA112" s="2"/>
@@ -6995,7 +6957,7 @@
       <c r="U113" s="23"/>
       <c r="V113" s="24"/>
       <c r="W113" s="25"/>
-      <c r="X113" s="150"/>
+      <c r="X113" s="87"/>
       <c r="Y113" s="2"/>
       <c r="Z113" s="2"/>
       <c r="AA113" s="2"/>
@@ -7027,7 +6989,7 @@
       <c r="U114" s="32"/>
       <c r="V114" s="33"/>
       <c r="W114" s="34"/>
-      <c r="X114" s="150"/>
+      <c r="X114" s="87"/>
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
       <c r="AA114" s="2"/>
@@ -7059,7 +7021,7 @@
       <c r="U115" s="32"/>
       <c r="V115" s="33"/>
       <c r="W115" s="34"/>
-      <c r="X115" s="150"/>
+      <c r="X115" s="87"/>
       <c r="Y115" s="2"/>
       <c r="Z115" s="2"/>
       <c r="AA115" s="2"/>
@@ -7091,7 +7053,7 @@
       <c r="U116" s="32"/>
       <c r="V116" s="33"/>
       <c r="W116" s="34"/>
-      <c r="X116" s="150"/>
+      <c r="X116" s="87"/>
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
       <c r="AA116" s="2"/>
@@ -7123,7 +7085,7 @@
       <c r="U117" s="32"/>
       <c r="V117" s="33"/>
       <c r="W117" s="34"/>
-      <c r="X117" s="150"/>
+      <c r="X117" s="87"/>
       <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
       <c r="AA117" s="2"/>
@@ -7155,7 +7117,7 @@
       <c r="U118" s="32"/>
       <c r="V118" s="33"/>
       <c r="W118" s="34"/>
-      <c r="X118" s="150"/>
+      <c r="X118" s="87"/>
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
       <c r="AA118" s="2"/>
@@ -7187,7 +7149,7 @@
       <c r="U119" s="32"/>
       <c r="V119" s="33"/>
       <c r="W119" s="34"/>
-      <c r="X119" s="150"/>
+      <c r="X119" s="87"/>
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
       <c r="AA119" s="2"/>
@@ -7219,7 +7181,7 @@
       <c r="U120" s="32"/>
       <c r="V120" s="33"/>
       <c r="W120" s="34"/>
-      <c r="X120" s="150"/>
+      <c r="X120" s="87"/>
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
       <c r="AA120" s="2"/>
@@ -7251,7 +7213,7 @@
       <c r="U121" s="32"/>
       <c r="V121" s="33"/>
       <c r="W121" s="34"/>
-      <c r="X121" s="150"/>
+      <c r="X121" s="87"/>
       <c r="Y121" s="2"/>
       <c r="Z121" s="2"/>
       <c r="AA121" s="2"/>
@@ -7283,7 +7245,7 @@
       <c r="U122" s="32"/>
       <c r="V122" s="33"/>
       <c r="W122" s="34"/>
-      <c r="X122" s="150"/>
+      <c r="X122" s="87"/>
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
       <c r="AA122" s="2"/>
@@ -7315,7 +7277,7 @@
       <c r="U123" s="32"/>
       <c r="V123" s="33"/>
       <c r="W123" s="34"/>
-      <c r="X123" s="150"/>
+      <c r="X123" s="87"/>
       <c r="Y123" s="2"/>
       <c r="Z123" s="2"/>
       <c r="AA123" s="2"/>
@@ -7328,7 +7290,7 @@
       <c r="B124" s="26"/>
       <c r="C124" s="37"/>
       <c r="D124" s="38"/>
-      <c r="E124" s="151"/>
+      <c r="E124" s="88"/>
       <c r="F124" s="40"/>
       <c r="G124" s="38"/>
       <c r="H124" s="41"/>
@@ -7347,7 +7309,7 @@
       <c r="U124" s="43"/>
       <c r="V124" s="44"/>
       <c r="W124" s="45"/>
-      <c r="X124" s="150"/>
+      <c r="X124" s="87"/>
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
       <c r="AA124" s="2"/>
@@ -7453,7 +7415,7 @@
       <c r="W126" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="X126" s="119"/>
+      <c r="X126" s="77"/>
       <c r="Y126" s="65"/>
       <c r="Z126" s="65"/>
       <c r="AA126" s="65"/>
@@ -7463,35 +7425,35 @@
     </row>
     <row r="127" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="59"/>
-      <c r="B127" s="185" t="s">
+      <c r="B127" s="176" t="s">
         <v>14</v>
       </c>
-      <c r="C127" s="67"/>
-      <c r="D127" s="68"/>
-      <c r="E127" s="69"/>
-      <c r="F127" s="70"/>
-      <c r="G127" s="190"/>
-      <c r="H127" s="69"/>
-      <c r="I127" s="70"/>
-      <c r="J127" s="71"/>
-      <c r="K127" s="69"/>
-      <c r="L127" s="70"/>
-      <c r="M127" s="68"/>
-      <c r="N127" s="69"/>
-      <c r="O127" s="70"/>
-      <c r="P127" s="72"/>
-      <c r="Q127" s="69"/>
-      <c r="R127" s="70"/>
-      <c r="S127" s="68"/>
-      <c r="T127" s="69"/>
-      <c r="U127" s="70"/>
-      <c r="V127" s="68"/>
-      <c r="W127" s="69"/>
-      <c r="X127" s="119"/>
-      <c r="Y127" s="75" t="s">
+      <c r="C127" s="131"/>
+      <c r="D127" s="132"/>
+      <c r="E127" s="133"/>
+      <c r="F127" s="134"/>
+      <c r="G127" s="135"/>
+      <c r="H127" s="133"/>
+      <c r="I127" s="134"/>
+      <c r="J127" s="136"/>
+      <c r="K127" s="133"/>
+      <c r="L127" s="134"/>
+      <c r="M127" s="132"/>
+      <c r="N127" s="133"/>
+      <c r="O127" s="134"/>
+      <c r="P127" s="137"/>
+      <c r="Q127" s="133"/>
+      <c r="R127" s="134"/>
+      <c r="S127" s="132"/>
+      <c r="T127" s="133"/>
+      <c r="U127" s="134"/>
+      <c r="V127" s="132"/>
+      <c r="W127" s="133"/>
+      <c r="X127" s="77"/>
+      <c r="Y127" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="Z127" s="76">
+      <c r="Z127" s="68">
         <f>COUNTIF(C127:W146,Y127)</f>
         <v>0</v>
       </c>
@@ -7502,33 +7464,33 @@
     </row>
     <row r="128" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="59"/>
-      <c r="B128" s="186"/>
-      <c r="C128" s="78"/>
-      <c r="D128" s="79"/>
-      <c r="E128" s="80"/>
-      <c r="F128" s="81"/>
-      <c r="G128" s="191"/>
-      <c r="H128" s="80"/>
-      <c r="I128" s="81"/>
-      <c r="J128" s="79"/>
-      <c r="K128" s="80"/>
-      <c r="L128" s="82"/>
-      <c r="M128" s="79"/>
-      <c r="N128" s="83"/>
-      <c r="O128" s="81"/>
-      <c r="P128" s="84"/>
-      <c r="Q128" s="80"/>
-      <c r="R128" s="82"/>
-      <c r="S128" s="79"/>
-      <c r="T128" s="80"/>
-      <c r="U128" s="81"/>
-      <c r="V128" s="79"/>
-      <c r="W128" s="83"/>
-      <c r="X128" s="119"/>
-      <c r="Y128" s="87" t="s">
+      <c r="B128" s="177"/>
+      <c r="C128" s="138"/>
+      <c r="D128" s="139"/>
+      <c r="E128" s="140"/>
+      <c r="F128" s="141"/>
+      <c r="G128" s="142"/>
+      <c r="H128" s="140"/>
+      <c r="I128" s="141"/>
+      <c r="J128" s="139"/>
+      <c r="K128" s="140"/>
+      <c r="L128" s="143"/>
+      <c r="M128" s="139"/>
+      <c r="N128" s="144"/>
+      <c r="O128" s="141"/>
+      <c r="P128" s="145"/>
+      <c r="Q128" s="140"/>
+      <c r="R128" s="143"/>
+      <c r="S128" s="139"/>
+      <c r="T128" s="140"/>
+      <c r="U128" s="141"/>
+      <c r="V128" s="139"/>
+      <c r="W128" s="144"/>
+      <c r="X128" s="77"/>
+      <c r="Y128" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="Z128" s="88">
+      <c r="Z128" s="70">
         <f>COUNTIF(C127:W146,Y128)</f>
         <v>0</v>
       </c>
@@ -7539,33 +7501,33 @@
     </row>
     <row r="129" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="59"/>
-      <c r="B129" s="186"/>
-      <c r="C129" s="78"/>
-      <c r="D129" s="79"/>
-      <c r="E129" s="80"/>
-      <c r="F129" s="81"/>
-      <c r="G129" s="191"/>
-      <c r="H129" s="80"/>
-      <c r="I129" s="81"/>
-      <c r="J129" s="79"/>
-      <c r="K129" s="80"/>
-      <c r="L129" s="82"/>
-      <c r="M129" s="79"/>
-      <c r="N129" s="83"/>
-      <c r="O129" s="81"/>
-      <c r="P129" s="84"/>
-      <c r="Q129" s="83"/>
-      <c r="R129" s="81"/>
-      <c r="S129" s="79"/>
-      <c r="T129" s="83"/>
-      <c r="U129" s="81"/>
-      <c r="V129" s="79"/>
-      <c r="W129" s="83"/>
-      <c r="X129" s="119"/>
-      <c r="Y129" s="87" t="s">
+      <c r="B129" s="177"/>
+      <c r="C129" s="138"/>
+      <c r="D129" s="139"/>
+      <c r="E129" s="140"/>
+      <c r="F129" s="141"/>
+      <c r="G129" s="142"/>
+      <c r="H129" s="140"/>
+      <c r="I129" s="141"/>
+      <c r="J129" s="139"/>
+      <c r="K129" s="140"/>
+      <c r="L129" s="143"/>
+      <c r="M129" s="139"/>
+      <c r="N129" s="144"/>
+      <c r="O129" s="141"/>
+      <c r="P129" s="145"/>
+      <c r="Q129" s="144"/>
+      <c r="R129" s="141"/>
+      <c r="S129" s="139"/>
+      <c r="T129" s="144"/>
+      <c r="U129" s="141"/>
+      <c r="V129" s="139"/>
+      <c r="W129" s="144"/>
+      <c r="X129" s="77"/>
+      <c r="Y129" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="Z129" s="88">
+      <c r="Z129" s="70">
         <f>COUNTIF(C127:W146,Y129)</f>
         <v>0</v>
       </c>
@@ -7576,33 +7538,33 @@
     </row>
     <row r="130" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="59"/>
-      <c r="B130" s="186"/>
-      <c r="C130" s="89"/>
-      <c r="D130" s="79"/>
-      <c r="E130" s="83"/>
-      <c r="F130" s="82"/>
-      <c r="G130" s="79"/>
-      <c r="H130" s="83"/>
-      <c r="I130" s="82"/>
-      <c r="J130" s="79"/>
-      <c r="K130" s="83"/>
-      <c r="L130" s="82"/>
-      <c r="M130" s="79"/>
-      <c r="N130" s="83"/>
-      <c r="O130" s="82"/>
-      <c r="P130" s="84"/>
-      <c r="Q130" s="83"/>
-      <c r="R130" s="82"/>
-      <c r="S130" s="79"/>
-      <c r="T130" s="83"/>
-      <c r="U130" s="81"/>
-      <c r="V130" s="79"/>
-      <c r="W130" s="83"/>
-      <c r="X130" s="119"/>
-      <c r="Y130" s="87" t="s">
+      <c r="B130" s="177"/>
+      <c r="C130" s="146"/>
+      <c r="D130" s="139"/>
+      <c r="E130" s="144"/>
+      <c r="F130" s="143"/>
+      <c r="G130" s="139"/>
+      <c r="H130" s="144"/>
+      <c r="I130" s="143"/>
+      <c r="J130" s="139"/>
+      <c r="K130" s="144"/>
+      <c r="L130" s="143"/>
+      <c r="M130" s="139"/>
+      <c r="N130" s="144"/>
+      <c r="O130" s="143"/>
+      <c r="P130" s="145"/>
+      <c r="Q130" s="144"/>
+      <c r="R130" s="143"/>
+      <c r="S130" s="139"/>
+      <c r="T130" s="144"/>
+      <c r="U130" s="141"/>
+      <c r="V130" s="139"/>
+      <c r="W130" s="144"/>
+      <c r="X130" s="77"/>
+      <c r="Y130" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="Z130" s="88">
+      <c r="Z130" s="70">
         <f>COUNTIF(C127:W146,Y130)</f>
         <v>0</v>
       </c>
@@ -7613,33 +7575,33 @@
     </row>
     <row r="131" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="59"/>
-      <c r="B131" s="189"/>
-      <c r="C131" s="91"/>
-      <c r="D131" s="92"/>
-      <c r="E131" s="93"/>
-      <c r="F131" s="94"/>
-      <c r="G131" s="92"/>
-      <c r="H131" s="93"/>
-      <c r="I131" s="95"/>
-      <c r="J131" s="92"/>
-      <c r="K131" s="93"/>
-      <c r="L131" s="96"/>
-      <c r="M131" s="92"/>
-      <c r="N131" s="93"/>
-      <c r="O131" s="94"/>
-      <c r="P131" s="97"/>
-      <c r="Q131" s="93"/>
-      <c r="R131" s="95"/>
-      <c r="S131" s="92"/>
-      <c r="T131" s="93"/>
-      <c r="U131" s="95"/>
-      <c r="V131" s="92"/>
-      <c r="W131" s="93"/>
-      <c r="X131" s="119"/>
-      <c r="Y131" s="87" t="s">
+      <c r="B131" s="178"/>
+      <c r="C131" s="147"/>
+      <c r="D131" s="148"/>
+      <c r="E131" s="149"/>
+      <c r="F131" s="150"/>
+      <c r="G131" s="148"/>
+      <c r="H131" s="149"/>
+      <c r="I131" s="151"/>
+      <c r="J131" s="148"/>
+      <c r="K131" s="149"/>
+      <c r="L131" s="152"/>
+      <c r="M131" s="148"/>
+      <c r="N131" s="149"/>
+      <c r="O131" s="150"/>
+      <c r="P131" s="153"/>
+      <c r="Q131" s="149"/>
+      <c r="R131" s="151"/>
+      <c r="S131" s="148"/>
+      <c r="T131" s="149"/>
+      <c r="U131" s="151"/>
+      <c r="V131" s="148"/>
+      <c r="W131" s="149"/>
+      <c r="X131" s="77"/>
+      <c r="Y131" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="Z131" s="88">
+      <c r="Z131" s="70">
         <f>COUNTIF(C127:W146,Y131)</f>
         <v>0</v>
       </c>
@@ -7650,35 +7612,35 @@
     </row>
     <row r="132" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="59"/>
-      <c r="B132" s="101" t="s">
+      <c r="B132" s="179" t="s">
         <v>20</v>
       </c>
-      <c r="C132" s="102"/>
-      <c r="D132" s="103"/>
-      <c r="E132" s="104"/>
-      <c r="F132" s="102"/>
-      <c r="G132" s="103"/>
-      <c r="H132" s="104"/>
-      <c r="I132" s="102"/>
-      <c r="J132" s="103"/>
-      <c r="K132" s="104"/>
-      <c r="L132" s="102"/>
-      <c r="M132" s="103"/>
-      <c r="N132" s="104"/>
-      <c r="O132" s="102"/>
-      <c r="P132" s="103"/>
-      <c r="Q132" s="104"/>
-      <c r="R132" s="102"/>
-      <c r="S132" s="105"/>
-      <c r="T132" s="106"/>
-      <c r="U132" s="102"/>
-      <c r="V132" s="105"/>
-      <c r="W132" s="106"/>
-      <c r="X132" s="119"/>
-      <c r="Y132" s="87" t="s">
+      <c r="C132" s="154"/>
+      <c r="D132" s="155"/>
+      <c r="E132" s="156"/>
+      <c r="F132" s="154"/>
+      <c r="G132" s="155"/>
+      <c r="H132" s="156"/>
+      <c r="I132" s="154"/>
+      <c r="J132" s="155"/>
+      <c r="K132" s="156"/>
+      <c r="L132" s="154"/>
+      <c r="M132" s="155"/>
+      <c r="N132" s="156"/>
+      <c r="O132" s="154"/>
+      <c r="P132" s="155"/>
+      <c r="Q132" s="156"/>
+      <c r="R132" s="154"/>
+      <c r="S132" s="157"/>
+      <c r="T132" s="158"/>
+      <c r="U132" s="154"/>
+      <c r="V132" s="157"/>
+      <c r="W132" s="158"/>
+      <c r="X132" s="77"/>
+      <c r="Y132" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="Z132" s="88">
+      <c r="Z132" s="70">
         <f>COUNTIF(C127:W146,Y132)</f>
         <v>0</v>
       </c>
@@ -7689,35 +7651,35 @@
     </row>
     <row r="133" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="59"/>
-      <c r="B133" s="185" t="s">
+      <c r="B133" s="176" t="s">
         <v>29</v>
       </c>
-      <c r="C133" s="67"/>
-      <c r="D133" s="108"/>
-      <c r="E133" s="109"/>
-      <c r="F133" s="110"/>
-      <c r="G133" s="68"/>
-      <c r="H133" s="109"/>
-      <c r="I133" s="110"/>
-      <c r="J133" s="68"/>
-      <c r="K133" s="109"/>
-      <c r="L133" s="110"/>
-      <c r="M133" s="68"/>
-      <c r="N133" s="109"/>
-      <c r="O133" s="110"/>
-      <c r="P133" s="68"/>
-      <c r="Q133" s="109"/>
-      <c r="R133" s="110"/>
-      <c r="S133" s="68"/>
-      <c r="T133" s="109"/>
-      <c r="U133" s="110"/>
-      <c r="V133" s="68"/>
-      <c r="W133" s="152"/>
-      <c r="X133" s="119"/>
-      <c r="Y133" s="87" t="s">
+      <c r="C133" s="131"/>
+      <c r="D133" s="159"/>
+      <c r="E133" s="160"/>
+      <c r="F133" s="161"/>
+      <c r="G133" s="132"/>
+      <c r="H133" s="160"/>
+      <c r="I133" s="161"/>
+      <c r="J133" s="132"/>
+      <c r="K133" s="160"/>
+      <c r="L133" s="161"/>
+      <c r="M133" s="132"/>
+      <c r="N133" s="160"/>
+      <c r="O133" s="161"/>
+      <c r="P133" s="132"/>
+      <c r="Q133" s="160"/>
+      <c r="R133" s="161"/>
+      <c r="S133" s="132"/>
+      <c r="T133" s="160"/>
+      <c r="U133" s="161"/>
+      <c r="V133" s="132"/>
+      <c r="W133" s="175"/>
+      <c r="X133" s="77"/>
+      <c r="Y133" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="Z133" s="88">
+      <c r="Z133" s="70">
         <f>COUNTIF(C127:W146,Y133)</f>
         <v>0</v>
       </c>
@@ -7728,33 +7690,33 @@
     </row>
     <row r="134" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="59"/>
-      <c r="B134" s="186"/>
-      <c r="C134" s="78"/>
-      <c r="D134" s="79"/>
-      <c r="E134" s="113"/>
-      <c r="F134" s="81"/>
-      <c r="G134" s="79"/>
-      <c r="H134" s="113"/>
-      <c r="I134" s="81"/>
-      <c r="J134" s="114"/>
-      <c r="K134" s="113"/>
-      <c r="L134" s="81"/>
-      <c r="M134" s="79"/>
-      <c r="N134" s="113"/>
-      <c r="O134" s="81"/>
-      <c r="P134" s="79"/>
-      <c r="Q134" s="113"/>
-      <c r="R134" s="81"/>
-      <c r="S134" s="114"/>
-      <c r="T134" s="113"/>
-      <c r="U134" s="81"/>
-      <c r="V134" s="79"/>
-      <c r="W134" s="113"/>
-      <c r="X134" s="119"/>
-      <c r="Y134" s="87" t="s">
+      <c r="B134" s="177"/>
+      <c r="C134" s="138"/>
+      <c r="D134" s="139"/>
+      <c r="E134" s="162"/>
+      <c r="F134" s="141"/>
+      <c r="G134" s="139"/>
+      <c r="H134" s="162"/>
+      <c r="I134" s="141"/>
+      <c r="J134" s="163"/>
+      <c r="K134" s="162"/>
+      <c r="L134" s="141"/>
+      <c r="M134" s="139"/>
+      <c r="N134" s="162"/>
+      <c r="O134" s="141"/>
+      <c r="P134" s="139"/>
+      <c r="Q134" s="162"/>
+      <c r="R134" s="141"/>
+      <c r="S134" s="163"/>
+      <c r="T134" s="162"/>
+      <c r="U134" s="141"/>
+      <c r="V134" s="139"/>
+      <c r="W134" s="162"/>
+      <c r="X134" s="77"/>
+      <c r="Y134" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="Z134" s="88">
+      <c r="Z134" s="70">
         <f>COUNTIF(C127:W146,Y134)</f>
         <v>0</v>
       </c>
@@ -7765,33 +7727,33 @@
     </row>
     <row r="135" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="59"/>
-      <c r="B135" s="186"/>
-      <c r="C135" s="78"/>
-      <c r="D135" s="79"/>
-      <c r="E135" s="113"/>
-      <c r="F135" s="81"/>
-      <c r="G135" s="79"/>
-      <c r="H135" s="113"/>
-      <c r="I135" s="81"/>
-      <c r="J135" s="114"/>
-      <c r="K135" s="113"/>
-      <c r="L135" s="81"/>
-      <c r="M135" s="79"/>
-      <c r="N135" s="113"/>
-      <c r="O135" s="81"/>
-      <c r="P135" s="79"/>
-      <c r="Q135" s="113"/>
-      <c r="R135" s="81"/>
-      <c r="S135" s="114"/>
-      <c r="T135" s="113"/>
-      <c r="U135" s="81"/>
-      <c r="V135" s="79"/>
-      <c r="W135" s="113"/>
-      <c r="X135" s="119"/>
-      <c r="Y135" s="87" t="s">
+      <c r="B135" s="177"/>
+      <c r="C135" s="138"/>
+      <c r="D135" s="139"/>
+      <c r="E135" s="162"/>
+      <c r="F135" s="141"/>
+      <c r="G135" s="139"/>
+      <c r="H135" s="162"/>
+      <c r="I135" s="141"/>
+      <c r="J135" s="163"/>
+      <c r="K135" s="162"/>
+      <c r="L135" s="141"/>
+      <c r="M135" s="139"/>
+      <c r="N135" s="162"/>
+      <c r="O135" s="141"/>
+      <c r="P135" s="139"/>
+      <c r="Q135" s="162"/>
+      <c r="R135" s="141"/>
+      <c r="S135" s="163"/>
+      <c r="T135" s="162"/>
+      <c r="U135" s="141"/>
+      <c r="V135" s="139"/>
+      <c r="W135" s="162"/>
+      <c r="X135" s="77"/>
+      <c r="Y135" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="Z135" s="88">
+      <c r="Z135" s="70">
         <f>COUNTIF(C127:W146,Y135)</f>
         <v>0</v>
       </c>
@@ -7802,33 +7764,33 @@
     </row>
     <row r="136" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="59"/>
-      <c r="B136" s="186"/>
-      <c r="C136" s="78"/>
-      <c r="D136" s="79"/>
-      <c r="E136" s="80"/>
-      <c r="F136" s="81"/>
-      <c r="G136" s="114"/>
-      <c r="H136" s="80"/>
-      <c r="I136" s="81"/>
-      <c r="J136" s="79"/>
-      <c r="K136" s="80"/>
-      <c r="L136" s="81"/>
-      <c r="M136" s="79"/>
-      <c r="N136" s="80"/>
-      <c r="O136" s="81"/>
-      <c r="P136" s="79"/>
-      <c r="Q136" s="80"/>
-      <c r="R136" s="81"/>
-      <c r="S136" s="79"/>
-      <c r="T136" s="80"/>
-      <c r="U136" s="81"/>
-      <c r="V136" s="79"/>
-      <c r="W136" s="113"/>
-      <c r="X136" s="119"/>
-      <c r="Y136" s="153" t="s">
+      <c r="B136" s="177"/>
+      <c r="C136" s="138"/>
+      <c r="D136" s="139"/>
+      <c r="E136" s="140"/>
+      <c r="F136" s="141"/>
+      <c r="G136" s="163"/>
+      <c r="H136" s="140"/>
+      <c r="I136" s="141"/>
+      <c r="J136" s="139"/>
+      <c r="K136" s="140"/>
+      <c r="L136" s="141"/>
+      <c r="M136" s="139"/>
+      <c r="N136" s="140"/>
+      <c r="O136" s="141"/>
+      <c r="P136" s="139"/>
+      <c r="Q136" s="140"/>
+      <c r="R136" s="141"/>
+      <c r="S136" s="139"/>
+      <c r="T136" s="140"/>
+      <c r="U136" s="141"/>
+      <c r="V136" s="139"/>
+      <c r="W136" s="162"/>
+      <c r="X136" s="77"/>
+      <c r="Y136" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="Z136" s="117">
+      <c r="Z136" s="76">
         <f>COUNTIF(C127:W146,Y136)</f>
         <v>0</v>
       </c>
@@ -7839,29 +7801,29 @@
     </row>
     <row r="137" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="59"/>
-      <c r="B137" s="186"/>
-      <c r="C137" s="89"/>
-      <c r="D137" s="79"/>
-      <c r="E137" s="113"/>
-      <c r="F137" s="82"/>
-      <c r="G137" s="79"/>
-      <c r="H137" s="113"/>
-      <c r="I137" s="82"/>
-      <c r="J137" s="114"/>
-      <c r="K137" s="113"/>
-      <c r="L137" s="82"/>
-      <c r="M137" s="79"/>
-      <c r="N137" s="113"/>
-      <c r="O137" s="82"/>
-      <c r="P137" s="79"/>
-      <c r="Q137" s="113"/>
-      <c r="R137" s="82"/>
-      <c r="S137" s="114"/>
-      <c r="T137" s="113"/>
-      <c r="U137" s="82"/>
-      <c r="V137" s="79"/>
-      <c r="W137" s="113"/>
-      <c r="X137" s="119"/>
+      <c r="B137" s="177"/>
+      <c r="C137" s="146"/>
+      <c r="D137" s="139"/>
+      <c r="E137" s="162"/>
+      <c r="F137" s="143"/>
+      <c r="G137" s="139"/>
+      <c r="H137" s="162"/>
+      <c r="I137" s="143"/>
+      <c r="J137" s="163"/>
+      <c r="K137" s="162"/>
+      <c r="L137" s="143"/>
+      <c r="M137" s="139"/>
+      <c r="N137" s="162"/>
+      <c r="O137" s="143"/>
+      <c r="P137" s="139"/>
+      <c r="Q137" s="162"/>
+      <c r="R137" s="143"/>
+      <c r="S137" s="163"/>
+      <c r="T137" s="162"/>
+      <c r="U137" s="143"/>
+      <c r="V137" s="139"/>
+      <c r="W137" s="162"/>
+      <c r="X137" s="77"/>
       <c r="Y137" s="65"/>
       <c r="Z137" s="65"/>
       <c r="AA137" s="65"/>
@@ -7871,29 +7833,29 @@
     </row>
     <row r="138" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="59"/>
-      <c r="B138" s="186"/>
-      <c r="C138" s="89"/>
-      <c r="D138" s="79"/>
-      <c r="E138" s="113"/>
-      <c r="F138" s="82"/>
-      <c r="G138" s="79"/>
-      <c r="H138" s="113"/>
-      <c r="I138" s="82"/>
-      <c r="J138" s="114"/>
-      <c r="K138" s="113"/>
-      <c r="L138" s="82"/>
-      <c r="M138" s="79"/>
-      <c r="N138" s="113"/>
-      <c r="O138" s="82"/>
-      <c r="P138" s="79"/>
-      <c r="Q138" s="113"/>
-      <c r="R138" s="82"/>
-      <c r="S138" s="114"/>
-      <c r="T138" s="113"/>
-      <c r="U138" s="81"/>
-      <c r="V138" s="79"/>
-      <c r="W138" s="113"/>
-      <c r="X138" s="119"/>
+      <c r="B138" s="177"/>
+      <c r="C138" s="146"/>
+      <c r="D138" s="139"/>
+      <c r="E138" s="162"/>
+      <c r="F138" s="143"/>
+      <c r="G138" s="139"/>
+      <c r="H138" s="162"/>
+      <c r="I138" s="143"/>
+      <c r="J138" s="163"/>
+      <c r="K138" s="162"/>
+      <c r="L138" s="143"/>
+      <c r="M138" s="139"/>
+      <c r="N138" s="162"/>
+      <c r="O138" s="143"/>
+      <c r="P138" s="139"/>
+      <c r="Q138" s="162"/>
+      <c r="R138" s="143"/>
+      <c r="S138" s="163"/>
+      <c r="T138" s="162"/>
+      <c r="U138" s="141"/>
+      <c r="V138" s="139"/>
+      <c r="W138" s="162"/>
+      <c r="X138" s="77"/>
       <c r="Y138" s="65"/>
       <c r="Z138" s="65"/>
       <c r="AA138" s="65"/>
@@ -7903,29 +7865,29 @@
     </row>
     <row r="139" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="59"/>
-      <c r="B139" s="186"/>
-      <c r="C139" s="78"/>
-      <c r="D139" s="79"/>
-      <c r="E139" s="113"/>
-      <c r="F139" s="81"/>
-      <c r="G139" s="79"/>
-      <c r="H139" s="113"/>
-      <c r="I139" s="82"/>
-      <c r="J139" s="114"/>
-      <c r="K139" s="113"/>
-      <c r="L139" s="82"/>
-      <c r="M139" s="79"/>
-      <c r="N139" s="113"/>
-      <c r="O139" s="81"/>
-      <c r="P139" s="79"/>
-      <c r="Q139" s="113"/>
-      <c r="R139" s="81"/>
-      <c r="S139" s="114"/>
-      <c r="T139" s="113"/>
-      <c r="U139" s="82"/>
-      <c r="V139" s="79"/>
-      <c r="W139" s="113"/>
-      <c r="X139" s="119"/>
+      <c r="B139" s="177"/>
+      <c r="C139" s="138"/>
+      <c r="D139" s="139"/>
+      <c r="E139" s="162"/>
+      <c r="F139" s="141"/>
+      <c r="G139" s="139"/>
+      <c r="H139" s="162"/>
+      <c r="I139" s="143"/>
+      <c r="J139" s="163"/>
+      <c r="K139" s="162"/>
+      <c r="L139" s="143"/>
+      <c r="M139" s="139"/>
+      <c r="N139" s="162"/>
+      <c r="O139" s="141"/>
+      <c r="P139" s="139"/>
+      <c r="Q139" s="162"/>
+      <c r="R139" s="141"/>
+      <c r="S139" s="163"/>
+      <c r="T139" s="162"/>
+      <c r="U139" s="143"/>
+      <c r="V139" s="139"/>
+      <c r="W139" s="162"/>
+      <c r="X139" s="77"/>
       <c r="Y139" s="65"/>
       <c r="Z139" s="65"/>
       <c r="AA139" s="65"/>
@@ -7935,29 +7897,29 @@
     </row>
     <row r="140" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="59"/>
-      <c r="B140" s="186"/>
-      <c r="C140" s="78"/>
-      <c r="D140" s="79"/>
-      <c r="E140" s="80"/>
-      <c r="F140" s="81"/>
-      <c r="G140" s="79"/>
-      <c r="H140" s="80"/>
-      <c r="I140" s="81"/>
-      <c r="J140" s="121"/>
-      <c r="K140" s="80"/>
-      <c r="L140" s="81"/>
-      <c r="M140" s="79"/>
-      <c r="N140" s="80"/>
-      <c r="O140" s="81"/>
-      <c r="P140" s="79"/>
-      <c r="Q140" s="80"/>
-      <c r="R140" s="81"/>
-      <c r="S140" s="114"/>
-      <c r="T140" s="113"/>
-      <c r="U140" s="81"/>
-      <c r="V140" s="79"/>
-      <c r="W140" s="113"/>
-      <c r="X140" s="119"/>
+      <c r="B140" s="177"/>
+      <c r="C140" s="138"/>
+      <c r="D140" s="139"/>
+      <c r="E140" s="140"/>
+      <c r="F140" s="141"/>
+      <c r="G140" s="139"/>
+      <c r="H140" s="140"/>
+      <c r="I140" s="141"/>
+      <c r="J140" s="164"/>
+      <c r="K140" s="140"/>
+      <c r="L140" s="141"/>
+      <c r="M140" s="139"/>
+      <c r="N140" s="140"/>
+      <c r="O140" s="141"/>
+      <c r="P140" s="139"/>
+      <c r="Q140" s="140"/>
+      <c r="R140" s="141"/>
+      <c r="S140" s="163"/>
+      <c r="T140" s="162"/>
+      <c r="U140" s="141"/>
+      <c r="V140" s="139"/>
+      <c r="W140" s="162"/>
+      <c r="X140" s="77"/>
       <c r="Y140" s="65"/>
       <c r="Z140" s="65"/>
       <c r="AA140" s="65"/>
@@ -7967,29 +7929,29 @@
     </row>
     <row r="141" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="59"/>
-      <c r="B141" s="186"/>
-      <c r="C141" s="78"/>
-      <c r="D141" s="79"/>
-      <c r="E141" s="113"/>
-      <c r="F141" s="81"/>
-      <c r="G141" s="79"/>
-      <c r="H141" s="113"/>
-      <c r="I141" s="81"/>
-      <c r="J141" s="79"/>
-      <c r="K141" s="113"/>
-      <c r="L141" s="81"/>
-      <c r="M141" s="79"/>
-      <c r="N141" s="113"/>
-      <c r="O141" s="81"/>
-      <c r="P141" s="79"/>
-      <c r="Q141" s="113"/>
-      <c r="R141" s="81"/>
-      <c r="S141" s="79"/>
-      <c r="T141" s="113"/>
-      <c r="U141" s="81"/>
-      <c r="V141" s="79"/>
-      <c r="W141" s="80"/>
-      <c r="X141" s="119"/>
+      <c r="B141" s="177"/>
+      <c r="C141" s="138"/>
+      <c r="D141" s="139"/>
+      <c r="E141" s="162"/>
+      <c r="F141" s="141"/>
+      <c r="G141" s="139"/>
+      <c r="H141" s="162"/>
+      <c r="I141" s="141"/>
+      <c r="J141" s="139"/>
+      <c r="K141" s="162"/>
+      <c r="L141" s="141"/>
+      <c r="M141" s="139"/>
+      <c r="N141" s="162"/>
+      <c r="O141" s="141"/>
+      <c r="P141" s="139"/>
+      <c r="Q141" s="162"/>
+      <c r="R141" s="141"/>
+      <c r="S141" s="139"/>
+      <c r="T141" s="162"/>
+      <c r="U141" s="141"/>
+      <c r="V141" s="139"/>
+      <c r="W141" s="140"/>
+      <c r="X141" s="77"/>
       <c r="Y141" s="65"/>
       <c r="Z141" s="65"/>
       <c r="AA141" s="65"/>
@@ -7998,62 +7960,62 @@
       <c r="AD141" s="66"/>
     </row>
     <row r="142" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="125"/>
-      <c r="B142" s="186"/>
-      <c r="C142" s="78"/>
-      <c r="D142" s="126"/>
-      <c r="E142" s="113"/>
-      <c r="F142" s="81"/>
-      <c r="G142" s="126"/>
-      <c r="H142" s="113"/>
-      <c r="I142" s="127"/>
-      <c r="J142" s="126"/>
-      <c r="K142" s="113"/>
-      <c r="L142" s="81"/>
-      <c r="M142" s="126"/>
-      <c r="N142" s="113"/>
-      <c r="O142" s="127"/>
-      <c r="P142" s="126"/>
-      <c r="Q142" s="113"/>
-      <c r="R142" s="127"/>
-      <c r="S142" s="126"/>
-      <c r="T142" s="113"/>
-      <c r="U142" s="81"/>
-      <c r="V142" s="126"/>
-      <c r="W142" s="113"/>
-      <c r="X142" s="149"/>
-      <c r="Y142" s="129"/>
-      <c r="Z142" s="129"/>
-      <c r="AA142" s="129"/>
-      <c r="AB142" s="129"/>
-      <c r="AC142" s="129"/>
-      <c r="AD142" s="129"/>
+      <c r="A142" s="79"/>
+      <c r="B142" s="177"/>
+      <c r="C142" s="138"/>
+      <c r="D142" s="165"/>
+      <c r="E142" s="162"/>
+      <c r="F142" s="141"/>
+      <c r="G142" s="165"/>
+      <c r="H142" s="162"/>
+      <c r="I142" s="166"/>
+      <c r="J142" s="165"/>
+      <c r="K142" s="162"/>
+      <c r="L142" s="141"/>
+      <c r="M142" s="165"/>
+      <c r="N142" s="162"/>
+      <c r="O142" s="166"/>
+      <c r="P142" s="165"/>
+      <c r="Q142" s="162"/>
+      <c r="R142" s="166"/>
+      <c r="S142" s="165"/>
+      <c r="T142" s="162"/>
+      <c r="U142" s="141"/>
+      <c r="V142" s="165"/>
+      <c r="W142" s="162"/>
+      <c r="X142" s="86"/>
+      <c r="Y142" s="81"/>
+      <c r="Z142" s="81"/>
+      <c r="AA142" s="81"/>
+      <c r="AB142" s="81"/>
+      <c r="AC142" s="81"/>
+      <c r="AD142" s="81"/>
     </row>
     <row r="143" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="4"/>
-      <c r="B143" s="77"/>
-      <c r="C143" s="78"/>
-      <c r="D143" s="79"/>
-      <c r="E143" s="113"/>
-      <c r="F143" s="81"/>
-      <c r="G143" s="79"/>
-      <c r="H143" s="113"/>
-      <c r="I143" s="81"/>
-      <c r="J143" s="79"/>
-      <c r="K143" s="113"/>
-      <c r="L143" s="81"/>
-      <c r="M143" s="79"/>
-      <c r="N143" s="113"/>
-      <c r="O143" s="81"/>
-      <c r="P143" s="79"/>
-      <c r="Q143" s="113"/>
-      <c r="R143" s="81"/>
-      <c r="S143" s="79"/>
-      <c r="T143" s="113"/>
-      <c r="U143" s="81"/>
-      <c r="V143" s="79"/>
-      <c r="W143" s="113"/>
-      <c r="X143" s="150"/>
+      <c r="B143" s="180"/>
+      <c r="C143" s="138"/>
+      <c r="D143" s="139"/>
+      <c r="E143" s="162"/>
+      <c r="F143" s="141"/>
+      <c r="G143" s="139"/>
+      <c r="H143" s="162"/>
+      <c r="I143" s="141"/>
+      <c r="J143" s="139"/>
+      <c r="K143" s="162"/>
+      <c r="L143" s="141"/>
+      <c r="M143" s="139"/>
+      <c r="N143" s="162"/>
+      <c r="O143" s="141"/>
+      <c r="P143" s="139"/>
+      <c r="Q143" s="162"/>
+      <c r="R143" s="141"/>
+      <c r="S143" s="139"/>
+      <c r="T143" s="162"/>
+      <c r="U143" s="141"/>
+      <c r="V143" s="139"/>
+      <c r="W143" s="162"/>
+      <c r="X143" s="87"/>
       <c r="Y143" s="2"/>
       <c r="Z143" s="2"/>
       <c r="AA143" s="2"/>
@@ -8063,29 +8025,29 @@
     </row>
     <row r="144" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
-      <c r="B144" s="90"/>
-      <c r="C144" s="154"/>
-      <c r="D144" s="92"/>
-      <c r="E144" s="131"/>
-      <c r="F144" s="95"/>
-      <c r="G144" s="92"/>
-      <c r="H144" s="131"/>
-      <c r="I144" s="95"/>
-      <c r="J144" s="92"/>
-      <c r="K144" s="131"/>
-      <c r="L144" s="95"/>
-      <c r="M144" s="92"/>
-      <c r="N144" s="131"/>
-      <c r="O144" s="95"/>
-      <c r="P144" s="92"/>
-      <c r="Q144" s="131"/>
-      <c r="R144" s="95"/>
-      <c r="S144" s="92"/>
-      <c r="T144" s="131"/>
-      <c r="U144" s="95"/>
-      <c r="V144" s="92"/>
-      <c r="W144" s="131"/>
-      <c r="X144" s="150"/>
+      <c r="B144" s="181"/>
+      <c r="C144" s="167"/>
+      <c r="D144" s="148"/>
+      <c r="E144" s="168"/>
+      <c r="F144" s="151"/>
+      <c r="G144" s="148"/>
+      <c r="H144" s="168"/>
+      <c r="I144" s="151"/>
+      <c r="J144" s="148"/>
+      <c r="K144" s="168"/>
+      <c r="L144" s="151"/>
+      <c r="M144" s="148"/>
+      <c r="N144" s="168"/>
+      <c r="O144" s="151"/>
+      <c r="P144" s="148"/>
+      <c r="Q144" s="168"/>
+      <c r="R144" s="151"/>
+      <c r="S144" s="148"/>
+      <c r="T144" s="168"/>
+      <c r="U144" s="151"/>
+      <c r="V144" s="148"/>
+      <c r="W144" s="168"/>
+      <c r="X144" s="87"/>
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
       <c r="AA144" s="2"/>
@@ -8095,31 +8057,31 @@
     </row>
     <row r="145" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4"/>
-      <c r="B145" s="133" t="s">
+      <c r="B145" s="182" t="s">
         <v>27</v>
       </c>
-      <c r="C145" s="134"/>
-      <c r="D145" s="105"/>
-      <c r="E145" s="106"/>
-      <c r="F145" s="135"/>
-      <c r="G145" s="105"/>
-      <c r="H145" s="106"/>
-      <c r="I145" s="135"/>
-      <c r="J145" s="105"/>
-      <c r="K145" s="106"/>
-      <c r="L145" s="135"/>
-      <c r="M145" s="105"/>
-      <c r="N145" s="106"/>
-      <c r="O145" s="135"/>
-      <c r="P145" s="105"/>
-      <c r="Q145" s="106"/>
-      <c r="R145" s="135"/>
-      <c r="S145" s="105"/>
-      <c r="T145" s="106"/>
-      <c r="U145" s="135"/>
-      <c r="V145" s="105"/>
-      <c r="W145" s="106"/>
-      <c r="X145" s="150"/>
+      <c r="C145" s="169"/>
+      <c r="D145" s="157"/>
+      <c r="E145" s="158"/>
+      <c r="F145" s="170"/>
+      <c r="G145" s="157"/>
+      <c r="H145" s="158"/>
+      <c r="I145" s="170"/>
+      <c r="J145" s="157"/>
+      <c r="K145" s="158"/>
+      <c r="L145" s="170"/>
+      <c r="M145" s="157"/>
+      <c r="N145" s="158"/>
+      <c r="O145" s="170"/>
+      <c r="P145" s="157"/>
+      <c r="Q145" s="158"/>
+      <c r="R145" s="170"/>
+      <c r="S145" s="157"/>
+      <c r="T145" s="158"/>
+      <c r="U145" s="170"/>
+      <c r="V145" s="157"/>
+      <c r="W145" s="158"/>
+      <c r="X145" s="87"/>
       <c r="Y145" s="2"/>
       <c r="Z145" s="2"/>
       <c r="AA145" s="2"/>
@@ -8129,31 +8091,31 @@
     </row>
     <row r="146" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4"/>
-      <c r="B146" s="139" t="s">
+      <c r="B146" s="183" t="s">
         <v>28</v>
       </c>
-      <c r="C146" s="155"/>
-      <c r="D146" s="141"/>
-      <c r="E146" s="142"/>
-      <c r="F146" s="144"/>
-      <c r="G146" s="141"/>
-      <c r="H146" s="142"/>
-      <c r="I146" s="144"/>
-      <c r="J146" s="141"/>
-      <c r="K146" s="142"/>
-      <c r="L146" s="144"/>
-      <c r="M146" s="141"/>
-      <c r="N146" s="142"/>
-      <c r="O146" s="144"/>
-      <c r="P146" s="141"/>
-      <c r="Q146" s="142"/>
-      <c r="R146" s="144"/>
-      <c r="S146" s="141"/>
-      <c r="T146" s="142"/>
-      <c r="U146" s="144"/>
-      <c r="V146" s="141"/>
-      <c r="W146" s="142"/>
-      <c r="X146" s="150"/>
+      <c r="C146" s="171"/>
+      <c r="D146" s="172"/>
+      <c r="E146" s="173"/>
+      <c r="F146" s="174"/>
+      <c r="G146" s="172"/>
+      <c r="H146" s="173"/>
+      <c r="I146" s="174"/>
+      <c r="J146" s="172"/>
+      <c r="K146" s="173"/>
+      <c r="L146" s="174"/>
+      <c r="M146" s="172"/>
+      <c r="N146" s="173"/>
+      <c r="O146" s="174"/>
+      <c r="P146" s="172"/>
+      <c r="Q146" s="173"/>
+      <c r="R146" s="174"/>
+      <c r="S146" s="172"/>
+      <c r="T146" s="173"/>
+      <c r="U146" s="174"/>
+      <c r="V146" s="172"/>
+      <c r="W146" s="173"/>
+      <c r="X146" s="87"/>
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
       <c r="AA146" s="2"/>
@@ -8163,29 +8125,29 @@
     </row>
     <row r="147" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4"/>
-      <c r="B147" s="147"/>
-      <c r="C147" s="174"/>
-      <c r="D147" s="175"/>
-      <c r="E147" s="176"/>
-      <c r="F147" s="177"/>
-      <c r="G147" s="175"/>
-      <c r="H147" s="176"/>
-      <c r="I147" s="177"/>
-      <c r="J147" s="175"/>
-      <c r="K147" s="176"/>
-      <c r="L147" s="177"/>
-      <c r="M147" s="175"/>
-      <c r="N147" s="176"/>
-      <c r="O147" s="177"/>
-      <c r="P147" s="175"/>
-      <c r="Q147" s="176"/>
-      <c r="R147" s="177"/>
-      <c r="S147" s="175"/>
-      <c r="T147" s="176"/>
-      <c r="U147" s="179"/>
-      <c r="V147" s="180"/>
-      <c r="W147" s="181"/>
-      <c r="X147" s="150"/>
+      <c r="B147" s="84"/>
+      <c r="C147" s="118"/>
+      <c r="D147" s="116"/>
+      <c r="E147" s="117"/>
+      <c r="F147" s="115"/>
+      <c r="G147" s="116"/>
+      <c r="H147" s="117"/>
+      <c r="I147" s="115"/>
+      <c r="J147" s="116"/>
+      <c r="K147" s="117"/>
+      <c r="L147" s="115"/>
+      <c r="M147" s="116"/>
+      <c r="N147" s="117"/>
+      <c r="O147" s="115"/>
+      <c r="P147" s="116"/>
+      <c r="Q147" s="117"/>
+      <c r="R147" s="115"/>
+      <c r="S147" s="116"/>
+      <c r="T147" s="117"/>
+      <c r="U147" s="109"/>
+      <c r="V147" s="110"/>
+      <c r="W147" s="111"/>
+      <c r="X147" s="87"/>
       <c r="Y147" s="2"/>
       <c r="Z147" s="2"/>
       <c r="AA147" s="2"/>
@@ -8196,7 +8158,7 @@
     <row r="148" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4"/>
       <c r="B148" s="9"/>
-      <c r="C148" s="148" t="s">
+      <c r="C148" s="85" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="15" t="s">
@@ -8259,7 +8221,7 @@
       <c r="W148" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="X148" s="150"/>
+      <c r="X148" s="87"/>
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
       <c r="AA148" s="2"/>
@@ -8291,7 +8253,7 @@
       <c r="U149" s="23"/>
       <c r="V149" s="24"/>
       <c r="W149" s="25"/>
-      <c r="X149" s="150"/>
+      <c r="X149" s="87"/>
       <c r="Y149" s="2"/>
       <c r="Z149" s="2"/>
       <c r="AA149" s="2"/>
@@ -8323,7 +8285,7 @@
       <c r="U150" s="32"/>
       <c r="V150" s="33"/>
       <c r="W150" s="34"/>
-      <c r="X150" s="150"/>
+      <c r="X150" s="87"/>
       <c r="Y150" s="2"/>
       <c r="Z150" s="2"/>
       <c r="AA150" s="2"/>
@@ -8355,7 +8317,7 @@
       <c r="U151" s="32"/>
       <c r="V151" s="33"/>
       <c r="W151" s="34"/>
-      <c r="X151" s="150"/>
+      <c r="X151" s="87"/>
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
       <c r="AA151" s="2"/>
@@ -8387,7 +8349,7 @@
       <c r="U152" s="32"/>
       <c r="V152" s="33"/>
       <c r="W152" s="34"/>
-      <c r="X152" s="150"/>
+      <c r="X152" s="87"/>
       <c r="Y152" s="2"/>
       <c r="Z152" s="2"/>
       <c r="AA152" s="2"/>
@@ -8419,7 +8381,7 @@
       <c r="U153" s="32"/>
       <c r="V153" s="33"/>
       <c r="W153" s="34"/>
-      <c r="X153" s="150"/>
+      <c r="X153" s="87"/>
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
       <c r="AA153" s="2"/>
@@ -8451,7 +8413,7 @@
       <c r="U154" s="32"/>
       <c r="V154" s="33"/>
       <c r="W154" s="34"/>
-      <c r="X154" s="150"/>
+      <c r="X154" s="87"/>
       <c r="Y154" s="2"/>
       <c r="Z154" s="2"/>
       <c r="AA154" s="2"/>
@@ -8483,7 +8445,7 @@
       <c r="U155" s="32"/>
       <c r="V155" s="33"/>
       <c r="W155" s="34"/>
-      <c r="X155" s="150"/>
+      <c r="X155" s="87"/>
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
       <c r="AA155" s="2"/>
@@ -8515,7 +8477,7 @@
       <c r="U156" s="32"/>
       <c r="V156" s="33"/>
       <c r="W156" s="34"/>
-      <c r="X156" s="150"/>
+      <c r="X156" s="87"/>
       <c r="Y156" s="2"/>
       <c r="Z156" s="2"/>
       <c r="AA156" s="2"/>
@@ -8547,7 +8509,7 @@
       <c r="U157" s="32"/>
       <c r="V157" s="33"/>
       <c r="W157" s="34"/>
-      <c r="X157" s="150"/>
+      <c r="X157" s="87"/>
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
       <c r="AA157" s="2"/>
@@ -8579,7 +8541,7 @@
       <c r="U158" s="32"/>
       <c r="V158" s="33"/>
       <c r="W158" s="34"/>
-      <c r="X158" s="150"/>
+      <c r="X158" s="87"/>
       <c r="Y158" s="2"/>
       <c r="Z158" s="2"/>
       <c r="AA158" s="2"/>
@@ -8611,7 +8573,7 @@
       <c r="U159" s="32"/>
       <c r="V159" s="33"/>
       <c r="W159" s="34"/>
-      <c r="X159" s="150"/>
+      <c r="X159" s="87"/>
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
       <c r="AA159" s="2"/>
@@ -8624,7 +8586,7 @@
       <c r="B160" s="26"/>
       <c r="C160" s="37"/>
       <c r="D160" s="38"/>
-      <c r="E160" s="151"/>
+      <c r="E160" s="88"/>
       <c r="F160" s="40"/>
       <c r="G160" s="38"/>
       <c r="H160" s="41"/>
@@ -8643,7 +8605,7 @@
       <c r="U160" s="43"/>
       <c r="V160" s="44"/>
       <c r="W160" s="45"/>
-      <c r="X160" s="150"/>
+      <c r="X160" s="87"/>
       <c r="Y160" s="2"/>
       <c r="Z160" s="2"/>
       <c r="AA160" s="2"/>
@@ -8749,7 +8711,7 @@
       <c r="W162" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="X162" s="119"/>
+      <c r="X162" s="77"/>
       <c r="Y162" s="65"/>
       <c r="Z162" s="65"/>
       <c r="AA162" s="65"/>
@@ -8759,35 +8721,35 @@
     </row>
     <row r="163" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="59"/>
-      <c r="B163" s="185" t="s">
+      <c r="B163" s="176" t="s">
         <v>14</v>
       </c>
-      <c r="C163" s="67"/>
-      <c r="D163" s="68"/>
-      <c r="E163" s="69"/>
-      <c r="F163" s="70"/>
-      <c r="G163" s="190"/>
-      <c r="H163" s="69"/>
-      <c r="I163" s="70"/>
-      <c r="J163" s="71"/>
-      <c r="K163" s="69"/>
-      <c r="L163" s="70"/>
-      <c r="M163" s="68"/>
-      <c r="N163" s="69"/>
-      <c r="O163" s="70"/>
-      <c r="P163" s="72"/>
-      <c r="Q163" s="69"/>
-      <c r="R163" s="70"/>
-      <c r="S163" s="68"/>
-      <c r="T163" s="69"/>
-      <c r="U163" s="70"/>
-      <c r="V163" s="68"/>
-      <c r="W163" s="69"/>
-      <c r="X163" s="119"/>
-      <c r="Y163" s="75" t="s">
+      <c r="C163" s="131"/>
+      <c r="D163" s="132"/>
+      <c r="E163" s="133"/>
+      <c r="F163" s="134"/>
+      <c r="G163" s="135"/>
+      <c r="H163" s="133"/>
+      <c r="I163" s="134"/>
+      <c r="J163" s="136"/>
+      <c r="K163" s="133"/>
+      <c r="L163" s="134"/>
+      <c r="M163" s="132"/>
+      <c r="N163" s="133"/>
+      <c r="O163" s="134"/>
+      <c r="P163" s="137"/>
+      <c r="Q163" s="133"/>
+      <c r="R163" s="134"/>
+      <c r="S163" s="132"/>
+      <c r="T163" s="133"/>
+      <c r="U163" s="134"/>
+      <c r="V163" s="132"/>
+      <c r="W163" s="133"/>
+      <c r="X163" s="77"/>
+      <c r="Y163" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="Z163" s="76">
+      <c r="Z163" s="68">
         <f>COUNTIF(C163:W182,Y163)</f>
         <v>0</v>
       </c>
@@ -8798,33 +8760,33 @@
     </row>
     <row r="164" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="59"/>
-      <c r="B164" s="186"/>
-      <c r="C164" s="78"/>
-      <c r="D164" s="79"/>
-      <c r="E164" s="80"/>
-      <c r="F164" s="81"/>
-      <c r="G164" s="191"/>
-      <c r="H164" s="80"/>
-      <c r="I164" s="81"/>
-      <c r="J164" s="79"/>
-      <c r="K164" s="80"/>
-      <c r="L164" s="82"/>
-      <c r="M164" s="79"/>
-      <c r="N164" s="83"/>
-      <c r="O164" s="81"/>
-      <c r="P164" s="84"/>
-      <c r="Q164" s="80"/>
-      <c r="R164" s="82"/>
-      <c r="S164" s="79"/>
-      <c r="T164" s="80"/>
-      <c r="U164" s="81"/>
-      <c r="V164" s="79"/>
-      <c r="W164" s="83"/>
-      <c r="X164" s="119"/>
-      <c r="Y164" s="87" t="s">
+      <c r="B164" s="177"/>
+      <c r="C164" s="138"/>
+      <c r="D164" s="139"/>
+      <c r="E164" s="140"/>
+      <c r="F164" s="141"/>
+      <c r="G164" s="142"/>
+      <c r="H164" s="140"/>
+      <c r="I164" s="141"/>
+      <c r="J164" s="139"/>
+      <c r="K164" s="140"/>
+      <c r="L164" s="143"/>
+      <c r="M164" s="139"/>
+      <c r="N164" s="144"/>
+      <c r="O164" s="141"/>
+      <c r="P164" s="145"/>
+      <c r="Q164" s="140"/>
+      <c r="R164" s="143"/>
+      <c r="S164" s="139"/>
+      <c r="T164" s="140"/>
+      <c r="U164" s="141"/>
+      <c r="V164" s="139"/>
+      <c r="W164" s="144"/>
+      <c r="X164" s="77"/>
+      <c r="Y164" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="Z164" s="88">
+      <c r="Z164" s="70">
         <f>COUNTIF(C163:W182,Y164)</f>
         <v>0</v>
       </c>
@@ -8835,33 +8797,33 @@
     </row>
     <row r="165" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="59"/>
-      <c r="B165" s="186"/>
-      <c r="C165" s="78"/>
-      <c r="D165" s="79"/>
-      <c r="E165" s="80"/>
-      <c r="F165" s="81"/>
-      <c r="G165" s="191"/>
-      <c r="H165" s="80"/>
-      <c r="I165" s="81"/>
-      <c r="J165" s="79"/>
-      <c r="K165" s="80"/>
-      <c r="L165" s="82"/>
-      <c r="M165" s="79"/>
-      <c r="N165" s="83"/>
-      <c r="O165" s="81"/>
-      <c r="P165" s="84"/>
-      <c r="Q165" s="83"/>
-      <c r="R165" s="81"/>
-      <c r="S165" s="79"/>
-      <c r="T165" s="83"/>
-      <c r="U165" s="81"/>
-      <c r="V165" s="79"/>
-      <c r="W165" s="83"/>
-      <c r="X165" s="119"/>
-      <c r="Y165" s="87" t="s">
+      <c r="B165" s="177"/>
+      <c r="C165" s="138"/>
+      <c r="D165" s="139"/>
+      <c r="E165" s="140"/>
+      <c r="F165" s="141"/>
+      <c r="G165" s="142"/>
+      <c r="H165" s="140"/>
+      <c r="I165" s="141"/>
+      <c r="J165" s="139"/>
+      <c r="K165" s="140"/>
+      <c r="L165" s="143"/>
+      <c r="M165" s="139"/>
+      <c r="N165" s="144"/>
+      <c r="O165" s="141"/>
+      <c r="P165" s="145"/>
+      <c r="Q165" s="144"/>
+      <c r="R165" s="141"/>
+      <c r="S165" s="139"/>
+      <c r="T165" s="144"/>
+      <c r="U165" s="141"/>
+      <c r="V165" s="139"/>
+      <c r="W165" s="144"/>
+      <c r="X165" s="77"/>
+      <c r="Y165" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="Z165" s="88">
+      <c r="Z165" s="70">
         <f>COUNTIF(C163:W182,Y165)</f>
         <v>0</v>
       </c>
@@ -8872,33 +8834,33 @@
     </row>
     <row r="166" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="59"/>
-      <c r="B166" s="186"/>
-      <c r="C166" s="89"/>
-      <c r="D166" s="79"/>
-      <c r="E166" s="83"/>
-      <c r="F166" s="82"/>
-      <c r="G166" s="79"/>
-      <c r="H166" s="83"/>
-      <c r="I166" s="82"/>
-      <c r="J166" s="79"/>
-      <c r="K166" s="83"/>
-      <c r="L166" s="82"/>
-      <c r="M166" s="79"/>
-      <c r="N166" s="83"/>
-      <c r="O166" s="82"/>
-      <c r="P166" s="84"/>
-      <c r="Q166" s="83"/>
-      <c r="R166" s="82"/>
-      <c r="S166" s="79"/>
-      <c r="T166" s="83"/>
-      <c r="U166" s="81"/>
-      <c r="V166" s="79"/>
-      <c r="W166" s="83"/>
-      <c r="X166" s="119"/>
-      <c r="Y166" s="87" t="s">
+      <c r="B166" s="177"/>
+      <c r="C166" s="146"/>
+      <c r="D166" s="139"/>
+      <c r="E166" s="144"/>
+      <c r="F166" s="143"/>
+      <c r="G166" s="139"/>
+      <c r="H166" s="144"/>
+      <c r="I166" s="143"/>
+      <c r="J166" s="139"/>
+      <c r="K166" s="144"/>
+      <c r="L166" s="143"/>
+      <c r="M166" s="139"/>
+      <c r="N166" s="144"/>
+      <c r="O166" s="143"/>
+      <c r="P166" s="145"/>
+      <c r="Q166" s="144"/>
+      <c r="R166" s="143"/>
+      <c r="S166" s="139"/>
+      <c r="T166" s="144"/>
+      <c r="U166" s="141"/>
+      <c r="V166" s="139"/>
+      <c r="W166" s="144"/>
+      <c r="X166" s="77"/>
+      <c r="Y166" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="Z166" s="88">
+      <c r="Z166" s="70">
         <f>COUNTIF(C163:W182,Y166)</f>
         <v>0</v>
       </c>
@@ -8909,33 +8871,33 @@
     </row>
     <row r="167" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="59"/>
-      <c r="B167" s="189"/>
-      <c r="C167" s="91"/>
-      <c r="D167" s="92"/>
-      <c r="E167" s="93"/>
-      <c r="F167" s="94"/>
-      <c r="G167" s="92"/>
-      <c r="H167" s="93"/>
-      <c r="I167" s="95"/>
-      <c r="J167" s="92"/>
-      <c r="K167" s="93"/>
-      <c r="L167" s="96"/>
-      <c r="M167" s="92"/>
-      <c r="N167" s="93"/>
-      <c r="O167" s="94"/>
-      <c r="P167" s="97"/>
-      <c r="Q167" s="93"/>
-      <c r="R167" s="95"/>
-      <c r="S167" s="92"/>
-      <c r="T167" s="93"/>
-      <c r="U167" s="95"/>
-      <c r="V167" s="92"/>
-      <c r="W167" s="93"/>
-      <c r="X167" s="119"/>
-      <c r="Y167" s="87" t="s">
+      <c r="B167" s="178"/>
+      <c r="C167" s="147"/>
+      <c r="D167" s="148"/>
+      <c r="E167" s="149"/>
+      <c r="F167" s="150"/>
+      <c r="G167" s="148"/>
+      <c r="H167" s="149"/>
+      <c r="I167" s="151"/>
+      <c r="J167" s="148"/>
+      <c r="K167" s="149"/>
+      <c r="L167" s="152"/>
+      <c r="M167" s="148"/>
+      <c r="N167" s="149"/>
+      <c r="O167" s="150"/>
+      <c r="P167" s="153"/>
+      <c r="Q167" s="149"/>
+      <c r="R167" s="151"/>
+      <c r="S167" s="148"/>
+      <c r="T167" s="149"/>
+      <c r="U167" s="151"/>
+      <c r="V167" s="148"/>
+      <c r="W167" s="149"/>
+      <c r="X167" s="77"/>
+      <c r="Y167" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="Z167" s="88">
+      <c r="Z167" s="70">
         <f>COUNTIF(C163:W182,Y167)</f>
         <v>0</v>
       </c>
@@ -8946,35 +8908,35 @@
     </row>
     <row r="168" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="59"/>
-      <c r="B168" s="101" t="s">
+      <c r="B168" s="179" t="s">
         <v>20</v>
       </c>
-      <c r="C168" s="102"/>
-      <c r="D168" s="103"/>
-      <c r="E168" s="104"/>
-      <c r="F168" s="102"/>
-      <c r="G168" s="103"/>
-      <c r="H168" s="104"/>
-      <c r="I168" s="102"/>
-      <c r="J168" s="103"/>
-      <c r="K168" s="104"/>
-      <c r="L168" s="102"/>
-      <c r="M168" s="103"/>
-      <c r="N168" s="104"/>
-      <c r="O168" s="102"/>
-      <c r="P168" s="103"/>
-      <c r="Q168" s="104"/>
-      <c r="R168" s="102"/>
-      <c r="S168" s="105"/>
-      <c r="T168" s="106"/>
-      <c r="U168" s="102"/>
-      <c r="V168" s="105"/>
-      <c r="W168" s="106"/>
-      <c r="X168" s="119"/>
-      <c r="Y168" s="87" t="s">
+      <c r="C168" s="154"/>
+      <c r="D168" s="155"/>
+      <c r="E168" s="156"/>
+      <c r="F168" s="154"/>
+      <c r="G168" s="155"/>
+      <c r="H168" s="156"/>
+      <c r="I168" s="154"/>
+      <c r="J168" s="155"/>
+      <c r="K168" s="156"/>
+      <c r="L168" s="154"/>
+      <c r="M168" s="155"/>
+      <c r="N168" s="156"/>
+      <c r="O168" s="154"/>
+      <c r="P168" s="155"/>
+      <c r="Q168" s="156"/>
+      <c r="R168" s="154"/>
+      <c r="S168" s="157"/>
+      <c r="T168" s="158"/>
+      <c r="U168" s="154"/>
+      <c r="V168" s="157"/>
+      <c r="W168" s="158"/>
+      <c r="X168" s="77"/>
+      <c r="Y168" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="Z168" s="88">
+      <c r="Z168" s="70">
         <f>COUNTIF(C163:W182,Y168)</f>
         <v>0</v>
       </c>
@@ -8985,35 +8947,35 @@
     </row>
     <row r="169" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="59"/>
-      <c r="B169" s="185" t="s">
+      <c r="B169" s="176" t="s">
         <v>29</v>
       </c>
-      <c r="C169" s="67"/>
-      <c r="D169" s="108"/>
-      <c r="E169" s="109"/>
-      <c r="F169" s="110"/>
-      <c r="G169" s="68"/>
-      <c r="H169" s="109"/>
-      <c r="I169" s="110"/>
-      <c r="J169" s="68"/>
-      <c r="K169" s="109"/>
-      <c r="L169" s="110"/>
-      <c r="M169" s="68"/>
-      <c r="N169" s="109"/>
-      <c r="O169" s="110"/>
-      <c r="P169" s="68"/>
-      <c r="Q169" s="109"/>
-      <c r="R169" s="110"/>
-      <c r="S169" s="68"/>
-      <c r="T169" s="109"/>
-      <c r="U169" s="110"/>
-      <c r="V169" s="68"/>
-      <c r="W169" s="152"/>
-      <c r="X169" s="119"/>
-      <c r="Y169" s="87" t="s">
+      <c r="C169" s="131"/>
+      <c r="D169" s="159"/>
+      <c r="E169" s="160"/>
+      <c r="F169" s="161"/>
+      <c r="G169" s="132"/>
+      <c r="H169" s="160"/>
+      <c r="I169" s="161"/>
+      <c r="J169" s="132"/>
+      <c r="K169" s="160"/>
+      <c r="L169" s="161"/>
+      <c r="M169" s="132"/>
+      <c r="N169" s="160"/>
+      <c r="O169" s="161"/>
+      <c r="P169" s="132"/>
+      <c r="Q169" s="160"/>
+      <c r="R169" s="161"/>
+      <c r="S169" s="132"/>
+      <c r="T169" s="160"/>
+      <c r="U169" s="161"/>
+      <c r="V169" s="132"/>
+      <c r="W169" s="175"/>
+      <c r="X169" s="77"/>
+      <c r="Y169" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="Z169" s="88">
+      <c r="Z169" s="70">
         <f>COUNTIF(C163:W182,Y169)</f>
         <v>0</v>
       </c>
@@ -9024,33 +8986,33 @@
     </row>
     <row r="170" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="59"/>
-      <c r="B170" s="186"/>
-      <c r="C170" s="78"/>
-      <c r="D170" s="79"/>
-      <c r="E170" s="113"/>
-      <c r="F170" s="81"/>
-      <c r="G170" s="79"/>
-      <c r="H170" s="113"/>
-      <c r="I170" s="81"/>
-      <c r="J170" s="114"/>
-      <c r="K170" s="113"/>
-      <c r="L170" s="81"/>
-      <c r="M170" s="79"/>
-      <c r="N170" s="113"/>
-      <c r="O170" s="81"/>
-      <c r="P170" s="79"/>
-      <c r="Q170" s="113"/>
-      <c r="R170" s="81"/>
-      <c r="S170" s="114"/>
-      <c r="T170" s="113"/>
-      <c r="U170" s="81"/>
-      <c r="V170" s="79"/>
-      <c r="W170" s="113"/>
-      <c r="X170" s="119"/>
-      <c r="Y170" s="87" t="s">
+      <c r="B170" s="177"/>
+      <c r="C170" s="138"/>
+      <c r="D170" s="139"/>
+      <c r="E170" s="162"/>
+      <c r="F170" s="141"/>
+      <c r="G170" s="139"/>
+      <c r="H170" s="162"/>
+      <c r="I170" s="141"/>
+      <c r="J170" s="163"/>
+      <c r="K170" s="162"/>
+      <c r="L170" s="141"/>
+      <c r="M170" s="139"/>
+      <c r="N170" s="162"/>
+      <c r="O170" s="141"/>
+      <c r="P170" s="139"/>
+      <c r="Q170" s="162"/>
+      <c r="R170" s="141"/>
+      <c r="S170" s="163"/>
+      <c r="T170" s="162"/>
+      <c r="U170" s="141"/>
+      <c r="V170" s="139"/>
+      <c r="W170" s="162"/>
+      <c r="X170" s="77"/>
+      <c r="Y170" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="Z170" s="88">
+      <c r="Z170" s="70">
         <f>COUNTIF(C163:W182,Y170)</f>
         <v>0</v>
       </c>
@@ -9061,33 +9023,33 @@
     </row>
     <row r="171" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="59"/>
-      <c r="B171" s="186"/>
-      <c r="C171" s="78"/>
-      <c r="D171" s="79"/>
-      <c r="E171" s="113"/>
-      <c r="F171" s="81"/>
-      <c r="G171" s="79"/>
-      <c r="H171" s="113"/>
-      <c r="I171" s="81"/>
-      <c r="J171" s="114"/>
-      <c r="K171" s="113"/>
-      <c r="L171" s="81"/>
-      <c r="M171" s="79"/>
-      <c r="N171" s="113"/>
-      <c r="O171" s="81"/>
-      <c r="P171" s="79"/>
-      <c r="Q171" s="113"/>
-      <c r="R171" s="81"/>
-      <c r="S171" s="114"/>
-      <c r="T171" s="113"/>
-      <c r="U171" s="81"/>
-      <c r="V171" s="79"/>
-      <c r="W171" s="113"/>
-      <c r="X171" s="119"/>
-      <c r="Y171" s="87" t="s">
+      <c r="B171" s="177"/>
+      <c r="C171" s="138"/>
+      <c r="D171" s="139"/>
+      <c r="E171" s="162"/>
+      <c r="F171" s="141"/>
+      <c r="G171" s="139"/>
+      <c r="H171" s="162"/>
+      <c r="I171" s="141"/>
+      <c r="J171" s="163"/>
+      <c r="K171" s="162"/>
+      <c r="L171" s="141"/>
+      <c r="M171" s="139"/>
+      <c r="N171" s="162"/>
+      <c r="O171" s="141"/>
+      <c r="P171" s="139"/>
+      <c r="Q171" s="162"/>
+      <c r="R171" s="141"/>
+      <c r="S171" s="163"/>
+      <c r="T171" s="162"/>
+      <c r="U171" s="141"/>
+      <c r="V171" s="139"/>
+      <c r="W171" s="162"/>
+      <c r="X171" s="77"/>
+      <c r="Y171" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="Z171" s="88">
+      <c r="Z171" s="70">
         <f>COUNTIF(C163:W182,Y171)</f>
         <v>0</v>
       </c>
@@ -9098,33 +9060,33 @@
     </row>
     <row r="172" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="59"/>
-      <c r="B172" s="186"/>
-      <c r="C172" s="78"/>
-      <c r="D172" s="79"/>
-      <c r="E172" s="80"/>
-      <c r="F172" s="81"/>
-      <c r="G172" s="114"/>
-      <c r="H172" s="80"/>
-      <c r="I172" s="81"/>
-      <c r="J172" s="79"/>
-      <c r="K172" s="80"/>
-      <c r="L172" s="81"/>
-      <c r="M172" s="79"/>
-      <c r="N172" s="80"/>
-      <c r="O172" s="81"/>
-      <c r="P172" s="79"/>
-      <c r="Q172" s="80"/>
-      <c r="R172" s="81"/>
-      <c r="S172" s="79"/>
-      <c r="T172" s="80"/>
-      <c r="U172" s="81"/>
-      <c r="V172" s="79"/>
-      <c r="W172" s="113"/>
-      <c r="X172" s="119"/>
-      <c r="Y172" s="153" t="s">
+      <c r="B172" s="177"/>
+      <c r="C172" s="138"/>
+      <c r="D172" s="139"/>
+      <c r="E172" s="140"/>
+      <c r="F172" s="141"/>
+      <c r="G172" s="163"/>
+      <c r="H172" s="140"/>
+      <c r="I172" s="141"/>
+      <c r="J172" s="139"/>
+      <c r="K172" s="140"/>
+      <c r="L172" s="141"/>
+      <c r="M172" s="139"/>
+      <c r="N172" s="140"/>
+      <c r="O172" s="141"/>
+      <c r="P172" s="139"/>
+      <c r="Q172" s="140"/>
+      <c r="R172" s="141"/>
+      <c r="S172" s="139"/>
+      <c r="T172" s="140"/>
+      <c r="U172" s="141"/>
+      <c r="V172" s="139"/>
+      <c r="W172" s="162"/>
+      <c r="X172" s="77"/>
+      <c r="Y172" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="Z172" s="117">
+      <c r="Z172" s="76">
         <f>COUNTIF(C163:W182,Y172)</f>
         <v>0</v>
       </c>
@@ -9135,29 +9097,29 @@
     </row>
     <row r="173" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="59"/>
-      <c r="B173" s="186"/>
-      <c r="C173" s="89"/>
-      <c r="D173" s="79"/>
-      <c r="E173" s="113"/>
-      <c r="F173" s="82"/>
-      <c r="G173" s="79"/>
-      <c r="H173" s="113"/>
-      <c r="I173" s="82"/>
-      <c r="J173" s="114"/>
-      <c r="K173" s="113"/>
-      <c r="L173" s="82"/>
-      <c r="M173" s="79"/>
-      <c r="N173" s="113"/>
-      <c r="O173" s="82"/>
-      <c r="P173" s="79"/>
-      <c r="Q173" s="113"/>
-      <c r="R173" s="82"/>
-      <c r="S173" s="114"/>
-      <c r="T173" s="113"/>
-      <c r="U173" s="82"/>
-      <c r="V173" s="79"/>
-      <c r="W173" s="113"/>
-      <c r="X173" s="119"/>
+      <c r="B173" s="177"/>
+      <c r="C173" s="146"/>
+      <c r="D173" s="139"/>
+      <c r="E173" s="162"/>
+      <c r="F173" s="143"/>
+      <c r="G173" s="139"/>
+      <c r="H173" s="162"/>
+      <c r="I173" s="143"/>
+      <c r="J173" s="163"/>
+      <c r="K173" s="162"/>
+      <c r="L173" s="143"/>
+      <c r="M173" s="139"/>
+      <c r="N173" s="162"/>
+      <c r="O173" s="143"/>
+      <c r="P173" s="139"/>
+      <c r="Q173" s="162"/>
+      <c r="R173" s="143"/>
+      <c r="S173" s="163"/>
+      <c r="T173" s="162"/>
+      <c r="U173" s="143"/>
+      <c r="V173" s="139"/>
+      <c r="W173" s="162"/>
+      <c r="X173" s="77"/>
       <c r="Y173" s="65"/>
       <c r="Z173" s="65"/>
       <c r="AA173" s="65"/>
@@ -9167,29 +9129,29 @@
     </row>
     <row r="174" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="59"/>
-      <c r="B174" s="186"/>
-      <c r="C174" s="89"/>
-      <c r="D174" s="79"/>
-      <c r="E174" s="113"/>
-      <c r="F174" s="82"/>
-      <c r="G174" s="79"/>
-      <c r="H174" s="113"/>
-      <c r="I174" s="82"/>
-      <c r="J174" s="114"/>
-      <c r="K174" s="113"/>
-      <c r="L174" s="82"/>
-      <c r="M174" s="79"/>
-      <c r="N174" s="113"/>
-      <c r="O174" s="82"/>
-      <c r="P174" s="79"/>
-      <c r="Q174" s="113"/>
-      <c r="R174" s="82"/>
-      <c r="S174" s="114"/>
-      <c r="T174" s="113"/>
-      <c r="U174" s="81"/>
-      <c r="V174" s="79"/>
-      <c r="W174" s="113"/>
-      <c r="X174" s="119"/>
+      <c r="B174" s="177"/>
+      <c r="C174" s="146"/>
+      <c r="D174" s="139"/>
+      <c r="E174" s="162"/>
+      <c r="F174" s="143"/>
+      <c r="G174" s="139"/>
+      <c r="H174" s="162"/>
+      <c r="I174" s="143"/>
+      <c r="J174" s="163"/>
+      <c r="K174" s="162"/>
+      <c r="L174" s="143"/>
+      <c r="M174" s="139"/>
+      <c r="N174" s="162"/>
+      <c r="O174" s="143"/>
+      <c r="P174" s="139"/>
+      <c r="Q174" s="162"/>
+      <c r="R174" s="143"/>
+      <c r="S174" s="163"/>
+      <c r="T174" s="162"/>
+      <c r="U174" s="141"/>
+      <c r="V174" s="139"/>
+      <c r="W174" s="162"/>
+      <c r="X174" s="77"/>
       <c r="Y174" s="65"/>
       <c r="Z174" s="65"/>
       <c r="AA174" s="65"/>
@@ -9199,29 +9161,29 @@
     </row>
     <row r="175" spans="1:30" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="59"/>
-      <c r="B175" s="186"/>
-      <c r="C175" s="78"/>
-      <c r="D175" s="79"/>
-      <c r="E175" s="113"/>
-      <c r="F175" s="81"/>
-      <c r="G175" s="79"/>
-      <c r="H175" s="113"/>
-      <c r="I175" s="82"/>
-      <c r="J175" s="114"/>
-      <c r="K175" s="113"/>
-      <c r="L175" s="82"/>
-      <c r="M175" s="79"/>
-      <c r="N175" s="113"/>
-      <c r="O175" s="81"/>
-      <c r="P175" s="79"/>
-      <c r="Q175" s="113"/>
-      <c r="R175" s="81"/>
-      <c r="S175" s="114"/>
-      <c r="T175" s="113"/>
-      <c r="U175" s="82"/>
-      <c r="V175" s="79"/>
-      <c r="W175" s="113"/>
-      <c r="X175" s="119"/>
+      <c r="B175" s="177"/>
+      <c r="C175" s="138"/>
+      <c r="D175" s="139"/>
+      <c r="E175" s="162"/>
+      <c r="F175" s="141"/>
+      <c r="G175" s="139"/>
+      <c r="H175" s="162"/>
+      <c r="I175" s="143"/>
+      <c r="J175" s="163"/>
+      <c r="K175" s="162"/>
+      <c r="L175" s="143"/>
+      <c r="M175" s="139"/>
+      <c r="N175" s="162"/>
+      <c r="O175" s="141"/>
+      <c r="P175" s="139"/>
+      <c r="Q175" s="162"/>
+      <c r="R175" s="141"/>
+      <c r="S175" s="163"/>
+      <c r="T175" s="162"/>
+      <c r="U175" s="143"/>
+      <c r="V175" s="139"/>
+      <c r="W175" s="162"/>
+      <c r="X175" s="77"/>
       <c r="Y175" s="65"/>
       <c r="Z175" s="65"/>
       <c r="AA175" s="65"/>
@@ -9231,29 +9193,29 @@
     </row>
     <row r="176" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="59"/>
-      <c r="B176" s="186"/>
-      <c r="C176" s="78"/>
-      <c r="D176" s="79"/>
-      <c r="E176" s="80"/>
-      <c r="F176" s="81"/>
-      <c r="G176" s="79"/>
-      <c r="H176" s="80"/>
-      <c r="I176" s="81"/>
-      <c r="J176" s="121"/>
-      <c r="K176" s="80"/>
-      <c r="L176" s="81"/>
-      <c r="M176" s="79"/>
-      <c r="N176" s="80"/>
-      <c r="O176" s="81"/>
-      <c r="P176" s="79"/>
-      <c r="Q176" s="80"/>
-      <c r="R176" s="81"/>
-      <c r="S176" s="114"/>
-      <c r="T176" s="113"/>
-      <c r="U176" s="81"/>
-      <c r="V176" s="79"/>
-      <c r="W176" s="113"/>
-      <c r="X176" s="119"/>
+      <c r="B176" s="177"/>
+      <c r="C176" s="138"/>
+      <c r="D176" s="139"/>
+      <c r="E176" s="140"/>
+      <c r="F176" s="141"/>
+      <c r="G176" s="139"/>
+      <c r="H176" s="140"/>
+      <c r="I176" s="141"/>
+      <c r="J176" s="164"/>
+      <c r="K176" s="140"/>
+      <c r="L176" s="141"/>
+      <c r="M176" s="139"/>
+      <c r="N176" s="140"/>
+      <c r="O176" s="141"/>
+      <c r="P176" s="139"/>
+      <c r="Q176" s="140"/>
+      <c r="R176" s="141"/>
+      <c r="S176" s="163"/>
+      <c r="T176" s="162"/>
+      <c r="U176" s="141"/>
+      <c r="V176" s="139"/>
+      <c r="W176" s="162"/>
+      <c r="X176" s="77"/>
       <c r="Y176" s="65"/>
       <c r="Z176" s="65"/>
       <c r="AA176" s="65"/>
@@ -9263,29 +9225,29 @@
     </row>
     <row r="177" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="59"/>
-      <c r="B177" s="186"/>
-      <c r="C177" s="78"/>
-      <c r="D177" s="79"/>
-      <c r="E177" s="113"/>
-      <c r="F177" s="81"/>
-      <c r="G177" s="79"/>
-      <c r="H177" s="113"/>
-      <c r="I177" s="81"/>
-      <c r="J177" s="79"/>
-      <c r="K177" s="113"/>
-      <c r="L177" s="81"/>
-      <c r="M177" s="79"/>
-      <c r="N177" s="113"/>
-      <c r="O177" s="81"/>
-      <c r="P177" s="79"/>
-      <c r="Q177" s="113"/>
-      <c r="R177" s="81"/>
-      <c r="S177" s="79"/>
-      <c r="T177" s="113"/>
-      <c r="U177" s="81"/>
-      <c r="V177" s="79"/>
-      <c r="W177" s="80"/>
-      <c r="X177" s="119"/>
+      <c r="B177" s="177"/>
+      <c r="C177" s="138"/>
+      <c r="D177" s="139"/>
+      <c r="E177" s="162"/>
+      <c r="F177" s="141"/>
+      <c r="G177" s="139"/>
+      <c r="H177" s="162"/>
+      <c r="I177" s="141"/>
+      <c r="J177" s="139"/>
+      <c r="K177" s="162"/>
+      <c r="L177" s="141"/>
+      <c r="M177" s="139"/>
+      <c r="N177" s="162"/>
+      <c r="O177" s="141"/>
+      <c r="P177" s="139"/>
+      <c r="Q177" s="162"/>
+      <c r="R177" s="141"/>
+      <c r="S177" s="139"/>
+      <c r="T177" s="162"/>
+      <c r="U177" s="141"/>
+      <c r="V177" s="139"/>
+      <c r="W177" s="140"/>
+      <c r="X177" s="77"/>
       <c r="Y177" s="65"/>
       <c r="Z177" s="65"/>
       <c r="AA177" s="65"/>
@@ -9294,62 +9256,62 @@
       <c r="AD177" s="66"/>
     </row>
     <row r="178" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="125"/>
-      <c r="B178" s="186"/>
-      <c r="C178" s="78"/>
-      <c r="D178" s="126"/>
-      <c r="E178" s="113"/>
-      <c r="F178" s="81"/>
-      <c r="G178" s="126"/>
-      <c r="H178" s="113"/>
-      <c r="I178" s="127"/>
-      <c r="J178" s="126"/>
-      <c r="K178" s="113"/>
-      <c r="L178" s="81"/>
-      <c r="M178" s="126"/>
-      <c r="N178" s="113"/>
-      <c r="O178" s="127"/>
-      <c r="P178" s="126"/>
-      <c r="Q178" s="113"/>
-      <c r="R178" s="127"/>
-      <c r="S178" s="126"/>
-      <c r="T178" s="113"/>
-      <c r="U178" s="81"/>
-      <c r="V178" s="126"/>
-      <c r="W178" s="113"/>
-      <c r="X178" s="149"/>
-      <c r="Y178" s="129"/>
-      <c r="Z178" s="129"/>
-      <c r="AA178" s="129"/>
-      <c r="AB178" s="129"/>
-      <c r="AC178" s="129"/>
-      <c r="AD178" s="129"/>
+      <c r="A178" s="79"/>
+      <c r="B178" s="177"/>
+      <c r="C178" s="138"/>
+      <c r="D178" s="165"/>
+      <c r="E178" s="162"/>
+      <c r="F178" s="141"/>
+      <c r="G178" s="165"/>
+      <c r="H178" s="162"/>
+      <c r="I178" s="166"/>
+      <c r="J178" s="165"/>
+      <c r="K178" s="162"/>
+      <c r="L178" s="141"/>
+      <c r="M178" s="165"/>
+      <c r="N178" s="162"/>
+      <c r="O178" s="166"/>
+      <c r="P178" s="165"/>
+      <c r="Q178" s="162"/>
+      <c r="R178" s="166"/>
+      <c r="S178" s="165"/>
+      <c r="T178" s="162"/>
+      <c r="U178" s="141"/>
+      <c r="V178" s="165"/>
+      <c r="W178" s="162"/>
+      <c r="X178" s="86"/>
+      <c r="Y178" s="81"/>
+      <c r="Z178" s="81"/>
+      <c r="AA178" s="81"/>
+      <c r="AB178" s="81"/>
+      <c r="AC178" s="81"/>
+      <c r="AD178" s="81"/>
     </row>
     <row r="179" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="4"/>
-      <c r="B179" s="77"/>
-      <c r="C179" s="78"/>
-      <c r="D179" s="79"/>
-      <c r="E179" s="113"/>
-      <c r="F179" s="81"/>
-      <c r="G179" s="79"/>
-      <c r="H179" s="113"/>
-      <c r="I179" s="81"/>
-      <c r="J179" s="79"/>
-      <c r="K179" s="113"/>
-      <c r="L179" s="81"/>
-      <c r="M179" s="79"/>
-      <c r="N179" s="113"/>
-      <c r="O179" s="81"/>
-      <c r="P179" s="79"/>
-      <c r="Q179" s="113"/>
-      <c r="R179" s="81"/>
-      <c r="S179" s="79"/>
-      <c r="T179" s="113"/>
-      <c r="U179" s="81"/>
-      <c r="V179" s="79"/>
-      <c r="W179" s="113"/>
-      <c r="X179" s="150"/>
+      <c r="B179" s="180"/>
+      <c r="C179" s="138"/>
+      <c r="D179" s="139"/>
+      <c r="E179" s="162"/>
+      <c r="F179" s="141"/>
+      <c r="G179" s="139"/>
+      <c r="H179" s="162"/>
+      <c r="I179" s="141"/>
+      <c r="J179" s="139"/>
+      <c r="K179" s="162"/>
+      <c r="L179" s="141"/>
+      <c r="M179" s="139"/>
+      <c r="N179" s="162"/>
+      <c r="O179" s="141"/>
+      <c r="P179" s="139"/>
+      <c r="Q179" s="162"/>
+      <c r="R179" s="141"/>
+      <c r="S179" s="139"/>
+      <c r="T179" s="162"/>
+      <c r="U179" s="141"/>
+      <c r="V179" s="139"/>
+      <c r="W179" s="162"/>
+      <c r="X179" s="87"/>
       <c r="Y179" s="2"/>
       <c r="Z179" s="2"/>
       <c r="AA179" s="2"/>
@@ -9359,29 +9321,29 @@
     </row>
     <row r="180" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="4"/>
-      <c r="B180" s="90"/>
-      <c r="C180" s="154"/>
-      <c r="D180" s="92"/>
-      <c r="E180" s="131"/>
-      <c r="F180" s="95"/>
-      <c r="G180" s="92"/>
-      <c r="H180" s="131"/>
-      <c r="I180" s="95"/>
-      <c r="J180" s="92"/>
-      <c r="K180" s="131"/>
-      <c r="L180" s="95"/>
-      <c r="M180" s="92"/>
-      <c r="N180" s="131"/>
-      <c r="O180" s="95"/>
-      <c r="P180" s="92"/>
-      <c r="Q180" s="131"/>
-      <c r="R180" s="95"/>
-      <c r="S180" s="92"/>
-      <c r="T180" s="131"/>
-      <c r="U180" s="95"/>
-      <c r="V180" s="92"/>
-      <c r="W180" s="131"/>
-      <c r="X180" s="150"/>
+      <c r="B180" s="181"/>
+      <c r="C180" s="167"/>
+      <c r="D180" s="148"/>
+      <c r="E180" s="168"/>
+      <c r="F180" s="151"/>
+      <c r="G180" s="148"/>
+      <c r="H180" s="168"/>
+      <c r="I180" s="151"/>
+      <c r="J180" s="148"/>
+      <c r="K180" s="168"/>
+      <c r="L180" s="151"/>
+      <c r="M180" s="148"/>
+      <c r="N180" s="168"/>
+      <c r="O180" s="151"/>
+      <c r="P180" s="148"/>
+      <c r="Q180" s="168"/>
+      <c r="R180" s="151"/>
+      <c r="S180" s="148"/>
+      <c r="T180" s="168"/>
+      <c r="U180" s="151"/>
+      <c r="V180" s="148"/>
+      <c r="W180" s="168"/>
+      <c r="X180" s="87"/>
       <c r="Y180" s="2"/>
       <c r="Z180" s="2"/>
       <c r="AA180" s="2"/>
@@ -9391,31 +9353,31 @@
     </row>
     <row r="181" spans="1:30" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="4"/>
-      <c r="B181" s="133" t="s">
+      <c r="B181" s="182" t="s">
         <v>27</v>
       </c>
-      <c r="C181" s="134"/>
-      <c r="D181" s="105"/>
-      <c r="E181" s="106"/>
-      <c r="F181" s="135"/>
-      <c r="G181" s="105"/>
-      <c r="H181" s="106"/>
-      <c r="I181" s="135"/>
-      <c r="J181" s="105"/>
-      <c r="K181" s="106"/>
-      <c r="L181" s="135"/>
-      <c r="M181" s="105"/>
-      <c r="N181" s="106"/>
-      <c r="O181" s="135"/>
-      <c r="P181" s="105"/>
-      <c r="Q181" s="106"/>
-      <c r="R181" s="135"/>
-      <c r="S181" s="105"/>
-      <c r="T181" s="106"/>
-      <c r="U181" s="135"/>
-      <c r="V181" s="105"/>
-      <c r="W181" s="106"/>
-      <c r="X181" s="150"/>
+      <c r="C181" s="169"/>
+      <c r="D181" s="157"/>
+      <c r="E181" s="158"/>
+      <c r="F181" s="170"/>
+      <c r="G181" s="157"/>
+      <c r="H181" s="158"/>
+      <c r="I181" s="170"/>
+      <c r="J181" s="157"/>
+      <c r="K181" s="158"/>
+      <c r="L181" s="170"/>
+      <c r="M181" s="157"/>
+      <c r="N181" s="158"/>
+      <c r="O181" s="170"/>
+      <c r="P181" s="157"/>
+      <c r="Q181" s="158"/>
+      <c r="R181" s="170"/>
+      <c r="S181" s="157"/>
+      <c r="T181" s="158"/>
+      <c r="U181" s="170"/>
+      <c r="V181" s="157"/>
+      <c r="W181" s="158"/>
+      <c r="X181" s="87"/>
       <c r="Y181" s="2"/>
       <c r="Z181" s="2"/>
       <c r="AA181" s="2"/>
@@ -9425,31 +9387,31 @@
     </row>
     <row r="182" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="4"/>
-      <c r="B182" s="139" t="s">
+      <c r="B182" s="183" t="s">
         <v>28</v>
       </c>
-      <c r="C182" s="155"/>
-      <c r="D182" s="141"/>
-      <c r="E182" s="142"/>
-      <c r="F182" s="144"/>
-      <c r="G182" s="141"/>
-      <c r="H182" s="142"/>
-      <c r="I182" s="144"/>
-      <c r="J182" s="141"/>
-      <c r="K182" s="142"/>
-      <c r="L182" s="144"/>
-      <c r="M182" s="141"/>
-      <c r="N182" s="142"/>
-      <c r="O182" s="144"/>
-      <c r="P182" s="141"/>
-      <c r="Q182" s="142"/>
-      <c r="R182" s="144"/>
-      <c r="S182" s="141"/>
-      <c r="T182" s="142"/>
-      <c r="U182" s="144"/>
-      <c r="V182" s="141"/>
-      <c r="W182" s="142"/>
-      <c r="X182" s="150"/>
+      <c r="C182" s="171"/>
+      <c r="D182" s="172"/>
+      <c r="E182" s="173"/>
+      <c r="F182" s="174"/>
+      <c r="G182" s="172"/>
+      <c r="H182" s="173"/>
+      <c r="I182" s="174"/>
+      <c r="J182" s="172"/>
+      <c r="K182" s="173"/>
+      <c r="L182" s="174"/>
+      <c r="M182" s="172"/>
+      <c r="N182" s="173"/>
+      <c r="O182" s="174"/>
+      <c r="P182" s="172"/>
+      <c r="Q182" s="173"/>
+      <c r="R182" s="174"/>
+      <c r="S182" s="172"/>
+      <c r="T182" s="173"/>
+      <c r="U182" s="174"/>
+      <c r="V182" s="172"/>
+      <c r="W182" s="173"/>
+      <c r="X182" s="87"/>
       <c r="Y182" s="2"/>
       <c r="Z182" s="2"/>
       <c r="AA182" s="2"/>
@@ -9459,29 +9421,29 @@
     </row>
     <row r="183" spans="1:30" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="4"/>
-      <c r="B183" s="147"/>
-      <c r="C183" s="174"/>
-      <c r="D183" s="175"/>
-      <c r="E183" s="176"/>
-      <c r="F183" s="177"/>
-      <c r="G183" s="175"/>
-      <c r="H183" s="176"/>
-      <c r="I183" s="177"/>
-      <c r="J183" s="175"/>
-      <c r="K183" s="176"/>
-      <c r="L183" s="177"/>
-      <c r="M183" s="175"/>
-      <c r="N183" s="176"/>
-      <c r="O183" s="177"/>
-      <c r="P183" s="175"/>
-      <c r="Q183" s="176"/>
-      <c r="R183" s="177"/>
-      <c r="S183" s="175"/>
-      <c r="T183" s="176"/>
-      <c r="U183" s="179"/>
-      <c r="V183" s="180"/>
-      <c r="W183" s="181"/>
-      <c r="X183" s="150"/>
+      <c r="B183" s="84"/>
+      <c r="C183" s="118"/>
+      <c r="D183" s="116"/>
+      <c r="E183" s="117"/>
+      <c r="F183" s="115"/>
+      <c r="G183" s="116"/>
+      <c r="H183" s="117"/>
+      <c r="I183" s="115"/>
+      <c r="J183" s="116"/>
+      <c r="K183" s="117"/>
+      <c r="L183" s="115"/>
+      <c r="M183" s="116"/>
+      <c r="N183" s="117"/>
+      <c r="O183" s="115"/>
+      <c r="P183" s="116"/>
+      <c r="Q183" s="117"/>
+      <c r="R183" s="115"/>
+      <c r="S183" s="116"/>
+      <c r="T183" s="117"/>
+      <c r="U183" s="109"/>
+      <c r="V183" s="110"/>
+      <c r="W183" s="111"/>
+      <c r="X183" s="87"/>
       <c r="Y183" s="2"/>
       <c r="Z183" s="2"/>
       <c r="AA183" s="2"/>
@@ -9492,7 +9454,7 @@
     <row r="184" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="4"/>
       <c r="B184" s="9"/>
-      <c r="C184" s="148" t="s">
+      <c r="C184" s="85" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="15" t="s">
@@ -9555,7 +9517,7 @@
       <c r="W184" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="X184" s="150"/>
+      <c r="X184" s="87"/>
       <c r="Y184" s="2"/>
       <c r="Z184" s="2"/>
       <c r="AA184" s="2"/>
@@ -9587,7 +9549,7 @@
       <c r="U185" s="23"/>
       <c r="V185" s="24"/>
       <c r="W185" s="25"/>
-      <c r="X185" s="150"/>
+      <c r="X185" s="87"/>
       <c r="Y185" s="2"/>
       <c r="Z185" s="2"/>
       <c r="AA185" s="2"/>
@@ -9619,7 +9581,7 @@
       <c r="U186" s="32"/>
       <c r="V186" s="33"/>
       <c r="W186" s="34"/>
-      <c r="X186" s="150"/>
+      <c r="X186" s="87"/>
       <c r="Y186" s="2"/>
       <c r="Z186" s="2"/>
       <c r="AA186" s="2"/>
@@ -9651,7 +9613,7 @@
       <c r="U187" s="32"/>
       <c r="V187" s="33"/>
       <c r="W187" s="34"/>
-      <c r="X187" s="150"/>
+      <c r="X187" s="87"/>
       <c r="Y187" s="2"/>
       <c r="Z187" s="2"/>
       <c r="AA187" s="2"/>
@@ -9683,7 +9645,7 @@
       <c r="U188" s="32"/>
       <c r="V188" s="33"/>
       <c r="W188" s="34"/>
-      <c r="X188" s="150"/>
+      <c r="X188" s="87"/>
       <c r="Y188" s="2"/>
       <c r="Z188" s="2"/>
       <c r="AA188" s="2"/>
@@ -9715,7 +9677,7 @@
       <c r="U189" s="32"/>
       <c r="V189" s="33"/>
       <c r="W189" s="34"/>
-      <c r="X189" s="150"/>
+      <c r="X189" s="87"/>
       <c r="Y189" s="2"/>
       <c r="Z189" s="2"/>
       <c r="AA189" s="2"/>
@@ -9747,7 +9709,7 @@
       <c r="U190" s="32"/>
       <c r="V190" s="33"/>
       <c r="W190" s="34"/>
-      <c r="X190" s="150"/>
+      <c r="X190" s="87"/>
       <c r="Y190" s="2"/>
       <c r="Z190" s="2"/>
       <c r="AA190" s="2"/>
@@ -9779,7 +9741,7 @@
       <c r="U191" s="32"/>
       <c r="V191" s="33"/>
       <c r="W191" s="34"/>
-      <c r="X191" s="150"/>
+      <c r="X191" s="87"/>
       <c r="Y191" s="2"/>
       <c r="Z191" s="2"/>
       <c r="AA191" s="2"/>
@@ -9811,7 +9773,7 @@
       <c r="U192" s="32"/>
       <c r="V192" s="33"/>
       <c r="W192" s="34"/>
-      <c r="X192" s="150"/>
+      <c r="X192" s="87"/>
       <c r="Y192" s="2"/>
       <c r="Z192" s="2"/>
       <c r="AA192" s="2"/>
@@ -9843,7 +9805,7 @@
       <c r="U193" s="32"/>
       <c r="V193" s="33"/>
       <c r="W193" s="34"/>
-      <c r="X193" s="150"/>
+      <c r="X193" s="87"/>
       <c r="Y193" s="2"/>
       <c r="Z193" s="2"/>
       <c r="AA193" s="2"/>
@@ -9875,7 +9837,7 @@
       <c r="U194" s="32"/>
       <c r="V194" s="33"/>
       <c r="W194" s="34"/>
-      <c r="X194" s="150"/>
+      <c r="X194" s="87"/>
       <c r="Y194" s="2"/>
       <c r="Z194" s="2"/>
       <c r="AA194" s="2"/>
@@ -9907,7 +9869,7 @@
       <c r="U195" s="32"/>
       <c r="V195" s="33"/>
       <c r="W195" s="34"/>
-      <c r="X195" s="150"/>
+      <c r="X195" s="87"/>
       <c r="Y195" s="2"/>
       <c r="Z195" s="2"/>
       <c r="AA195" s="2"/>
@@ -9920,7 +9882,7 @@
       <c r="B196" s="26"/>
       <c r="C196" s="37"/>
       <c r="D196" s="38"/>
-      <c r="E196" s="151"/>
+      <c r="E196" s="88"/>
       <c r="F196" s="40"/>
       <c r="G196" s="38"/>
       <c r="H196" s="41"/>
@@ -9939,7 +9901,7 @@
       <c r="U196" s="43"/>
       <c r="V196" s="44"/>
       <c r="W196" s="45"/>
-      <c r="X196" s="150"/>
+      <c r="X196" s="87"/>
       <c r="Y196" s="2"/>
       <c r="Z196" s="2"/>
       <c r="AA196" s="2"/>
@@ -9971,7 +9933,7 @@
       <c r="U197" s="54"/>
       <c r="V197" s="55"/>
       <c r="W197" s="56"/>
-      <c r="X197" s="150"/>
+      <c r="X197" s="87"/>
       <c r="Y197" s="2"/>
       <c r="Z197" s="2"/>
       <c r="AA197" s="2"/>
@@ -10045,7 +10007,7 @@
       <c r="W198" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="X198" s="150"/>
+      <c r="X198" s="87"/>
       <c r="Y198" s="2"/>
       <c r="Z198" s="2"/>
       <c r="AA198" s="2"/>
@@ -10055,31 +10017,31 @@
     </row>
     <row r="199" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="4"/>
-      <c r="B199" s="185" t="s">
+      <c r="B199" s="176" t="s">
         <v>14</v>
       </c>
-      <c r="C199" s="67"/>
-      <c r="D199" s="68"/>
-      <c r="E199" s="69"/>
-      <c r="F199" s="70"/>
-      <c r="G199" s="190"/>
-      <c r="H199" s="69"/>
-      <c r="I199" s="70"/>
-      <c r="J199" s="71"/>
-      <c r="K199" s="69"/>
-      <c r="L199" s="70"/>
-      <c r="M199" s="68"/>
-      <c r="N199" s="69"/>
-      <c r="O199" s="70"/>
-      <c r="P199" s="72"/>
-      <c r="Q199" s="69"/>
-      <c r="R199" s="70"/>
-      <c r="S199" s="68"/>
-      <c r="T199" s="69"/>
-      <c r="U199" s="70"/>
-      <c r="V199" s="68"/>
-      <c r="W199" s="69"/>
-      <c r="X199" s="150"/>
+      <c r="C199" s="131"/>
+      <c r="D199" s="132"/>
+      <c r="E199" s="133"/>
+      <c r="F199" s="134"/>
+      <c r="G199" s="135"/>
+      <c r="H199" s="133"/>
+      <c r="I199" s="134"/>
+      <c r="J199" s="136"/>
+      <c r="K199" s="133"/>
+      <c r="L199" s="134"/>
+      <c r="M199" s="132"/>
+      <c r="N199" s="133"/>
+      <c r="O199" s="134"/>
+      <c r="P199" s="137"/>
+      <c r="Q199" s="133"/>
+      <c r="R199" s="134"/>
+      <c r="S199" s="132"/>
+      <c r="T199" s="133"/>
+      <c r="U199" s="134"/>
+      <c r="V199" s="132"/>
+      <c r="W199" s="133"/>
+      <c r="X199" s="87"/>
       <c r="Y199" s="2"/>
       <c r="Z199" s="2"/>
       <c r="AA199" s="2"/>
@@ -10089,29 +10051,29 @@
     </row>
     <row r="200" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="4"/>
-      <c r="B200" s="186"/>
-      <c r="C200" s="78"/>
-      <c r="D200" s="79"/>
-      <c r="E200" s="80"/>
-      <c r="F200" s="81"/>
-      <c r="G200" s="191"/>
-      <c r="H200" s="80"/>
-      <c r="I200" s="81"/>
-      <c r="J200" s="79"/>
-      <c r="K200" s="80"/>
-      <c r="L200" s="82"/>
-      <c r="M200" s="79"/>
-      <c r="N200" s="83"/>
-      <c r="O200" s="81"/>
-      <c r="P200" s="84"/>
-      <c r="Q200" s="80"/>
-      <c r="R200" s="82"/>
-      <c r="S200" s="79"/>
-      <c r="T200" s="80"/>
-      <c r="U200" s="81"/>
-      <c r="V200" s="79"/>
-      <c r="W200" s="83"/>
-      <c r="X200" s="150"/>
+      <c r="B200" s="177"/>
+      <c r="C200" s="138"/>
+      <c r="D200" s="139"/>
+      <c r="E200" s="140"/>
+      <c r="F200" s="141"/>
+      <c r="G200" s="142"/>
+      <c r="H200" s="140"/>
+      <c r="I200" s="141"/>
+      <c r="J200" s="139"/>
+      <c r="K200" s="140"/>
+      <c r="L200" s="143"/>
+      <c r="M200" s="139"/>
+      <c r="N200" s="144"/>
+      <c r="O200" s="141"/>
+      <c r="P200" s="145"/>
+      <c r="Q200" s="140"/>
+      <c r="R200" s="143"/>
+      <c r="S200" s="139"/>
+      <c r="T200" s="140"/>
+      <c r="U200" s="141"/>
+      <c r="V200" s="139"/>
+      <c r="W200" s="144"/>
+      <c r="X200" s="87"/>
       <c r="Y200" s="2"/>
       <c r="Z200" s="2"/>
       <c r="AA200" s="2"/>
@@ -10121,29 +10083,29 @@
     </row>
     <row r="201" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="4"/>
-      <c r="B201" s="186"/>
-      <c r="C201" s="78"/>
-      <c r="D201" s="79"/>
-      <c r="E201" s="80"/>
-      <c r="F201" s="81"/>
-      <c r="G201" s="191"/>
-      <c r="H201" s="80"/>
-      <c r="I201" s="81"/>
-      <c r="J201" s="79"/>
-      <c r="K201" s="80"/>
-      <c r="L201" s="82"/>
-      <c r="M201" s="79"/>
-      <c r="N201" s="83"/>
-      <c r="O201" s="81"/>
-      <c r="P201" s="84"/>
-      <c r="Q201" s="83"/>
-      <c r="R201" s="81"/>
-      <c r="S201" s="79"/>
-      <c r="T201" s="83"/>
-      <c r="U201" s="81"/>
-      <c r="V201" s="79"/>
-      <c r="W201" s="83"/>
-      <c r="X201" s="150"/>
+      <c r="B201" s="177"/>
+      <c r="C201" s="138"/>
+      <c r="D201" s="139"/>
+      <c r="E201" s="140"/>
+      <c r="F201" s="141"/>
+      <c r="G201" s="142"/>
+      <c r="H201" s="140"/>
+      <c r="I201" s="141"/>
+      <c r="J201" s="139"/>
+      <c r="K201" s="140"/>
+      <c r="L201" s="143"/>
+      <c r="M201" s="139"/>
+      <c r="N201" s="144"/>
+      <c r="O201" s="141"/>
+      <c r="P201" s="145"/>
+      <c r="Q201" s="144"/>
+      <c r="R201" s="141"/>
+      <c r="S201" s="139"/>
+      <c r="T201" s="144"/>
+      <c r="U201" s="141"/>
+      <c r="V201" s="139"/>
+      <c r="W201" s="144"/>
+      <c r="X201" s="87"/>
       <c r="Y201" s="2"/>
       <c r="Z201" s="2"/>
       <c r="AA201" s="2"/>
@@ -10153,29 +10115,29 @@
     </row>
     <row r="202" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="4"/>
-      <c r="B202" s="186"/>
-      <c r="C202" s="89"/>
-      <c r="D202" s="79"/>
-      <c r="E202" s="83"/>
-      <c r="F202" s="82"/>
-      <c r="G202" s="79"/>
-      <c r="H202" s="83"/>
-      <c r="I202" s="82"/>
-      <c r="J202" s="79"/>
-      <c r="K202" s="83"/>
-      <c r="L202" s="82"/>
-      <c r="M202" s="79"/>
-      <c r="N202" s="83"/>
-      <c r="O202" s="82"/>
-      <c r="P202" s="84"/>
-      <c r="Q202" s="83"/>
-      <c r="R202" s="82"/>
-      <c r="S202" s="79"/>
-      <c r="T202" s="83"/>
-      <c r="U202" s="81"/>
-      <c r="V202" s="79"/>
-      <c r="W202" s="83"/>
-      <c r="X202" s="150"/>
+      <c r="B202" s="177"/>
+      <c r="C202" s="146"/>
+      <c r="D202" s="139"/>
+      <c r="E202" s="144"/>
+      <c r="F202" s="143"/>
+      <c r="G202" s="139"/>
+      <c r="H202" s="144"/>
+      <c r="I202" s="143"/>
+      <c r="J202" s="139"/>
+      <c r="K202" s="144"/>
+      <c r="L202" s="143"/>
+      <c r="M202" s="139"/>
+      <c r="N202" s="144"/>
+      <c r="O202" s="143"/>
+      <c r="P202" s="145"/>
+      <c r="Q202" s="144"/>
+      <c r="R202" s="143"/>
+      <c r="S202" s="139"/>
+      <c r="T202" s="144"/>
+      <c r="U202" s="141"/>
+      <c r="V202" s="139"/>
+      <c r="W202" s="144"/>
+      <c r="X202" s="87"/>
       <c r="Y202" s="2"/>
       <c r="Z202" s="2"/>
       <c r="AA202" s="2"/>
@@ -10185,29 +10147,29 @@
     </row>
     <row r="203" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="4"/>
-      <c r="B203" s="189"/>
-      <c r="C203" s="91"/>
-      <c r="D203" s="92"/>
-      <c r="E203" s="93"/>
-      <c r="F203" s="94"/>
-      <c r="G203" s="92"/>
-      <c r="H203" s="93"/>
-      <c r="I203" s="95"/>
-      <c r="J203" s="92"/>
-      <c r="K203" s="93"/>
-      <c r="L203" s="96"/>
-      <c r="M203" s="92"/>
-      <c r="N203" s="93"/>
-      <c r="O203" s="94"/>
-      <c r="P203" s="97"/>
-      <c r="Q203" s="93"/>
-      <c r="R203" s="95"/>
-      <c r="S203" s="92"/>
-      <c r="T203" s="93"/>
-      <c r="U203" s="95"/>
-      <c r="V203" s="92"/>
-      <c r="W203" s="93"/>
-      <c r="X203" s="150"/>
+      <c r="B203" s="178"/>
+      <c r="C203" s="147"/>
+      <c r="D203" s="148"/>
+      <c r="E203" s="149"/>
+      <c r="F203" s="150"/>
+      <c r="G203" s="148"/>
+      <c r="H203" s="149"/>
+      <c r="I203" s="151"/>
+      <c r="J203" s="148"/>
+      <c r="K203" s="149"/>
+      <c r="L203" s="152"/>
+      <c r="M203" s="148"/>
+      <c r="N203" s="149"/>
+      <c r="O203" s="150"/>
+      <c r="P203" s="153"/>
+      <c r="Q203" s="149"/>
+      <c r="R203" s="151"/>
+      <c r="S203" s="148"/>
+      <c r="T203" s="149"/>
+      <c r="U203" s="151"/>
+      <c r="V203" s="148"/>
+      <c r="W203" s="149"/>
+      <c r="X203" s="87"/>
       <c r="Y203" s="2"/>
       <c r="Z203" s="2"/>
       <c r="AA203" s="2"/>
@@ -10217,31 +10179,31 @@
     </row>
     <row r="204" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="4"/>
-      <c r="B204" s="101" t="s">
+      <c r="B204" s="179" t="s">
         <v>20</v>
       </c>
-      <c r="C204" s="102"/>
-      <c r="D204" s="103"/>
-      <c r="E204" s="104"/>
-      <c r="F204" s="102"/>
-      <c r="G204" s="103"/>
-      <c r="H204" s="104"/>
-      <c r="I204" s="102"/>
-      <c r="J204" s="103"/>
-      <c r="K204" s="104"/>
-      <c r="L204" s="102"/>
-      <c r="M204" s="103"/>
-      <c r="N204" s="104"/>
-      <c r="O204" s="102"/>
-      <c r="P204" s="103"/>
-      <c r="Q204" s="104"/>
-      <c r="R204" s="102"/>
-      <c r="S204" s="105"/>
-      <c r="T204" s="106"/>
-      <c r="U204" s="102"/>
-      <c r="V204" s="105"/>
-      <c r="W204" s="106"/>
-      <c r="X204" s="150"/>
+      <c r="C204" s="154"/>
+      <c r="D204" s="155"/>
+      <c r="E204" s="156"/>
+      <c r="F204" s="154"/>
+      <c r="G204" s="155"/>
+      <c r="H204" s="156"/>
+      <c r="I204" s="154"/>
+      <c r="J204" s="155"/>
+      <c r="K204" s="156"/>
+      <c r="L204" s="154"/>
+      <c r="M204" s="155"/>
+      <c r="N204" s="156"/>
+      <c r="O204" s="154"/>
+      <c r="P204" s="155"/>
+      <c r="Q204" s="156"/>
+      <c r="R204" s="154"/>
+      <c r="S204" s="157"/>
+      <c r="T204" s="158"/>
+      <c r="U204" s="154"/>
+      <c r="V204" s="157"/>
+      <c r="W204" s="158"/>
+      <c r="X204" s="87"/>
       <c r="Y204" s="2"/>
       <c r="Z204" s="2"/>
       <c r="AA204" s="2"/>
@@ -10251,31 +10213,31 @@
     </row>
     <row r="205" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="4"/>
-      <c r="B205" s="185" t="s">
+      <c r="B205" s="176" t="s">
         <v>29</v>
       </c>
-      <c r="C205" s="67"/>
-      <c r="D205" s="108"/>
-      <c r="E205" s="109"/>
-      <c r="F205" s="110"/>
-      <c r="G205" s="68"/>
-      <c r="H205" s="109"/>
-      <c r="I205" s="110"/>
-      <c r="J205" s="68"/>
-      <c r="K205" s="109"/>
-      <c r="L205" s="110"/>
-      <c r="M205" s="68"/>
-      <c r="N205" s="109"/>
-      <c r="O205" s="110"/>
-      <c r="P205" s="68"/>
-      <c r="Q205" s="109"/>
-      <c r="R205" s="110"/>
-      <c r="S205" s="68"/>
-      <c r="T205" s="109"/>
-      <c r="U205" s="110"/>
-      <c r="V205" s="68"/>
-      <c r="W205" s="152"/>
-      <c r="X205" s="150"/>
+      <c r="C205" s="131"/>
+      <c r="D205" s="159"/>
+      <c r="E205" s="160"/>
+      <c r="F205" s="161"/>
+      <c r="G205" s="132"/>
+      <c r="H205" s="160"/>
+      <c r="I205" s="161"/>
+      <c r="J205" s="132"/>
+      <c r="K205" s="160"/>
+      <c r="L205" s="161"/>
+      <c r="M205" s="132"/>
+      <c r="N205" s="160"/>
+      <c r="O205" s="161"/>
+      <c r="P205" s="132"/>
+      <c r="Q205" s="160"/>
+      <c r="R205" s="161"/>
+      <c r="S205" s="132"/>
+      <c r="T205" s="160"/>
+      <c r="U205" s="161"/>
+      <c r="V205" s="132"/>
+      <c r="W205" s="175"/>
+      <c r="X205" s="87"/>
       <c r="Y205" s="2"/>
       <c r="Z205" s="2"/>
       <c r="AA205" s="2"/>
@@ -10285,29 +10247,29 @@
     </row>
     <row r="206" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="4"/>
-      <c r="B206" s="186"/>
-      <c r="C206" s="78"/>
-      <c r="D206" s="79"/>
-      <c r="E206" s="113"/>
-      <c r="F206" s="81"/>
-      <c r="G206" s="79"/>
-      <c r="H206" s="113"/>
-      <c r="I206" s="81"/>
-      <c r="J206" s="114"/>
-      <c r="K206" s="113"/>
-      <c r="L206" s="81"/>
-      <c r="M206" s="79"/>
-      <c r="N206" s="113"/>
-      <c r="O206" s="81"/>
-      <c r="P206" s="79"/>
-      <c r="Q206" s="113"/>
-      <c r="R206" s="81"/>
-      <c r="S206" s="114"/>
-      <c r="T206" s="113"/>
-      <c r="U206" s="81"/>
-      <c r="V206" s="79"/>
-      <c r="W206" s="113"/>
-      <c r="X206" s="150"/>
+      <c r="B206" s="177"/>
+      <c r="C206" s="138"/>
+      <c r="D206" s="139"/>
+      <c r="E206" s="162"/>
+      <c r="F206" s="141"/>
+      <c r="G206" s="139"/>
+      <c r="H206" s="162"/>
+      <c r="I206" s="141"/>
+      <c r="J206" s="163"/>
+      <c r="K206" s="162"/>
+      <c r="L206" s="141"/>
+      <c r="M206" s="139"/>
+      <c r="N206" s="162"/>
+      <c r="O206" s="141"/>
+      <c r="P206" s="139"/>
+      <c r="Q206" s="162"/>
+      <c r="R206" s="141"/>
+      <c r="S206" s="163"/>
+      <c r="T206" s="162"/>
+      <c r="U206" s="141"/>
+      <c r="V206" s="139"/>
+      <c r="W206" s="162"/>
+      <c r="X206" s="87"/>
       <c r="Y206" s="2"/>
       <c r="Z206" s="2"/>
       <c r="AA206" s="2"/>
@@ -10317,29 +10279,29 @@
     </row>
     <row r="207" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="4"/>
-      <c r="B207" s="186"/>
-      <c r="C207" s="78"/>
-      <c r="D207" s="79"/>
-      <c r="E207" s="113"/>
-      <c r="F207" s="81"/>
-      <c r="G207" s="79"/>
-      <c r="H207" s="113"/>
-      <c r="I207" s="81"/>
-      <c r="J207" s="114"/>
-      <c r="K207" s="113"/>
-      <c r="L207" s="81"/>
-      <c r="M207" s="79"/>
-      <c r="N207" s="113"/>
-      <c r="O207" s="81"/>
-      <c r="P207" s="79"/>
-      <c r="Q207" s="113"/>
-      <c r="R207" s="81"/>
-      <c r="S207" s="114"/>
-      <c r="T207" s="113"/>
-      <c r="U207" s="81"/>
-      <c r="V207" s="79"/>
-      <c r="W207" s="113"/>
-      <c r="X207" s="150"/>
+      <c r="B207" s="177"/>
+      <c r="C207" s="138"/>
+      <c r="D207" s="139"/>
+      <c r="E207" s="162"/>
+      <c r="F207" s="141"/>
+      <c r="G207" s="139"/>
+      <c r="H207" s="162"/>
+      <c r="I207" s="141"/>
+      <c r="J207" s="163"/>
+      <c r="K207" s="162"/>
+      <c r="L207" s="141"/>
+      <c r="M207" s="139"/>
+      <c r="N207" s="162"/>
+      <c r="O207" s="141"/>
+      <c r="P207" s="139"/>
+      <c r="Q207" s="162"/>
+      <c r="R207" s="141"/>
+      <c r="S207" s="163"/>
+      <c r="T207" s="162"/>
+      <c r="U207" s="141"/>
+      <c r="V207" s="139"/>
+      <c r="W207" s="162"/>
+      <c r="X207" s="87"/>
       <c r="Y207" s="2"/>
       <c r="Z207" s="2"/>
       <c r="AA207" s="2"/>
@@ -10349,29 +10311,29 @@
     </row>
     <row r="208" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="4"/>
-      <c r="B208" s="186"/>
-      <c r="C208" s="78"/>
-      <c r="D208" s="79"/>
-      <c r="E208" s="80"/>
-      <c r="F208" s="81"/>
-      <c r="G208" s="114"/>
-      <c r="H208" s="80"/>
-      <c r="I208" s="81"/>
-      <c r="J208" s="79"/>
-      <c r="K208" s="80"/>
-      <c r="L208" s="81"/>
-      <c r="M208" s="79"/>
-      <c r="N208" s="80"/>
-      <c r="O208" s="81"/>
-      <c r="P208" s="79"/>
-      <c r="Q208" s="80"/>
-      <c r="R208" s="81"/>
-      <c r="S208" s="79"/>
-      <c r="T208" s="80"/>
-      <c r="U208" s="81"/>
-      <c r="V208" s="79"/>
-      <c r="W208" s="113"/>
-      <c r="X208" s="150"/>
+      <c r="B208" s="177"/>
+      <c r="C208" s="138"/>
+      <c r="D208" s="139"/>
+      <c r="E208" s="140"/>
+      <c r="F208" s="141"/>
+      <c r="G208" s="163"/>
+      <c r="H208" s="140"/>
+      <c r="I208" s="141"/>
+      <c r="J208" s="139"/>
+      <c r="K208" s="140"/>
+      <c r="L208" s="141"/>
+      <c r="M208" s="139"/>
+      <c r="N208" s="140"/>
+      <c r="O208" s="141"/>
+      <c r="P208" s="139"/>
+      <c r="Q208" s="140"/>
+      <c r="R208" s="141"/>
+      <c r="S208" s="139"/>
+      <c r="T208" s="140"/>
+      <c r="U208" s="141"/>
+      <c r="V208" s="139"/>
+      <c r="W208" s="162"/>
+      <c r="X208" s="87"/>
       <c r="Y208" s="2"/>
       <c r="Z208" s="2"/>
       <c r="AA208" s="2"/>
@@ -10381,29 +10343,29 @@
     </row>
     <row r="209" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="4"/>
-      <c r="B209" s="186"/>
-      <c r="C209" s="89"/>
-      <c r="D209" s="79"/>
-      <c r="E209" s="113"/>
-      <c r="F209" s="82"/>
-      <c r="G209" s="79"/>
-      <c r="H209" s="113"/>
-      <c r="I209" s="82"/>
-      <c r="J209" s="114"/>
-      <c r="K209" s="113"/>
-      <c r="L209" s="82"/>
-      <c r="M209" s="79"/>
-      <c r="N209" s="113"/>
-      <c r="O209" s="82"/>
-      <c r="P209" s="79"/>
-      <c r="Q209" s="113"/>
-      <c r="R209" s="82"/>
-      <c r="S209" s="114"/>
-      <c r="T209" s="113"/>
-      <c r="U209" s="82"/>
-      <c r="V209" s="79"/>
-      <c r="W209" s="113"/>
-      <c r="X209" s="150"/>
+      <c r="B209" s="177"/>
+      <c r="C209" s="146"/>
+      <c r="D209" s="139"/>
+      <c r="E209" s="162"/>
+      <c r="F209" s="143"/>
+      <c r="G209" s="139"/>
+      <c r="H209" s="162"/>
+      <c r="I209" s="143"/>
+      <c r="J209" s="163"/>
+      <c r="K209" s="162"/>
+      <c r="L209" s="143"/>
+      <c r="M209" s="139"/>
+      <c r="N209" s="162"/>
+      <c r="O209" s="143"/>
+      <c r="P209" s="139"/>
+      <c r="Q209" s="162"/>
+      <c r="R209" s="143"/>
+      <c r="S209" s="163"/>
+      <c r="T209" s="162"/>
+      <c r="U209" s="143"/>
+      <c r="V209" s="139"/>
+      <c r="W209" s="162"/>
+      <c r="X209" s="87"/>
       <c r="Y209" s="2"/>
       <c r="Z209" s="2"/>
       <c r="AA209" s="2"/>
@@ -10413,29 +10375,29 @@
     </row>
     <row r="210" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="4"/>
-      <c r="B210" s="186"/>
-      <c r="C210" s="89"/>
-      <c r="D210" s="79"/>
-      <c r="E210" s="113"/>
-      <c r="F210" s="82"/>
-      <c r="G210" s="79"/>
-      <c r="H210" s="113"/>
-      <c r="I210" s="82"/>
-      <c r="J210" s="114"/>
-      <c r="K210" s="113"/>
-      <c r="L210" s="82"/>
-      <c r="M210" s="79"/>
-      <c r="N210" s="113"/>
-      <c r="O210" s="82"/>
-      <c r="P210" s="79"/>
-      <c r="Q210" s="113"/>
-      <c r="R210" s="82"/>
-      <c r="S210" s="114"/>
-      <c r="T210" s="113"/>
-      <c r="U210" s="81"/>
-      <c r="V210" s="79"/>
-      <c r="W210" s="113"/>
-      <c r="X210" s="150"/>
+      <c r="B210" s="177"/>
+      <c r="C210" s="146"/>
+      <c r="D210" s="139"/>
+      <c r="E210" s="162"/>
+      <c r="F210" s="143"/>
+      <c r="G210" s="139"/>
+      <c r="H210" s="162"/>
+      <c r="I210" s="143"/>
+      <c r="J210" s="163"/>
+      <c r="K210" s="162"/>
+      <c r="L210" s="143"/>
+      <c r="M210" s="139"/>
+      <c r="N210" s="162"/>
+      <c r="O210" s="143"/>
+      <c r="P210" s="139"/>
+      <c r="Q210" s="162"/>
+      <c r="R210" s="143"/>
+      <c r="S210" s="163"/>
+      <c r="T210" s="162"/>
+      <c r="U210" s="141"/>
+      <c r="V210" s="139"/>
+      <c r="W210" s="162"/>
+      <c r="X210" s="87"/>
       <c r="Y210" s="2"/>
       <c r="Z210" s="2"/>
       <c r="AA210" s="2"/>
@@ -10445,29 +10407,29 @@
     </row>
     <row r="211" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="4"/>
-      <c r="B211" s="186"/>
-      <c r="C211" s="78"/>
-      <c r="D211" s="79"/>
-      <c r="E211" s="113"/>
-      <c r="F211" s="81"/>
-      <c r="G211" s="79"/>
-      <c r="H211" s="113"/>
-      <c r="I211" s="82"/>
-      <c r="J211" s="114"/>
-      <c r="K211" s="113"/>
-      <c r="L211" s="82"/>
-      <c r="M211" s="79"/>
-      <c r="N211" s="113"/>
-      <c r="O211" s="81"/>
-      <c r="P211" s="79"/>
-      <c r="Q211" s="113"/>
-      <c r="R211" s="81"/>
-      <c r="S211" s="114"/>
-      <c r="T211" s="113"/>
-      <c r="U211" s="82"/>
-      <c r="V211" s="79"/>
-      <c r="W211" s="113"/>
-      <c r="X211" s="150"/>
+      <c r="B211" s="177"/>
+      <c r="C211" s="138"/>
+      <c r="D211" s="139"/>
+      <c r="E211" s="162"/>
+      <c r="F211" s="141"/>
+      <c r="G211" s="139"/>
+      <c r="H211" s="162"/>
+      <c r="I211" s="143"/>
+      <c r="J211" s="163"/>
+      <c r="K211" s="162"/>
+      <c r="L211" s="143"/>
+      <c r="M211" s="139"/>
+      <c r="N211" s="162"/>
+      <c r="O211" s="141"/>
+      <c r="P211" s="139"/>
+      <c r="Q211" s="162"/>
+      <c r="R211" s="141"/>
+      <c r="S211" s="163"/>
+      <c r="T211" s="162"/>
+      <c r="U211" s="143"/>
+      <c r="V211" s="139"/>
+      <c r="W211" s="162"/>
+      <c r="X211" s="87"/>
       <c r="Y211" s="2"/>
       <c r="Z211" s="2"/>
       <c r="AA211" s="2"/>
@@ -10477,29 +10439,29 @@
     </row>
     <row r="212" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="4"/>
-      <c r="B212" s="186"/>
-      <c r="C212" s="78"/>
-      <c r="D212" s="79"/>
-      <c r="E212" s="80"/>
-      <c r="F212" s="81"/>
-      <c r="G212" s="79"/>
-      <c r="H212" s="80"/>
-      <c r="I212" s="81"/>
-      <c r="J212" s="121"/>
-      <c r="K212" s="80"/>
-      <c r="L212" s="81"/>
-      <c r="M212" s="79"/>
-      <c r="N212" s="80"/>
-      <c r="O212" s="81"/>
-      <c r="P212" s="79"/>
-      <c r="Q212" s="80"/>
-      <c r="R212" s="81"/>
-      <c r="S212" s="114"/>
-      <c r="T212" s="113"/>
-      <c r="U212" s="81"/>
-      <c r="V212" s="79"/>
-      <c r="W212" s="113"/>
-      <c r="X212" s="150"/>
+      <c r="B212" s="177"/>
+      <c r="C212" s="138"/>
+      <c r="D212" s="139"/>
+      <c r="E212" s="140"/>
+      <c r="F212" s="141"/>
+      <c r="G212" s="139"/>
+      <c r="H212" s="140"/>
+      <c r="I212" s="141"/>
+      <c r="J212" s="164"/>
+      <c r="K212" s="140"/>
+      <c r="L212" s="141"/>
+      <c r="M212" s="139"/>
+      <c r="N212" s="140"/>
+      <c r="O212" s="141"/>
+      <c r="P212" s="139"/>
+      <c r="Q212" s="140"/>
+      <c r="R212" s="141"/>
+      <c r="S212" s="163"/>
+      <c r="T212" s="162"/>
+      <c r="U212" s="141"/>
+      <c r="V212" s="139"/>
+      <c r="W212" s="162"/>
+      <c r="X212" s="87"/>
       <c r="Y212" s="2"/>
       <c r="Z212" s="2"/>
       <c r="AA212" s="2"/>
@@ -10509,29 +10471,29 @@
     </row>
     <row r="213" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="4"/>
-      <c r="B213" s="186"/>
-      <c r="C213" s="78"/>
-      <c r="D213" s="79"/>
-      <c r="E213" s="113"/>
-      <c r="F213" s="81"/>
-      <c r="G213" s="79"/>
-      <c r="H213" s="113"/>
-      <c r="I213" s="81"/>
-      <c r="J213" s="79"/>
-      <c r="K213" s="113"/>
-      <c r="L213" s="81"/>
-      <c r="M213" s="79"/>
-      <c r="N213" s="113"/>
-      <c r="O213" s="81"/>
-      <c r="P213" s="79"/>
-      <c r="Q213" s="113"/>
-      <c r="R213" s="81"/>
-      <c r="S213" s="79"/>
-      <c r="T213" s="113"/>
-      <c r="U213" s="81"/>
-      <c r="V213" s="79"/>
-      <c r="W213" s="80"/>
-      <c r="X213" s="150"/>
+      <c r="B213" s="177"/>
+      <c r="C213" s="138"/>
+      <c r="D213" s="139"/>
+      <c r="E213" s="162"/>
+      <c r="F213" s="141"/>
+      <c r="G213" s="139"/>
+      <c r="H213" s="162"/>
+      <c r="I213" s="141"/>
+      <c r="J213" s="139"/>
+      <c r="K213" s="162"/>
+      <c r="L213" s="141"/>
+      <c r="M213" s="139"/>
+      <c r="N213" s="162"/>
+      <c r="O213" s="141"/>
+      <c r="P213" s="139"/>
+      <c r="Q213" s="162"/>
+      <c r="R213" s="141"/>
+      <c r="S213" s="139"/>
+      <c r="T213" s="162"/>
+      <c r="U213" s="141"/>
+      <c r="V213" s="139"/>
+      <c r="W213" s="140"/>
+      <c r="X213" s="87"/>
       <c r="Y213" s="2"/>
       <c r="Z213" s="2"/>
       <c r="AA213" s="2"/>
@@ -10541,29 +10503,29 @@
     </row>
     <row r="214" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="4"/>
-      <c r="B214" s="186"/>
-      <c r="C214" s="78"/>
-      <c r="D214" s="126"/>
-      <c r="E214" s="113"/>
-      <c r="F214" s="81"/>
-      <c r="G214" s="126"/>
-      <c r="H214" s="113"/>
-      <c r="I214" s="127"/>
-      <c r="J214" s="126"/>
-      <c r="K214" s="113"/>
-      <c r="L214" s="81"/>
-      <c r="M214" s="126"/>
-      <c r="N214" s="113"/>
-      <c r="O214" s="127"/>
-      <c r="P214" s="126"/>
-      <c r="Q214" s="113"/>
-      <c r="R214" s="127"/>
-      <c r="S214" s="126"/>
-      <c r="T214" s="113"/>
-      <c r="U214" s="81"/>
-      <c r="V214" s="126"/>
-      <c r="W214" s="113"/>
-      <c r="X214" s="150"/>
+      <c r="B214" s="177"/>
+      <c r="C214" s="138"/>
+      <c r="D214" s="165"/>
+      <c r="E214" s="162"/>
+      <c r="F214" s="141"/>
+      <c r="G214" s="165"/>
+      <c r="H214" s="162"/>
+      <c r="I214" s="166"/>
+      <c r="J214" s="165"/>
+      <c r="K214" s="162"/>
+      <c r="L214" s="141"/>
+      <c r="M214" s="165"/>
+      <c r="N214" s="162"/>
+      <c r="O214" s="166"/>
+      <c r="P214" s="165"/>
+      <c r="Q214" s="162"/>
+      <c r="R214" s="166"/>
+      <c r="S214" s="165"/>
+      <c r="T214" s="162"/>
+      <c r="U214" s="141"/>
+      <c r="V214" s="165"/>
+      <c r="W214" s="162"/>
+      <c r="X214" s="87"/>
       <c r="Y214" s="2"/>
       <c r="Z214" s="2"/>
       <c r="AA214" s="2"/>
@@ -10573,29 +10535,29 @@
     </row>
     <row r="215" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="4"/>
-      <c r="B215" s="77"/>
-      <c r="C215" s="78"/>
-      <c r="D215" s="79"/>
-      <c r="E215" s="113"/>
-      <c r="F215" s="81"/>
-      <c r="G215" s="79"/>
-      <c r="H215" s="113"/>
-      <c r="I215" s="81"/>
-      <c r="J215" s="79"/>
-      <c r="K215" s="113"/>
-      <c r="L215" s="81"/>
-      <c r="M215" s="79"/>
-      <c r="N215" s="113"/>
-      <c r="O215" s="81"/>
-      <c r="P215" s="79"/>
-      <c r="Q215" s="113"/>
-      <c r="R215" s="81"/>
-      <c r="S215" s="79"/>
-      <c r="T215" s="113"/>
-      <c r="U215" s="81"/>
-      <c r="V215" s="79"/>
-      <c r="W215" s="113"/>
-      <c r="X215" s="150"/>
+      <c r="B215" s="180"/>
+      <c r="C215" s="138"/>
+      <c r="D215" s="139"/>
+      <c r="E215" s="162"/>
+      <c r="F215" s="141"/>
+      <c r="G215" s="139"/>
+      <c r="H215" s="162"/>
+      <c r="I215" s="141"/>
+      <c r="J215" s="139"/>
+      <c r="K215" s="162"/>
+      <c r="L215" s="141"/>
+      <c r="M215" s="139"/>
+      <c r="N215" s="162"/>
+      <c r="O215" s="141"/>
+      <c r="P215" s="139"/>
+      <c r="Q215" s="162"/>
+      <c r="R215" s="141"/>
+      <c r="S215" s="139"/>
+      <c r="T215" s="162"/>
+      <c r="U215" s="141"/>
+      <c r="V215" s="139"/>
+      <c r="W215" s="162"/>
+      <c r="X215" s="87"/>
       <c r="Y215" s="2"/>
       <c r="Z215" s="2"/>
       <c r="AA215" s="2"/>
@@ -10605,29 +10567,29 @@
     </row>
     <row r="216" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="4"/>
-      <c r="B216" s="90"/>
-      <c r="C216" s="154"/>
-      <c r="D216" s="92"/>
-      <c r="E216" s="131"/>
-      <c r="F216" s="95"/>
-      <c r="G216" s="92"/>
-      <c r="H216" s="131"/>
-      <c r="I216" s="95"/>
-      <c r="J216" s="92"/>
-      <c r="K216" s="131"/>
-      <c r="L216" s="95"/>
-      <c r="M216" s="92"/>
-      <c r="N216" s="131"/>
-      <c r="O216" s="95"/>
-      <c r="P216" s="92"/>
-      <c r="Q216" s="131"/>
-      <c r="R216" s="95"/>
-      <c r="S216" s="92"/>
-      <c r="T216" s="131"/>
-      <c r="U216" s="95"/>
-      <c r="V216" s="92"/>
-      <c r="W216" s="131"/>
-      <c r="X216" s="150"/>
+      <c r="B216" s="181"/>
+      <c r="C216" s="167"/>
+      <c r="D216" s="148"/>
+      <c r="E216" s="168"/>
+      <c r="F216" s="151"/>
+      <c r="G216" s="148"/>
+      <c r="H216" s="168"/>
+      <c r="I216" s="151"/>
+      <c r="J216" s="148"/>
+      <c r="K216" s="168"/>
+      <c r="L216" s="151"/>
+      <c r="M216" s="148"/>
+      <c r="N216" s="168"/>
+      <c r="O216" s="151"/>
+      <c r="P216" s="148"/>
+      <c r="Q216" s="168"/>
+      <c r="R216" s="151"/>
+      <c r="S216" s="148"/>
+      <c r="T216" s="168"/>
+      <c r="U216" s="151"/>
+      <c r="V216" s="148"/>
+      <c r="W216" s="168"/>
+      <c r="X216" s="87"/>
       <c r="Y216" s="2"/>
       <c r="Z216" s="2"/>
       <c r="AA216" s="2"/>
@@ -10637,31 +10599,31 @@
     </row>
     <row r="217" spans="1:30" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="4"/>
-      <c r="B217" s="133" t="s">
+      <c r="B217" s="182" t="s">
         <v>27</v>
       </c>
-      <c r="C217" s="134"/>
-      <c r="D217" s="105"/>
-      <c r="E217" s="106"/>
-      <c r="F217" s="135"/>
-      <c r="G217" s="105"/>
-      <c r="H217" s="106"/>
-      <c r="I217" s="135"/>
-      <c r="J217" s="105"/>
-      <c r="K217" s="106"/>
-      <c r="L217" s="135"/>
-      <c r="M217" s="105"/>
-      <c r="N217" s="106"/>
-      <c r="O217" s="135"/>
-      <c r="P217" s="105"/>
-      <c r="Q217" s="106"/>
-      <c r="R217" s="135"/>
-      <c r="S217" s="105"/>
-      <c r="T217" s="106"/>
-      <c r="U217" s="135"/>
-      <c r="V217" s="105"/>
-      <c r="W217" s="106"/>
-      <c r="X217" s="150"/>
+      <c r="C217" s="169"/>
+      <c r="D217" s="157"/>
+      <c r="E217" s="158"/>
+      <c r="F217" s="170"/>
+      <c r="G217" s="157"/>
+      <c r="H217" s="158"/>
+      <c r="I217" s="170"/>
+      <c r="J217" s="157"/>
+      <c r="K217" s="158"/>
+      <c r="L217" s="170"/>
+      <c r="M217" s="157"/>
+      <c r="N217" s="158"/>
+      <c r="O217" s="170"/>
+      <c r="P217" s="157"/>
+      <c r="Q217" s="158"/>
+      <c r="R217" s="170"/>
+      <c r="S217" s="157"/>
+      <c r="T217" s="158"/>
+      <c r="U217" s="170"/>
+      <c r="V217" s="157"/>
+      <c r="W217" s="158"/>
+      <c r="X217" s="87"/>
       <c r="Y217" s="2"/>
       <c r="Z217" s="2"/>
       <c r="AA217" s="2"/>
@@ -10671,31 +10633,31 @@
     </row>
     <row r="218" spans="1:30" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="4"/>
-      <c r="B218" s="139" t="s">
+      <c r="B218" s="183" t="s">
         <v>28</v>
       </c>
-      <c r="C218" s="155"/>
-      <c r="D218" s="141"/>
-      <c r="E218" s="142"/>
-      <c r="F218" s="144"/>
-      <c r="G218" s="141"/>
-      <c r="H218" s="142"/>
-      <c r="I218" s="144"/>
-      <c r="J218" s="141"/>
-      <c r="K218" s="142"/>
-      <c r="L218" s="144"/>
-      <c r="M218" s="141"/>
-      <c r="N218" s="142"/>
-      <c r="O218" s="144"/>
-      <c r="P218" s="141"/>
-      <c r="Q218" s="142"/>
-      <c r="R218" s="144"/>
-      <c r="S218" s="141"/>
-      <c r="T218" s="142"/>
-      <c r="U218" s="144"/>
-      <c r="V218" s="141"/>
-      <c r="W218" s="142"/>
-      <c r="X218" s="150"/>
+      <c r="C218" s="171"/>
+      <c r="D218" s="172"/>
+      <c r="E218" s="173"/>
+      <c r="F218" s="174"/>
+      <c r="G218" s="172"/>
+      <c r="H218" s="173"/>
+      <c r="I218" s="174"/>
+      <c r="J218" s="172"/>
+      <c r="K218" s="173"/>
+      <c r="L218" s="174"/>
+      <c r="M218" s="172"/>
+      <c r="N218" s="173"/>
+      <c r="O218" s="174"/>
+      <c r="P218" s="172"/>
+      <c r="Q218" s="173"/>
+      <c r="R218" s="174"/>
+      <c r="S218" s="172"/>
+      <c r="T218" s="173"/>
+      <c r="U218" s="174"/>
+      <c r="V218" s="172"/>
+      <c r="W218" s="173"/>
+      <c r="X218" s="87"/>
       <c r="Y218" s="2"/>
       <c r="Z218" s="2"/>
       <c r="AA218" s="2"/>
@@ -10705,28 +10667,28 @@
     </row>
     <row r="219" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="2"/>
-      <c r="B219" s="156"/>
-      <c r="C219" s="156"/>
-      <c r="D219" s="156"/>
-      <c r="E219" s="156"/>
-      <c r="F219" s="156"/>
-      <c r="G219" s="156"/>
-      <c r="H219" s="156"/>
-      <c r="I219" s="156"/>
-      <c r="J219" s="156"/>
-      <c r="K219" s="156"/>
-      <c r="L219" s="156"/>
-      <c r="M219" s="156"/>
-      <c r="N219" s="156"/>
-      <c r="O219" s="156"/>
-      <c r="P219" s="156"/>
-      <c r="Q219" s="156"/>
-      <c r="R219" s="156"/>
-      <c r="S219" s="156"/>
-      <c r="T219" s="156"/>
-      <c r="U219" s="156"/>
-      <c r="V219" s="156"/>
-      <c r="W219" s="156"/>
+      <c r="B219" s="90"/>
+      <c r="C219" s="90"/>
+      <c r="D219" s="90"/>
+      <c r="E219" s="90"/>
+      <c r="F219" s="90"/>
+      <c r="G219" s="90"/>
+      <c r="H219" s="90"/>
+      <c r="I219" s="90"/>
+      <c r="J219" s="90"/>
+      <c r="K219" s="90"/>
+      <c r="L219" s="90"/>
+      <c r="M219" s="90"/>
+      <c r="N219" s="90"/>
+      <c r="O219" s="90"/>
+      <c r="P219" s="90"/>
+      <c r="Q219" s="90"/>
+      <c r="R219" s="90"/>
+      <c r="S219" s="90"/>
+      <c r="T219" s="90"/>
+      <c r="U219" s="90"/>
+      <c r="V219" s="90"/>
+      <c r="W219" s="90"/>
       <c r="X219" s="2"/>
       <c r="Y219" s="2"/>
       <c r="Z219" s="2"/>
@@ -10769,27 +10731,27 @@
     </row>
     <row r="221" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2"/>
-      <c r="B221" s="157">
+      <c r="B221" s="91">
         <v>1</v>
       </c>
-      <c r="C221" s="112" t="s">
+      <c r="C221" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="D221" s="158">
+      <c r="D221" s="92">
         <f>COUNTIF(B2:W181,C221)</f>
         <v>0</v>
       </c>
       <c r="E221" s="2"/>
-      <c r="F221" s="159"/>
-      <c r="G221" s="159"/>
-      <c r="H221" s="160"/>
-      <c r="I221" s="161" t="s">
+      <c r="F221" s="93"/>
+      <c r="G221" s="93"/>
+      <c r="H221" s="94"/>
+      <c r="I221" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="J221" s="162"/>
+      <c r="J221" s="96"/>
       <c r="K221" s="2"/>
-      <c r="L221" s="196"/>
-      <c r="M221" s="197" t="s">
+      <c r="L221" s="106"/>
+      <c r="M221" s="107" t="s">
         <v>58</v>
       </c>
       <c r="N221" s="2"/>
@@ -10812,27 +10774,27 @@
     </row>
     <row r="222" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2"/>
-      <c r="B222" s="157">
+      <c r="B222" s="91">
         <v>2</v>
       </c>
-      <c r="C222" s="112" t="s">
+      <c r="C222" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="D222" s="158">
+      <c r="D222" s="92">
         <f>COUNTIF(B2:W181,C222)</f>
         <v>0</v>
       </c>
       <c r="E222" s="2"/>
-      <c r="F222" s="159"/>
-      <c r="G222" s="159"/>
-      <c r="H222" s="160"/>
-      <c r="I222" s="161" t="s">
+      <c r="F222" s="93"/>
+      <c r="G222" s="93"/>
+      <c r="H222" s="94"/>
+      <c r="I222" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="J222" s="162"/>
+      <c r="J222" s="96"/>
       <c r="K222" s="2"/>
-      <c r="L222" s="198"/>
-      <c r="M222" s="197" t="s">
+      <c r="L222" s="108"/>
+      <c r="M222" s="107" t="s">
         <v>59</v>
       </c>
       <c r="N222" s="2"/>
@@ -10855,24 +10817,24 @@
     </row>
     <row r="223" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2"/>
-      <c r="B223" s="157">
+      <c r="B223" s="91">
         <v>3</v>
       </c>
-      <c r="C223" s="112" t="s">
+      <c r="C223" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="D223" s="158">
+      <c r="D223" s="92">
         <f>COUNTIF(B2:W181,C223)</f>
         <v>0</v>
       </c>
       <c r="E223" s="2"/>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
-      <c r="H223" s="160"/>
-      <c r="I223" s="161" t="s">
+      <c r="H223" s="94"/>
+      <c r="I223" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="J223" s="162"/>
+      <c r="J223" s="96"/>
       <c r="K223" s="2"/>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -10896,22 +10858,22 @@
     </row>
     <row r="224" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2"/>
-      <c r="B224" s="157">
+      <c r="B224" s="91">
         <v>4</v>
       </c>
-      <c r="C224" s="112" t="s">
+      <c r="C224" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="D224" s="158">
+      <c r="D224" s="92">
         <f>COUNTIF(B2:W181,C224)</f>
         <v>0</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
-      <c r="H224" s="160"/>
-      <c r="I224" s="163"/>
-      <c r="J224" s="162"/>
+      <c r="H224" s="94"/>
+      <c r="I224" s="97"/>
+      <c r="J224" s="96"/>
       <c r="K224" s="2"/>
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
@@ -10935,24 +10897,24 @@
     </row>
     <row r="225" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2"/>
-      <c r="B225" s="157">
+      <c r="B225" s="91">
         <v>5</v>
       </c>
-      <c r="C225" s="112" t="s">
+      <c r="C225" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="D225" s="158">
+      <c r="D225" s="92">
         <f>COUNTIF(B2:W181,C225)</f>
         <v>0</v>
       </c>
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
-      <c r="H225" s="160"/>
-      <c r="I225" s="164" t="s">
+      <c r="H225" s="94"/>
+      <c r="I225" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="J225" s="162"/>
+      <c r="J225" s="96"/>
       <c r="K225" s="2"/>
       <c r="L225" s="2"/>
       <c r="M225" s="2"/>
@@ -10976,24 +10938,24 @@
     </row>
     <row r="226" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2"/>
-      <c r="B226" s="157">
+      <c r="B226" s="91">
         <v>6</v>
       </c>
-      <c r="C226" s="112" t="s">
+      <c r="C226" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="D226" s="158">
+      <c r="D226" s="92">
         <f>COUNTIF(B2:W182,C226)</f>
         <v>0</v>
       </c>
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
-      <c r="H226" s="160"/>
-      <c r="I226" s="165" t="s">
+      <c r="H226" s="94"/>
+      <c r="I226" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="J226" s="162"/>
+      <c r="J226" s="96"/>
       <c r="K226" s="2"/>
       <c r="L226" s="2"/>
       <c r="M226" s="2"/>
@@ -11017,24 +10979,24 @@
     </row>
     <row r="227" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2"/>
-      <c r="B227" s="157">
+      <c r="B227" s="91">
         <v>7</v>
       </c>
-      <c r="C227" s="112" t="s">
+      <c r="C227" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="D227" s="158">
+      <c r="D227" s="92">
         <f>COUNTIF(B2:W181,C227)</f>
         <v>0</v>
       </c>
       <c r="E227" s="2"/>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
-      <c r="H227" s="160"/>
-      <c r="I227" s="161" t="s">
+      <c r="H227" s="94"/>
+      <c r="I227" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="J227" s="162"/>
+      <c r="J227" s="96"/>
       <c r="K227" s="2"/>
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
@@ -11058,24 +11020,24 @@
     </row>
     <row r="228" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2"/>
-      <c r="B228" s="157">
+      <c r="B228" s="91">
         <v>8</v>
       </c>
-      <c r="C228" s="112" t="s">
+      <c r="C228" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="D228" s="158">
+      <c r="D228" s="92">
         <f>COUNTIF(B2:W181,C228)</f>
         <v>0</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
-      <c r="H228" s="160"/>
-      <c r="I228" s="161" t="s">
+      <c r="H228" s="94"/>
+      <c r="I228" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="J228" s="162"/>
+      <c r="J228" s="96"/>
       <c r="K228" s="2"/>
       <c r="L228" s="2"/>
       <c r="M228" s="2"/>
@@ -11099,24 +11061,24 @@
     </row>
     <row r="229" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2"/>
-      <c r="B229" s="157">
+      <c r="B229" s="91">
         <v>9</v>
       </c>
-      <c r="C229" s="112" t="s">
+      <c r="C229" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="D229" s="158">
+      <c r="D229" s="92">
         <f>COUNTIF(B2:W181,C229)</f>
         <v>0</v>
       </c>
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
-      <c r="H229" s="160"/>
-      <c r="I229" s="166" t="s">
+      <c r="H229" s="94"/>
+      <c r="I229" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="J229" s="162"/>
+      <c r="J229" s="96"/>
       <c r="K229" s="2"/>
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
@@ -11140,24 +11102,24 @@
     </row>
     <row r="230" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2"/>
-      <c r="B230" s="157">
+      <c r="B230" s="91">
         <v>10</v>
       </c>
-      <c r="C230" s="112" t="s">
+      <c r="C230" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="D230" s="158">
+      <c r="D230" s="92">
         <f>COUNTIF(B3:W182,C230)</f>
         <v>0</v>
       </c>
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
-      <c r="H230" s="160"/>
-      <c r="I230" s="161" t="s">
+      <c r="H230" s="94"/>
+      <c r="I230" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="J230" s="162"/>
+      <c r="J230" s="96"/>
       <c r="K230" s="2"/>
       <c r="L230" s="2"/>
       <c r="M230" s="2"/>
@@ -11181,24 +11143,24 @@
     </row>
     <row r="231" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2"/>
-      <c r="B231" s="157">
+      <c r="B231" s="91">
         <v>11</v>
       </c>
-      <c r="C231" s="112" t="s">
+      <c r="C231" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D231" s="158">
+      <c r="D231" s="92">
         <f>COUNTIF(B2:W181,C231)</f>
         <v>0</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
-      <c r="H231" s="160"/>
-      <c r="I231" s="166" t="s">
+      <c r="H231" s="94"/>
+      <c r="I231" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="J231" s="162"/>
+      <c r="J231" s="96"/>
       <c r="K231" s="2"/>
       <c r="L231" s="2"/>
       <c r="M231" s="2"/>
@@ -11222,24 +11184,24 @@
     </row>
     <row r="232" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2"/>
-      <c r="B232" s="157">
+      <c r="B232" s="91">
         <v>12</v>
       </c>
-      <c r="C232" s="112" t="s">
+      <c r="C232" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D232" s="158">
+      <c r="D232" s="92">
         <f>COUNTIF(B2:W181,C232)</f>
         <v>0</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
-      <c r="H232" s="160"/>
-      <c r="I232" s="161" t="s">
+      <c r="H232" s="94"/>
+      <c r="I232" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="J232" s="162"/>
+      <c r="J232" s="96"/>
       <c r="K232" s="2"/>
       <c r="L232" s="2"/>
       <c r="M232" s="2"/>
@@ -11263,22 +11225,22 @@
     </row>
     <row r="233" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2"/>
-      <c r="B233" s="157">
+      <c r="B233" s="91">
         <v>13</v>
       </c>
-      <c r="C233" s="112" t="s">
+      <c r="C233" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="D233" s="158">
+      <c r="D233" s="92">
         <f>COUNTIF(B6:W220,C233)</f>
         <v>0</v>
       </c>
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
-      <c r="H233" s="160"/>
-      <c r="I233" s="167"/>
-      <c r="J233" s="162"/>
+      <c r="H233" s="94"/>
+      <c r="I233" s="101"/>
+      <c r="J233" s="96"/>
       <c r="K233" s="2"/>
       <c r="L233" s="2"/>
       <c r="M233" s="2"/>
@@ -11302,24 +11264,24 @@
     </row>
     <row r="234" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2"/>
-      <c r="B234" s="157">
+      <c r="B234" s="91">
         <v>14</v>
       </c>
-      <c r="C234" s="112" t="s">
+      <c r="C234" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D234" s="158">
+      <c r="D234" s="92">
         <f>COUNTIF(B2:W181,C234)</f>
         <v>0</v>
       </c>
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
-      <c r="H234" s="160"/>
-      <c r="I234" s="161" t="s">
+      <c r="H234" s="94"/>
+      <c r="I234" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="J234" s="162"/>
+      <c r="J234" s="96"/>
       <c r="K234" s="2"/>
       <c r="L234" s="2"/>
       <c r="M234" s="2"/>
@@ -11343,24 +11305,24 @@
     </row>
     <row r="235" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2"/>
-      <c r="B235" s="157">
+      <c r="B235" s="91">
         <v>15</v>
       </c>
-      <c r="C235" s="112" t="s">
+      <c r="C235" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="D235" s="158">
+      <c r="D235" s="92">
         <f>COUNTIF(B2:W181,C235)</f>
         <v>0</v>
       </c>
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
-      <c r="H235" s="160"/>
-      <c r="I235" s="161" t="s">
+      <c r="H235" s="94"/>
+      <c r="I235" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="J235" s="162"/>
+      <c r="J235" s="96"/>
       <c r="K235" s="2"/>
       <c r="L235" s="2"/>
       <c r="M235" s="2"/>
@@ -11384,24 +11346,24 @@
     </row>
     <row r="236" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2"/>
-      <c r="B236" s="157">
+      <c r="B236" s="91">
         <v>16</v>
       </c>
-      <c r="C236" s="168" t="s">
+      <c r="C236" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="D236" s="158">
+      <c r="D236" s="92">
         <f>COUNTIF(B4:W183,C236)</f>
         <v>0</v>
       </c>
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
-      <c r="H236" s="160"/>
-      <c r="I236" s="161" t="s">
+      <c r="H236" s="94"/>
+      <c r="I236" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="J236" s="162"/>
+      <c r="J236" s="96"/>
       <c r="K236" s="2"/>
       <c r="L236" s="2"/>
       <c r="M236" s="2"/>
@@ -11425,21 +11387,21 @@
     </row>
     <row r="237" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2"/>
-      <c r="B237" s="157">
+      <c r="B237" s="91">
         <v>17</v>
       </c>
-      <c r="C237" s="168" t="s">
+      <c r="C237" s="102" t="s">
         <v>50</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
-      <c r="H237" s="160"/>
-      <c r="I237" s="161" t="s">
+      <c r="H237" s="94"/>
+      <c r="I237" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="J237" s="162"/>
+      <c r="J237" s="96"/>
       <c r="K237" s="2"/>
       <c r="L237" s="2"/>
       <c r="M237" s="2"/>
@@ -11463,21 +11425,21 @@
     </row>
     <row r="238" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2"/>
-      <c r="B238" s="157">
+      <c r="B238" s="91">
         <v>18</v>
       </c>
-      <c r="C238" s="168" t="s">
+      <c r="C238" s="102" t="s">
         <v>52</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
-      <c r="H238" s="160"/>
-      <c r="I238" s="169" t="s">
+      <c r="H238" s="94"/>
+      <c r="I238" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="J238" s="162"/>
+      <c r="J238" s="96"/>
       <c r="K238" s="2"/>
       <c r="L238" s="2"/>
       <c r="M238" s="2"/>
@@ -11501,21 +11463,21 @@
     </row>
     <row r="239" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2"/>
-      <c r="B239" s="157">
+      <c r="B239" s="91">
         <v>19</v>
       </c>
-      <c r="C239" s="168" t="s">
+      <c r="C239" s="102" t="s">
         <v>54</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
-      <c r="H239" s="160"/>
-      <c r="I239" s="170" t="s">
+      <c r="H239" s="94"/>
+      <c r="I239" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J239" s="162"/>
+      <c r="J239" s="96"/>
       <c r="K239" s="2"/>
       <c r="L239" s="2"/>
       <c r="M239" s="2"/>
@@ -11545,11 +11507,11 @@
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
-      <c r="H240" s="160"/>
-      <c r="I240" s="171" t="s">
+      <c r="H240" s="94"/>
+      <c r="I240" s="105" t="s">
         <v>56</v>
       </c>
-      <c r="J240" s="162"/>
+      <c r="J240" s="96"/>
       <c r="K240" s="2"/>
       <c r="L240" s="2"/>
       <c r="M240" s="2"/>
@@ -11580,7 +11542,7 @@
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
-      <c r="I241" s="156"/>
+      <c r="I241" s="90"/>
       <c r="J241" s="2"/>
       <c r="K241" s="2"/>
       <c r="L241" s="2"/>
@@ -15167,7 +15129,7 @@
       <c r="I353" s="2"/>
       <c r="J353" s="2"/>
       <c r="K353" s="2"/>
-      <c r="L353" s="168" t="s">
+      <c r="L353" s="102" t="s">
         <v>57</v>
       </c>
       <c r="M353" s="2"/>
@@ -15191,31 +15153,36 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="U183:W183"/>
-    <mergeCell ref="B199:B203"/>
-    <mergeCell ref="I183:K183"/>
-    <mergeCell ref="B205:B214"/>
-    <mergeCell ref="C183:E183"/>
-    <mergeCell ref="F183:H183"/>
-    <mergeCell ref="L183:N183"/>
-    <mergeCell ref="O183:Q183"/>
-    <mergeCell ref="R183:T183"/>
-    <mergeCell ref="G199:G201"/>
-    <mergeCell ref="U147:W147"/>
-    <mergeCell ref="B163:B167"/>
-    <mergeCell ref="I147:K147"/>
-    <mergeCell ref="R75:T75"/>
-    <mergeCell ref="B169:B178"/>
-    <mergeCell ref="B127:B131"/>
-    <mergeCell ref="G127:G129"/>
-    <mergeCell ref="B133:B142"/>
-    <mergeCell ref="C147:E147"/>
-    <mergeCell ref="F147:H147"/>
-    <mergeCell ref="L147:N147"/>
-    <mergeCell ref="O147:Q147"/>
-    <mergeCell ref="R147:T147"/>
-    <mergeCell ref="G91:G93"/>
-    <mergeCell ref="G163:G165"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="B61:B71"/>
+    <mergeCell ref="X3:X19"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="X20:X24"/>
+    <mergeCell ref="B25:B35"/>
+    <mergeCell ref="X25:X27"/>
+    <mergeCell ref="X31:X42"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="G55:G57"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="O39:Q39"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="U39:W39"/>
     <mergeCell ref="B55:B59"/>
     <mergeCell ref="U75:W75"/>
     <mergeCell ref="B91:B95"/>
@@ -15232,38 +15199,33 @@
     <mergeCell ref="I75:K75"/>
     <mergeCell ref="L75:N75"/>
     <mergeCell ref="O75:Q75"/>
-    <mergeCell ref="B61:B71"/>
-    <mergeCell ref="X3:X19"/>
-    <mergeCell ref="B19:B23"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="X20:X24"/>
-    <mergeCell ref="B25:B35"/>
-    <mergeCell ref="X25:X27"/>
-    <mergeCell ref="X31:X42"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="G55:G57"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="O39:Q39"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="U39:W39"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="U3:W3"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U147:W147"/>
+    <mergeCell ref="B163:B167"/>
+    <mergeCell ref="I147:K147"/>
+    <mergeCell ref="R75:T75"/>
+    <mergeCell ref="B169:B178"/>
+    <mergeCell ref="B127:B131"/>
+    <mergeCell ref="G127:G129"/>
+    <mergeCell ref="B133:B142"/>
+    <mergeCell ref="C147:E147"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="L147:N147"/>
+    <mergeCell ref="O147:Q147"/>
+    <mergeCell ref="R147:T147"/>
+    <mergeCell ref="G91:G93"/>
+    <mergeCell ref="G163:G165"/>
+    <mergeCell ref="U183:W183"/>
+    <mergeCell ref="B199:B203"/>
+    <mergeCell ref="I183:K183"/>
+    <mergeCell ref="B205:B214"/>
+    <mergeCell ref="C183:E183"/>
+    <mergeCell ref="F183:H183"/>
+    <mergeCell ref="L183:N183"/>
+    <mergeCell ref="O183:Q183"/>
+    <mergeCell ref="R183:T183"/>
+    <mergeCell ref="G199:G201"/>
   </mergeCells>
-  <phoneticPr fontId="11"/>
+  <phoneticPr fontId="9"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
